--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="504">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -295,7 +295,7 @@
     <t>Cards seeded from the reference guide are flagged as needing Market/Vertical/Standards detail.</t>
   </si>
   <si>
-    <t>businessView.js · needsEnrichment</t>
+    <t>business/index.js · needsEnrichment (data flag); businessView.js renders it</t>
   </si>
   <si>
     <t>3222</t>
@@ -712,19 +712,19 @@
     <t>Build an in-app document preview from the current view and options.</t>
   </si>
   <si>
-    <t>genModal.js · buildDoc()</t>
+    <t>genModal.js · buildDoc() / buildBusinessPreview()</t>
   </si>
   <si>
     <t>3255, 3256</t>
   </si>
   <si>
-    <t>Word export (.doc)</t>
-  </si>
-  <si>
-    <t>Download a styled Word document (System or Business content).</t>
-  </si>
-  <si>
-    <t>genModal.js · downloadWord()</t>
+    <t>Word export (.docx)</t>
+  </si>
+  <si>
+    <t>Download a branded Open Box .docx (System or Business content), generated with the docx library.</t>
+  </si>
+  <si>
+    <t>genModal.js · downloadWord() → docxExport.js · generateDocx(); house style from obDocStyle.js</t>
   </si>
   <si>
     <t>3255</t>
@@ -736,7 +736,7 @@
     <t>Open a print-ready styled page for Save-as-PDF.</t>
   </si>
   <si>
-    <t>genModal.js · downloadPDF()</t>
+    <t>genModal.js · downloadPDF(); house style from obDocStyle.js · houseStyleCSS()</t>
   </si>
   <si>
     <t>3256</t>
@@ -748,7 +748,7 @@
     <t>Choose to include overview, activities, prerequisites, and associated screens.</t>
   </si>
   <si>
-    <t>genModal.js</t>
+    <t>genModal.js · buildDoc(); docxExport.js · processBlock()</t>
   </si>
   <si>
     <t>Scope include filters</t>
@@ -757,7 +757,7 @@
     <t>Include/exclude Core, Custom, Out-of-Scope, and Untagged items in the document.</t>
   </si>
   <si>
-    <t>genModal.js · getScopeIncludes()</t>
+    <t>genModal.js · getScopeIncludes(); docxExport.js · scopePass()</t>
   </si>
   <si>
     <t>Scope summary table</t>
@@ -766,7 +766,7 @@
     <t>Document opens with a table of process counts per scope (total vs included).</t>
   </si>
   <si>
-    <t>genModal.js · buildScopeSummary()</t>
+    <t>genModal.js · buildScopeSummary(); docxExport.js · generateDocx()</t>
   </si>
   <si>
     <t>Current-tab or all-modules scope</t>
@@ -775,7 +775,7 @@
     <t>Export just the active module or all visible modules.</t>
   </si>
   <si>
-    <t>genModal.js · getDocTabs()</t>
+    <t>genModal.js · getDocTabs() / businessDocTabs()</t>
   </si>
   <si>
     <t>Business document mode</t>
@@ -784,7 +784,7 @@
     <t>Business view exports overview/activities plus market variations, vertical detail, and standards.</t>
   </si>
   <si>
-    <t>genModal.js · buildBusinessBody()</t>
+    <t>docxExport.js · generateBusinessDocx(); genModal.js · buildBusinessPreview()</t>
   </si>
   <si>
     <t>Detail Content</t>
@@ -883,10 +883,13 @@
     <t>Ensure each value stream has a clear, standardised naming convention accompanied by a description that explains its scope and purpose.</t>
   </si>
   <si>
+    <t>business/valueStreams.js · VALUE_STREAMS (label + note per stream; title + note per L2 group)</t>
+  </si>
+  <si>
     <t>New Requirement</t>
   </si>
   <si>
-    <t>Story 3270 under Feature 3197 (CRE Powered Value Streams Taxonomy). Added to DevOps. | Tested 2026-08-18</t>
+    <t>Story 3270 under Feature 3197 (CRE Powered Value Streams Taxonomy). Tested 2026-08-18. Confirmed Done 2026-09-14 — every value stream carries a label and a note, every L2 group a title and a note.</t>
   </si>
   <si>
     <t>Cross-market value-stream validation (US / UK)</t>
@@ -955,16 +958,25 @@
     <t>Clone an existing client version as a starting point for a similar client.</t>
   </si>
   <si>
-    <t>Future enhancement. Story 3283 under Feature 3211 (Client Versions). | Tested 2026-08-18</t>
+    <t>versionMenu.js · startDuplicate(); versions.js · duplicateVersion()</t>
+  </si>
+  <si>
+    <t>Story 3283 under Feature 3211 (Client Versions). Tested 2026-08-18. Confirmed Done 2026-09-14 — Duplicate control on each card in the Versions panel.</t>
   </si>
   <si>
     <t>Richer export templates</t>
   </si>
   <si>
-    <t>Branded documents with cover page, table of contents, and executive summary.</t>
-  </si>
-  <si>
-    <t>Future enhancement. Story 3284 under Feature 3213 (Word &amp; PDF Export).</t>
+    <t>Branded documents with cover page, table of contents, and executive summary. Cover page and TOC delivered; executive summary outstanding.</t>
+  </si>
+  <si>
+    <t>docxExport.js · buildBrandedDocument() (cover + TOC) — executive summary not built</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Partially delivered: cover page and auto table of contents built by the Open Box house-style export (70a941a, fa6d8fb); cover client name added 2026-09-14 (d349d98). Executive summary is the only outstanding element. Story 3284 under Feature 3213 (Word &amp; PDF Export).</t>
   </si>
   <si>
     <t>Progress dashboard</t>
@@ -997,10 +1009,46 @@
     <t>Added 2026-08-18. Future enhancement — search/filter versions panel when version count grows.</t>
   </si>
   <si>
+    <t>Discovery Baseline built-in version</t>
+  </si>
+  <si>
+    <t>Default landing version for a new engagement: loads the full taxonomy and link set with every scope and coverage tag cleared, so discovery starts untagged. Read-only.</t>
+  </si>
+  <si>
+    <t>main.js · loadVersion() / clearAllTags(); state.js · suppressAutoScope; versionMenu.js</t>
+  </si>
+  <si>
+    <t>— none (story needed)</t>
+  </si>
+  <si>
+    <t>App-only feature with no DevOps story — one should be raised. Identified 2026-09-09.</t>
+  </si>
+  <si>
+    <t>Built-in version edit lock</t>
+  </si>
+  <si>
+    <t>Save Changes is hidden and overwrite is blocked while a built-in baseline (Original / Discovery Baseline) is active, so factory content cannot be overwritten.</t>
+  </si>
+  <si>
+    <t>state.js · BUILTIN_VERSIONS; main.js · updateSaveChangesBtn() / saveChangesToVersion()</t>
+  </si>
+  <si>
+    <t>Client name on cover from version title</t>
+  </si>
+  <si>
+    <t>The document cover and footer take the client name from the saved version title; the built-in baselines fall back to a "Client Name" placeholder.</t>
+  </si>
+  <si>
+    <t>genModal.js · coverClientName(); docxExport.js · buildBrandedDocument()</t>
+  </si>
+  <si>
+    <t>Added 2026-09-14 (commit d349d98). Verified by unzipping the generated .docx — the cover runs and footer1.xml both carry the version title. No DevOps story yet.</t>
+  </si>
+  <si>
     <t>DevOps Backlog ⇄ App Feature Comparison</t>
   </si>
   <si>
-    <t>54 board stories · 50 matched to existing features · 4 on board only · 0 in app only · 0 new requirements pending. All new requirements and app-only features now have DevOps stories.</t>
+    <t>60 board stories referenced by the Feature List · 4 on board only (section B) · 3 in app only, no story yet (see Feature List) · 0 new requirements pending. Section E lists the nice-to-have stories 3281–3287. Updated 2026-09-14.</t>
   </si>
   <si>
     <t>A · Matched — board story ↔ existing feature</t>
@@ -1357,6 +1405,51 @@
     <t>Added: Story 3274</t>
   </si>
   <si>
+    <t>E · Nice to have — on the board, not in the delivered baseline</t>
+  </si>
+  <si>
+    <t>3281</t>
+  </si>
+  <si>
+    <t>Future enhancement. Feature List #76.</t>
+  </si>
+  <si>
+    <t>3282</t>
+  </si>
+  <si>
+    <t>Future enhancement. Feature List #77.</t>
+  </si>
+  <si>
+    <t>3283</t>
+  </si>
+  <si>
+    <t>Built: versionMenu.js · startDuplicate(). Feature List #78.</t>
+  </si>
+  <si>
+    <t>3284</t>
+  </si>
+  <si>
+    <t>Partially built</t>
+  </si>
+  <si>
+    <t>Cover page + TOC built; executive summary outstanding. Feature List #79.</t>
+  </si>
+  <si>
+    <t>3285</t>
+  </si>
+  <si>
+    <t>Future enhancement. Feature List #80.</t>
+  </si>
+  <si>
+    <t>3286</t>
+  </si>
+  <si>
+    <t>Future enhancement. Feature List #81.</t>
+  </si>
+  <si>
+    <t>Future enhancement. Feature List #82.</t>
+  </si>
+  <si>
     <t>Feature &amp; QA Summary</t>
   </si>
   <si>
@@ -1369,9 +1462,6 @@
     <t>% of total</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Backlog</t>
   </si>
   <si>
@@ -1381,9 +1471,6 @@
     <t>Total</t>
   </si>
   <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>Failed</t>
   </si>
   <si>
@@ -1417,7 +1504,7 @@
     <t>Allowed values &amp; meaning</t>
   </si>
   <si>
-    <t>Existing = already in the app (source-derived baseline).  DevOps Backlog = folded in from the board.</t>
+    <t>Existing = already in the app (source-derived baseline).  DevOps Backlog = folded in from the board.  New Requirement = raised during review.  Nice to Have = future enhancement.</t>
   </si>
   <si>
     <t>Done = built in the codebase.  In Progress = under active development.  Not Started / Backlog = planned only.  Blocked = cannot proceed.</t>
@@ -1426,7 +1513,7 @@
     <t>Yes = QA complete.  No = not yet tested.  Partial = some testing done.  N/A = no QA needed.</t>
   </si>
   <si>
-    <t>Not Tested · In Progress · Passed · Failed · Blocked — the outcome/progress of QA.</t>
+    <t>Not Tested · In Progress · Pass · Failed · Blocked — the outcome/progress of QA.</t>
   </si>
   <si>
     <t>Matched Azure DevOps story ID(s). Multiple IDs = feature spans several stories.</t>
@@ -2269,7 +2356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K86"/>
+  <dimension ref="A1:K89"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -4815,13 +4902,13 @@
         <v>288</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="H75" s="10" t="s">
         <v>109</v>
@@ -4833,7 +4920,7 @@
         <v>3270</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4844,16 +4931,16 @@
         <v>64</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E76" s="18" t="s">
         <v>272</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G76" s="10" t="s">
         <v>273</v>
@@ -4868,7 +4955,7 @@
         <v>3271</v>
       </c>
       <c r="K76" s="20" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -4879,16 +4966,16 @@
         <v>140</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>272</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G77" s="10" t="s">
         <v>273</v>
@@ -4903,7 +4990,7 @@
         <v>3272</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -4911,19 +4998,19 @@
         <v>74</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E78" s="18" t="s">
         <v>272</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G78" s="10" t="s">
         <v>273</v>
@@ -4938,7 +5025,7 @@
         <v>3273</v>
       </c>
       <c r="K78" s="20" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -4949,16 +5036,16 @@
         <v>185</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>272</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="G79" s="10" t="s">
         <v>273</v>
@@ -4973,7 +5060,7 @@
         <v>3274</v>
       </c>
       <c r="K79" s="13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -4984,16 +5071,16 @@
         <v>185</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E80" s="9" t="s">
         <v>272</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G80" s="10" t="s">
         <v>273</v>
@@ -5008,7 +5095,7 @@
         <v>3281</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5019,16 +5106,16 @@
         <v>13</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>272</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G81" s="10" t="s">
         <v>273</v>
@@ -5043,7 +5130,7 @@
         <v>3282</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5054,19 +5141,19 @@
         <v>185</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="H82" s="10" t="s">
         <v>109</v>
@@ -5078,7 +5165,7 @@
         <v>3283</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5089,22 +5176,22 @@
         <v>229</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>272</v>
+        <v>318</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>273</v>
+        <v>319</v>
       </c>
       <c r="H83" s="10" t="s">
-        <v>280</v>
+        <v>19</v>
       </c>
       <c r="I83" s="10" t="s">
         <v>20</v>
@@ -5113,7 +5200,7 @@
         <v>3284</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5124,16 +5211,16 @@
         <v>97</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>272</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>273</v>
@@ -5148,7 +5235,7 @@
         <v>3285</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5159,16 +5246,16 @@
         <v>121</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>272</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>273</v>
@@ -5183,7 +5270,7 @@
         <v>3286</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -5194,16 +5281,16 @@
         <v>185</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="E86" s="25" t="s">
         <v>272</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="G86" s="25" t="s">
         <v>273</v>
@@ -5215,10 +5302,115 @@
         <v>20</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="K86" s="25" t="s">
-        <v>326</v>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" s="5">
+        <v>83</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="E87" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I87" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="K87" s="13" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" s="25">
+        <v>84</v>
+      </c>
+      <c r="B88" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C88" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="D88" s="25" t="s">
+        <v>337</v>
+      </c>
+      <c r="E88" s="25" t="s">
+        <v>338</v>
+      </c>
+      <c r="F88" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I88" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J88" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="K88" s="25" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" s="5">
+        <v>85</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="I89" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="J89" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="K89" s="13" t="s">
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -5260,7 +5452,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I66"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -5275,7 +5467,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -5288,7 +5480,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -5301,7 +5493,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -5314,28 +5506,28 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>337</v>
+        <v>353</v>
       </c>
       <c r="I4" s="29" t="s">
         <v>22</v>
@@ -5346,13 +5538,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E5" s="32">
         <v>3</v>
@@ -5361,7 +5553,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H5" s="31" t="s">
         <v>22</v>
@@ -5372,22 +5564,22 @@
         <v>37</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E6" s="37">
         <v>2</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H6" s="36" t="s">
         <v>22</v>
@@ -5395,25 +5587,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E7" s="32">
         <v>2</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>346</v>
+        <v>362</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H7" s="31" t="s">
         <v>22</v>
@@ -5424,13 +5616,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E8" s="37">
         <v>3</v>
@@ -5439,7 +5631,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H8" s="36" t="s">
         <v>22</v>
@@ -5450,22 +5642,22 @@
         <v>33</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E9" s="32">
         <v>3</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H9" s="31" t="s">
         <v>22</v>
@@ -5476,13 +5668,13 @@
         <v>94</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E10" s="37">
         <v>2</v>
@@ -5491,7 +5683,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>22</v>
@@ -5502,13 +5694,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>352</v>
+        <v>368</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E11" s="32">
         <v>3</v>
@@ -5517,7 +5709,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H11" s="31" t="s">
         <v>22</v>
@@ -5528,13 +5720,13 @@
         <v>75</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>353</v>
+        <v>369</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E12" s="37">
         <v>3</v>
@@ -5543,7 +5735,7 @@
         <v>72</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H12" s="36" t="s">
         <v>22</v>
@@ -5554,13 +5746,13 @@
         <v>78</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>354</v>
+        <v>370</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E13" s="32">
         <v>2</v>
@@ -5569,7 +5761,7 @@
         <v>76</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H13" s="31" t="s">
         <v>22</v>
@@ -5580,13 +5772,13 @@
         <v>82</v>
       </c>
       <c r="B14" s="36" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>364</v>
+      </c>
+      <c r="D14" s="38" t="s">
         <v>356</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>348</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>340</v>
       </c>
       <c r="E14" s="37">
         <v>2</v>
@@ -5595,7 +5787,7 @@
         <v>79</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H14" s="36" t="s">
         <v>22</v>
@@ -5606,13 +5798,13 @@
         <v>86</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E15" s="32">
         <v>2</v>
@@ -5621,7 +5813,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H15" s="31" t="s">
         <v>22</v>
@@ -5632,22 +5824,22 @@
         <v>63</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>358</v>
+        <v>374</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E16" s="37">
         <v>3</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>359</v>
+        <v>375</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H16" s="36" t="s">
         <v>22</v>
@@ -5658,22 +5850,22 @@
         <v>52</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>360</v>
+        <v>376</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E17" s="32">
         <v>3</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>361</v>
+        <v>377</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H17" s="31" t="s">
         <v>22</v>
@@ -5684,13 +5876,13 @@
         <v>173</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="E18" s="37">
         <v>3</v>
@@ -5699,24 +5891,24 @@
         <v>174</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H18" s="36" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
-        <v>365</v>
+        <v>381</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>366</v>
+        <v>382</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>363</v>
+        <v>379</v>
       </c>
       <c r="E19" s="32">
         <v>3</v>
@@ -5725,10 +5917,10 @@
         <v>117</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>364</v>
+        <v>380</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -5736,51 +5928,51 @@
         <v>184</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>367</v>
+        <v>383</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="E20" s="37">
         <v>5</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>369</v>
+        <v>385</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
-        <v>371</v>
+        <v>387</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>368</v>
+        <v>384</v>
       </c>
       <c r="E21" s="32">
         <v>3</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -5788,22 +5980,22 @@
         <v>101</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>374</v>
+        <v>390</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E22" s="37">
         <v>5</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>375</v>
+        <v>391</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H22" s="36" t="s">
         <v>22</v>
@@ -5814,13 +6006,13 @@
         <v>111</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E23" s="32">
         <v>3</v>
@@ -5829,7 +6021,7 @@
         <v>106</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H23" s="31" t="s">
         <v>22</v>
@@ -5840,13 +6032,13 @@
         <v>105</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E24" s="37">
         <v>3</v>
@@ -5855,7 +6047,7 @@
         <v>102</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H24" s="36" t="s">
         <v>22</v>
@@ -5863,16 +6055,16 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>379</v>
+        <v>395</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E25" s="32">
         <v>3</v>
@@ -5881,7 +6073,7 @@
         <v>157</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H25" s="31" t="s">
         <v>22</v>
@@ -5889,28 +6081,28 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
-        <v>380</v>
+        <v>396</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>381</v>
+        <v>397</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E26" s="37">
         <v>2</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>382</v>
+        <v>398</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>383</v>
+        <v>399</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -5918,13 +6110,13 @@
         <v>164</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E27" s="32">
         <v>3</v>
@@ -5933,7 +6125,7 @@
         <v>161</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>22</v>
@@ -5944,13 +6136,13 @@
         <v>90</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E28" s="37">
         <v>3</v>
@@ -5959,7 +6151,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H28" s="36" t="s">
         <v>22</v>
@@ -5967,25 +6159,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E29" s="32">
         <v>3</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H29" s="31" t="s">
         <v>22</v>
@@ -5996,13 +6188,13 @@
         <v>144</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E30" s="37">
         <v>3</v>
@@ -6011,7 +6203,7 @@
         <v>141</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H30" s="36" t="s">
         <v>22</v>
@@ -6022,13 +6214,13 @@
         <v>156</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E31" s="32">
         <v>5</v>
@@ -6037,7 +6229,7 @@
         <v>153</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H31" s="31" t="s">
         <v>22</v>
@@ -6048,13 +6240,13 @@
         <v>148</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E32" s="37">
         <v>3</v>
@@ -6063,7 +6255,7 @@
         <v>145</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H32" s="36" t="s">
         <v>22</v>
@@ -6074,13 +6266,13 @@
         <v>152</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>392</v>
+        <v>408</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E33" s="32">
         <v>3</v>
@@ -6089,7 +6281,7 @@
         <v>149</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H33" s="31" t="s">
         <v>22</v>
@@ -6097,25 +6289,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="35" t="s">
-        <v>393</v>
+        <v>409</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E34" s="37">
         <v>5</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H34" s="36" t="s">
         <v>22</v>
@@ -6123,25 +6315,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E35" s="32">
         <v>5</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>398</v>
+        <v>414</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H35" s="31" t="s">
         <v>22</v>
@@ -6152,13 +6344,13 @@
         <v>261</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>399</v>
+        <v>415</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E36" s="37">
         <v>3</v>
@@ -6167,7 +6359,7 @@
         <v>258</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H36" s="36" t="s">
         <v>22</v>
@@ -6178,22 +6370,22 @@
         <v>189</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>400</v>
+        <v>416</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E37" s="32">
         <v>5</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>401</v>
+        <v>417</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H37" s="31" t="s">
         <v>22</v>
@@ -6204,13 +6396,13 @@
         <v>193</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E38" s="37">
         <v>3</v>
@@ -6219,7 +6411,7 @@
         <v>190</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H38" s="36" t="s">
         <v>22</v>
@@ -6230,13 +6422,13 @@
         <v>210</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E39" s="32">
         <v>3</v>
@@ -6245,7 +6437,7 @@
         <v>207</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H39" s="31" t="s">
         <v>22</v>
@@ -6256,22 +6448,22 @@
         <v>214</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E40" s="37">
         <v>2</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>405</v>
+        <v>421</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H40" s="36" t="s">
         <v>22</v>
@@ -6282,25 +6474,25 @@
         <v>222</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>406</v>
+        <v>422</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E41" s="32">
         <v>3</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>407</v>
+        <v>423</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>408</v>
+        <v>424</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6308,22 +6500,22 @@
         <v>237</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>409</v>
+        <v>425</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E42" s="37">
         <v>5</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H42" s="36" t="s">
         <v>22</v>
@@ -6334,13 +6526,13 @@
         <v>241</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E43" s="32">
         <v>3</v>
@@ -6349,7 +6541,7 @@
         <v>238</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="H43" s="31" t="s">
         <v>22</v>
@@ -6357,7 +6549,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -6370,25 +6562,25 @@
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>413</v>
+        <v>429</v>
       </c>
       <c r="H46" s="29" t="s">
         <v>22</v>
@@ -6405,19 +6597,19 @@
         <v>264</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E47" s="32">
         <v>2</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
@@ -6427,22 +6619,22 @@
         <v>274</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>415</v>
+        <v>431</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E48" s="32">
         <v>2</v>
       </c>
       <c r="F48" s="45" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
@@ -6455,19 +6647,19 @@
         <v>277</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E49" s="32">
         <v>8</v>
       </c>
       <c r="F49" s="45" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
@@ -6477,29 +6669,29 @@
         <v>285</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
       <c r="E50" s="32">
         <v>5</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="G50" s="31" t="s">
-        <v>421</v>
+        <v>437</v>
       </c>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
-        <v>422</v>
+        <v>438</v>
       </c>
       <c r="B52" s="46"/>
       <c r="C52" s="46"/>
@@ -6521,7 +6713,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>423</v>
+        <v>439</v>
       </c>
       <c r="E53" s="29" t="s">
         <v>22</v>
@@ -6550,7 +6742,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>424</v>
+        <v>440</v>
       </c>
       <c r="E54" s="31"/>
       <c r="F54" s="31"/>
@@ -6569,7 +6761,7 @@
         <v>44</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>425</v>
+        <v>441</v>
       </c>
       <c r="E55" s="31"/>
       <c r="F55" s="31"/>
@@ -6588,7 +6780,7 @@
         <v>139</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>426</v>
+        <v>442</v>
       </c>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
@@ -6607,7 +6799,7 @@
         <v>196</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
@@ -6626,7 +6818,7 @@
         <v>205</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>428</v>
+        <v>444</v>
       </c>
       <c r="E58" s="31"/>
       <c r="F58" s="31"/>
@@ -6636,7 +6828,7 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="49" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B60" s="49"/>
       <c r="C60" s="49"/>
@@ -6658,13 +6850,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>431</v>
+        <v>447</v>
       </c>
       <c r="G61" s="29" t="s">
         <v>22</v>
@@ -6684,16 +6876,16 @@
         <v>64</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>432</v>
+        <v>448</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>433</v>
+        <v>449</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>273</v>
+        <v>18</v>
       </c>
       <c r="F62" s="51" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="G62" s="51"/>
       <c r="H62" s="51"/>
@@ -6701,22 +6893,22 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="47" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B63" s="31" t="s">
         <v>64</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>436</v>
+        <v>452</v>
       </c>
       <c r="E63" s="50" t="s">
         <v>273</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>437</v>
+        <v>453</v>
       </c>
       <c r="G63" s="51"/>
       <c r="H63" s="51"/>
@@ -6724,22 +6916,22 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="47" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B64" s="31" t="s">
         <v>140</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>439</v>
+        <v>455</v>
       </c>
       <c r="E64" s="50" t="s">
         <v>273</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="G64" s="51"/>
       <c r="H64" s="51"/>
@@ -6747,22 +6939,22 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="47" t="s">
+        <v>299</v>
+      </c>
+      <c r="B65" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="B65" s="31" t="s">
-        <v>297</v>
-      </c>
       <c r="C65" s="31" t="s">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="E65" s="50" t="s">
         <v>273</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="G65" s="51"/>
       <c r="H65" s="51"/>
@@ -6770,26 +6962,221 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="47" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B66" s="31" t="s">
         <v>185</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>444</v>
+        <v>460</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="E66" s="50" t="s">
         <v>273</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
       <c r="I66" s="51"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="43" t="s">
+        <v>463</v>
+      </c>
+      <c r="B68" s="43"/>
+      <c r="C68" s="43"/>
+      <c r="D68" s="43"/>
+      <c r="E68" s="43"/>
+      <c r="F68" s="43"/>
+      <c r="G68" s="43"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="B69" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="C69" s="29" t="s">
+        <v>348</v>
+      </c>
+      <c r="D69" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="E69" s="29" t="s">
+        <v>350</v>
+      </c>
+      <c r="F69" s="29" t="s">
+        <v>352</v>
+      </c>
+      <c r="G69" s="29" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="30" t="s">
+        <v>464</v>
+      </c>
+      <c r="B70" s="31" t="s">
+        <v>305</v>
+      </c>
+      <c r="C70" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D70" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E70" s="32">
+        <v>5</v>
+      </c>
+      <c r="F70" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="G70" s="31" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>309</v>
+      </c>
+      <c r="C71" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D71" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E71" s="32">
+        <v>8</v>
+      </c>
+      <c r="F71" s="45" t="s">
+        <v>432</v>
+      </c>
+      <c r="G71" s="31" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="30" t="s">
+        <v>468</v>
+      </c>
+      <c r="B72" s="31" t="s">
+        <v>312</v>
+      </c>
+      <c r="C72" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D72" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E72" s="32">
+        <v>3</v>
+      </c>
+      <c r="F72" s="44" t="s">
+        <v>357</v>
+      </c>
+      <c r="G72" s="31" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="30" t="s">
+        <v>470</v>
+      </c>
+      <c r="B73" s="31" t="s">
+        <v>316</v>
+      </c>
+      <c r="C73" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D73" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E73" s="32">
+        <v>5</v>
+      </c>
+      <c r="F73" s="45" t="s">
+        <v>471</v>
+      </c>
+      <c r="G73" s="31" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="B74" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="C74" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D74" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E74" s="32">
+        <v>5</v>
+      </c>
+      <c r="F74" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="30" t="s">
+        <v>475</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>324</v>
+      </c>
+      <c r="C75" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D75" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E75" s="32">
+        <v>5</v>
+      </c>
+      <c r="F75" s="45" t="s">
+        <v>432</v>
+      </c>
+      <c r="G75" s="31" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="30" t="s">
+        <v>329</v>
+      </c>
+      <c r="B76" s="31" t="s">
+        <v>327</v>
+      </c>
+      <c r="C76" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D76" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E76" s="32">
+        <v>2</v>
+      </c>
+      <c r="F76" s="44" t="s">
+        <v>432</v>
+      </c>
+      <c r="G76" s="31" t="s">
+        <v>477</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -6831,14 +7218,14 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>447</v>
+        <v>478</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>448</v>
+        <v>479</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -6848,10 +7235,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -6859,21 +7246,21 @@
         <v>18</v>
       </c>
       <c r="B5" s="56">
-        <f>COUNTIF('Feature List'!$G$5:$G$79,"Done")</f>
+        <f>COUNTIF('Feature List'!$G$5:$G$200,"Done")</f>
       </c>
       <c r="C5" s="57">
-        <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Done")/COUNTA('Feature List'!$G$5:$G$79))</f>
+        <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Done")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
-        <v>451</v>
+        <v>319</v>
       </c>
       <c r="B6" s="56">
-        <f>COUNTIF('Feature List'!$G$5:$G$79,"In Progress")</f>
+        <f>COUNTIF('Feature List'!$G$5:$G$200,"In Progress")</f>
       </c>
       <c r="C6" s="57">
-        <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"In Progress")/COUNTA('Feature List'!$G$5:$G$79))</f>
+        <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"In Progress")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -6881,45 +7268,46 @@
         <v>273</v>
       </c>
       <c r="B7" s="56">
-        <f>COUNTIF('Feature List'!$G$5:$G$79,"Not Started")</f>
+        <f>COUNTIF('Feature List'!$G$5:$G$200,"Not Started")</f>
       </c>
       <c r="C7" s="57">
-        <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Not Started")/COUNTA('Feature List'!$G$5:$G$79))</f>
+        <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Not Started")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>452</v>
+        <v>482</v>
       </c>
       <c r="B8" s="56">
-        <f>COUNTIF('Feature List'!$G$5:$G$79,"Backlog")</f>
+        <f>COUNTIF('Feature List'!$G$5:$G$200,"Backlog")</f>
       </c>
       <c r="C8" s="57">
-        <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Backlog")/COUNTA('Feature List'!$G$5:$G$79))</f>
+        <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Backlog")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B9" s="56">
-        <f>COUNTIF('Feature List'!$G$5:$G$79,"Blocked")</f>
+        <f>COUNTIF('Feature List'!$G$5:$G$200,"Blocked")</f>
       </c>
       <c r="C9" s="57">
-        <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,COUNTIF('Feature List'!$G$5:$G$79,"Blocked")/COUNTA('Feature List'!$G$5:$G$79))</f>
+        <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Blocked")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="B10" s="59">
-        <f>COUNTA('Feature List'!$G$5:$G$79)</f>
+        <f>COUNTA('Feature List'!$G$5:$G$200)</f>
       </c>
       <c r="C10" s="60">
-        <f>IF(COUNTA('Feature List'!$G$5:$G$79)=0,0,1)</f>
-      </c>
-    </row>
+        <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,1)</f>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.25"/>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>10</v>
@@ -6932,10 +7320,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -6943,67 +7331,68 @@
         <v>20</v>
       </c>
       <c r="B14" s="56">
-        <f>COUNTIF('Feature List'!$I$5:$I$79,"Not Tested")</f>
+        <f>COUNTIF('Feature List'!$I$5:$I$200,"Not Tested")</f>
       </c>
       <c r="C14" s="57">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Not Tested")/COUNTA('Feature List'!$I$5:$I$79))</f>
+        <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Not Tested")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="55" t="s">
-        <v>451</v>
+        <v>319</v>
       </c>
       <c r="B15" s="56">
-        <f>COUNTIF('Feature List'!$I$5:$I$79,"In Progress")</f>
+        <f>COUNTIF('Feature List'!$I$5:$I$200,"In Progress")</f>
       </c>
       <c r="C15" s="57">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"In Progress")/COUNTA('Feature List'!$I$5:$I$79))</f>
+        <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"In Progress")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
-        <v>455</v>
+        <v>110</v>
       </c>
       <c r="B16" s="56">
-        <f>COUNTIF('Feature List'!$I$5:$I$79,"Passed")</f>
+        <f>COUNTIF('Feature List'!$I$5:$I$200,"Pass")</f>
       </c>
       <c r="C16" s="57">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Passed")/COUNTA('Feature List'!$I$5:$I$79))</f>
+        <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Pass")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
-        <v>456</v>
+        <v>485</v>
       </c>
       <c r="B17" s="56">
-        <f>COUNTIF('Feature List'!$I$5:$I$79,"Failed")</f>
+        <f>COUNTIF('Feature List'!$I$5:$I$200,"Failed")</f>
       </c>
       <c r="C17" s="57">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Failed")/COUNTA('Feature List'!$I$5:$I$79))</f>
+        <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Failed")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="55" t="s">
-        <v>453</v>
+        <v>483</v>
       </c>
       <c r="B18" s="56">
-        <f>COUNTIF('Feature List'!$I$5:$I$79,"Blocked")</f>
+        <f>COUNTIF('Feature List'!$I$5:$I$200,"Blocked")</f>
       </c>
       <c r="C18" s="57">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,COUNTIF('Feature List'!$I$5:$I$79,"Blocked")/COUNTA('Feature List'!$I$5:$I$79))</f>
+        <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Blocked")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
-        <v>454</v>
+        <v>484</v>
       </c>
       <c r="B19" s="59">
-        <f>COUNTA('Feature List'!$I$5:$I$79)</f>
+        <f>COUNTA('Feature List'!$I$5:$I$200)</f>
       </c>
       <c r="C19" s="60">
-        <f>IF(COUNTA('Feature List'!$I$5:$I$79)=0,0,1)</f>
-      </c>
-    </row>
+        <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,1)</f>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25"/>
     <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
         <v>7</v>
@@ -7016,10 +7405,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -7027,10 +7416,10 @@
         <v>17</v>
       </c>
       <c r="B23" s="56">
-        <f>COUNTIF('Feature List'!$F$5:$F$79,"Existing")</f>
+        <f>COUNTIF('Feature List'!$F$5:$F$200,"Existing")</f>
       </c>
       <c r="C23" s="57">
-        <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,COUNTIF('Feature List'!$F$5:$F$79,"Existing")/COUNTA('Feature List'!$F$5:$F$79))</f>
+        <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"Existing")/COUNTA('Feature List'!$F$5:$F$200))</f>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
@@ -7038,52 +7427,63 @@
         <v>267</v>
       </c>
       <c r="B24" s="56">
-        <f>COUNTIF('Feature List'!$F$5:$F$79,"DevOps Backlog")</f>
+        <f>COUNTIF('Feature List'!$F$5:$F$200,"DevOps Backlog")</f>
       </c>
       <c r="C24" s="57">
-        <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,COUNTIF('Feature List'!$F$5:$F$79,"DevOps Backlog")/COUNTA('Feature List'!$F$5:$F$79))</f>
+        <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"DevOps Backlog")/COUNTA('Feature List'!$F$5:$F$200))</f>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="55" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B25" s="56">
-        <f>COUNTIF('Feature List'!$F$5:$F$79,"New Requirement")</f>
+        <f>COUNTIF('Feature List'!$F$5:$F$200,"New Requirement")</f>
       </c>
       <c r="C25" s="57">
-        <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,COUNTIF('Feature List'!$F$5:$F$79,"New Requirement")/COUNTA('Feature List'!$F$5:$F$79))</f>
+        <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"New Requirement")/COUNTA('Feature List'!$F$5:$F$200))</f>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
-        <v>454</v>
+        <v>307</v>
       </c>
       <c r="B26" s="59">
-        <f>COUNTA('Feature List'!$F$5:$F$79)</f>
+        <f>COUNTIF('Feature List'!$F$5:$F$200,"Nice to Have")</f>
       </c>
       <c r="C26" s="60">
-        <f>IF(COUNTA('Feature List'!$F$5:$F$79)=0,0,1)</f>
+        <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"Nice to Have")/COUNTA('Feature List'!$F$5:$F$200))</f>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="58" t="s">
+        <v>484</v>
+      </c>
+      <c r="B27" s="59">
+        <f>COUNTA('Feature List'!$F$5:$F$200)</f>
+      </c>
+      <c r="C27" s="60">
+        <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,1)</f>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="61" t="s">
-        <v>457</v>
+        <v>486</v>
       </c>
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
-        <v>458</v>
+        <v>487</v>
       </c>
       <c r="B29" s="56">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="55" t="s">
-        <v>459</v>
+        <v>488</v>
       </c>
       <c r="B30" s="56">
         <v>50</v>
@@ -7091,7 +7491,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="55" t="s">
-        <v>460</v>
+        <v>489</v>
       </c>
       <c r="B31" s="56">
         <v>4</v>
@@ -7099,15 +7499,15 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="55" t="s">
-        <v>461</v>
+        <v>490</v>
       </c>
       <c r="B32" s="56">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="55" t="s">
-        <v>462</v>
+        <v>491</v>
       </c>
       <c r="B33" s="56">
         <v>0</v>
@@ -7115,7 +7515,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="55" t="s">
-        <v>463</v>
+        <v>492</v>
       </c>
       <c r="B34" s="56">
         <v>35</v>
@@ -7145,16 +7545,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>464</v>
+        <v>493</v>
       </c>
       <c r="B1" s="52"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
-        <v>465</v>
+        <v>494</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>466</v>
+        <v>495</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7162,7 +7562,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>467</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7170,7 +7570,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>468</v>
+        <v>497</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7178,7 +7578,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>469</v>
+        <v>498</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7186,7 +7586,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>470</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7194,7 +7594,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>471</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7202,15 +7602,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>472</v>
+        <v>501</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>473</v>
+        <v>502</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>474</v>
+        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="513">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -1018,21 +1018,27 @@
     <t>main.js · loadVersion() / clearAllTags(); state.js · suppressAutoScope; versionMenu.js</t>
   </si>
   <si>
+    <t>— Feature "Discovery Baseline template" (no story id in export)</t>
+  </si>
+  <si>
+    <t>App-only when identified 2026-09-09; the 2026-09-14 board export raised a matching Feature ("Discovery Baseline template"). Still has no user story beneath it.</t>
+  </si>
+  <si>
+    <t>Built-in version edit lock</t>
+  </si>
+  <si>
+    <t>Save Changes is hidden and overwrite is blocked while a built-in baseline (Original / Discovery Baseline) is active, so factory content cannot be overwritten.</t>
+  </si>
+  <si>
+    <t>state.js · BUILTIN_VERSIONS; main.js · updateSaveChangesBtn() / saveChangesToVersion()</t>
+  </si>
+  <si>
     <t>— none (story needed)</t>
   </si>
   <si>
     <t>App-only feature with no DevOps story — one should be raised. Identified 2026-09-09.</t>
   </si>
   <si>
-    <t>Built-in version edit lock</t>
-  </si>
-  <si>
-    <t>Save Changes is hidden and overwrite is blocked while a built-in baseline (Original / Discovery Baseline) is active, so factory content cannot be overwritten.</t>
-  </si>
-  <si>
-    <t>state.js · BUILTIN_VERSIONS; main.js · updateSaveChangesBtn() / saveChangesToVersion()</t>
-  </si>
-  <si>
     <t>Client name on cover from version title</t>
   </si>
   <si>
@@ -1045,10 +1051,25 @@
     <t>Added 2026-09-14 (commit d349d98). Verified by unzipping the generated .docx — the cover runs and footer1.xml both carry the version title. No DevOps story yet.</t>
   </si>
   <si>
+    <t>Original factory content baseline version</t>
+  </si>
+  <si>
+    <t>Restores every built-in module to factory content with its original scope and coverage tags and the full seeded link set — the fully-linked reference template, as distinct from the untagged Discovery Baseline.</t>
+  </si>
+  <si>
+    <t>main.js · loadVersion('original'); data/index.js · ORIGINAL_DATA; links.js · seedLinks()</t>
+  </si>
+  <si>
+    <t>— Feature "Fully linked Original Factory Content template" (no story id in export)</t>
+  </si>
+  <si>
+    <t>Added from the 2026-09-14 board export, which raised this as a Feature. Built but had no tracker row and still has no user story beneath the feature.</t>
+  </si>
+  <si>
     <t>DevOps Backlog ⇄ App Feature Comparison</t>
   </si>
   <si>
-    <t>60 board stories referenced by the Feature List · 4 on board only (section B) · 3 in app only, no story yet (see Feature List) · 0 new requirements pending. Section E lists the nice-to-have stories 3281–3287. Updated 2026-09-14.</t>
+    <t>Board export 2026-09-14: 60 user stories — 9 Closed, 6 Resolved, 3 Pending Feedback, 1 Testing, 1 Development, 40 New (20 of 60 progressed beyond New). 27 stories still read "New" although the tracker records them built. 4 app features have no story. 4 on board only (section B); section E = nice-to-haves.</t>
   </si>
   <si>
     <t>A · Matched — board story ↔ existing feature</t>
@@ -1093,6 +1114,9 @@
     <t>Open a detail panel for any card</t>
   </si>
   <si>
+    <t>Resolved</t>
+  </si>
+  <si>
     <t>Detail panel; Core activities &amp; overview</t>
   </si>
   <si>
@@ -1102,6 +1126,9 @@
     <t>Browse the Tab-Column-Card hierarchy</t>
   </si>
   <si>
+    <t>Pending Feedback</t>
+  </si>
+  <si>
     <t>Process/sub card grid; Module tab bar</t>
   </si>
   <si>
@@ -1111,6 +1138,9 @@
     <t>Should</t>
   </si>
   <si>
+    <t>Development</t>
+  </si>
+  <si>
     <t>Browse CRE value streams</t>
   </si>
   <si>
@@ -1153,7 +1183,7 @@
     <t>See linked counterparts in both directions</t>
   </si>
   <si>
-    <t>Pending Feedback</t>
+    <t>Closed</t>
   </si>
   <si>
     <t>Board = Pending Feedback; implemented in code.</t>
@@ -1168,9 +1198,6 @@
     <t>Add a link in Edit Mode</t>
   </si>
   <si>
-    <t>Resolved</t>
-  </si>
-  <si>
     <t>Inline link editor; Add-link drill-down combobox</t>
   </si>
   <si>
@@ -1480,10 +1507,10 @@
     <t>Board stories total</t>
   </si>
   <si>
-    <t>Matched to existing features</t>
-  </si>
-  <si>
-    <t>On board only (added / assess)</t>
+    <t>Matched to a tracker feature</t>
+  </si>
+  <si>
+    <t>On board only (section B)</t>
   </si>
   <si>
     <t>In app only (no story)</t>
@@ -2356,7 +2383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K89"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -5372,10 +5399,10 @@
         <v>20</v>
       </c>
       <c r="J88" s="25" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K88" s="25" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5386,13 +5413,13 @@
         <v>229</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>17</v>
@@ -5407,10 +5434,45 @@
         <v>110</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>342</v>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" s="25">
+        <v>86</v>
+      </c>
+      <c r="B90" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C90" s="25" t="s">
+        <v>345</v>
+      </c>
+      <c r="D90" s="25" t="s">
+        <v>346</v>
+      </c>
+      <c r="E90" s="25" t="s">
+        <v>347</v>
+      </c>
+      <c r="F90" s="25" t="s">
+        <v>267</v>
+      </c>
+      <c r="G90" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H90" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I90" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="J90" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="K90" s="25" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>
@@ -5467,7 +5529,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -5480,7 +5542,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -5493,7 +5555,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -5506,28 +5568,28 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="I4" s="29" t="s">
         <v>22</v>
@@ -5538,13 +5600,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E5" s="32">
         <v>3</v>
@@ -5553,7 +5615,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H5" s="31" t="s">
         <v>22</v>
@@ -5564,22 +5626,22 @@
         <v>37</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E6" s="37">
         <v>2</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H6" s="36" t="s">
         <v>22</v>
@@ -5587,25 +5649,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E7" s="32">
         <v>2</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H7" s="31" t="s">
         <v>22</v>
@@ -5616,13 +5678,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="E8" s="37">
         <v>3</v>
@@ -5631,7 +5693,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H8" s="36" t="s">
         <v>22</v>
@@ -5642,22 +5704,22 @@
         <v>33</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E9" s="32">
         <v>3</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H9" s="31" t="s">
         <v>22</v>
@@ -5668,13 +5730,13 @@
         <v>94</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E10" s="37">
         <v>2</v>
@@ -5683,7 +5745,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>22</v>
@@ -5694,13 +5756,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E11" s="32">
         <v>3</v>
@@ -5709,7 +5771,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H11" s="31" t="s">
         <v>22</v>
@@ -5720,13 +5782,13 @@
         <v>75</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E12" s="37">
         <v>3</v>
@@ -5735,7 +5797,7 @@
         <v>72</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H12" s="36" t="s">
         <v>22</v>
@@ -5746,13 +5808,13 @@
         <v>78</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E13" s="32">
         <v>2</v>
@@ -5761,7 +5823,7 @@
         <v>76</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H13" s="31" t="s">
         <v>22</v>
@@ -5772,13 +5834,13 @@
         <v>82</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>356</v>
+        <v>370</v>
       </c>
       <c r="E14" s="37">
         <v>2</v>
@@ -5787,7 +5849,7 @@
         <v>79</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H14" s="36" t="s">
         <v>22</v>
@@ -5798,13 +5860,13 @@
         <v>86</v>
       </c>
       <c r="B15" s="31" t="s">
+        <v>383</v>
+      </c>
+      <c r="C15" s="32" t="s">
         <v>373</v>
       </c>
-      <c r="C15" s="32" t="s">
-        <v>364</v>
-      </c>
       <c r="D15" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E15" s="32">
         <v>2</v>
@@ -5813,7 +5875,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H15" s="31" t="s">
         <v>22</v>
@@ -5824,22 +5886,22 @@
         <v>63</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E16" s="37">
         <v>3</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H16" s="36" t="s">
         <v>22</v>
@@ -5850,22 +5912,22 @@
         <v>52</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E17" s="32">
         <v>3</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H17" s="31" t="s">
         <v>22</v>
@@ -5876,13 +5938,13 @@
         <v>173</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="E18" s="37">
         <v>3</v>
@@ -5891,24 +5953,24 @@
         <v>174</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H18" s="36" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="E19" s="32">
         <v>3</v>
@@ -5917,10 +5979,10 @@
         <v>117</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -5928,51 +5990,51 @@
         <v>184</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E20" s="37">
         <v>5</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="E21" s="32">
         <v>3</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -5980,22 +6042,22 @@
         <v>101</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E22" s="37">
         <v>5</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H22" s="36" t="s">
         <v>22</v>
@@ -6006,13 +6068,13 @@
         <v>111</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="E23" s="32">
         <v>3</v>
@@ -6021,7 +6083,7 @@
         <v>106</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H23" s="31" t="s">
         <v>22</v>
@@ -6032,13 +6094,13 @@
         <v>105</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E24" s="37">
         <v>3</v>
@@ -6047,7 +6109,7 @@
         <v>102</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H24" s="36" t="s">
         <v>22</v>
@@ -6055,16 +6117,16 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E25" s="32">
         <v>3</v>
@@ -6073,7 +6135,7 @@
         <v>157</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H25" s="31" t="s">
         <v>22</v>
@@ -6081,28 +6143,28 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E26" s="37">
         <v>2</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -6110,13 +6172,13 @@
         <v>164</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E27" s="32">
         <v>3</v>
@@ -6125,7 +6187,7 @@
         <v>161</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>22</v>
@@ -6136,13 +6198,13 @@
         <v>90</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E28" s="37">
         <v>3</v>
@@ -6151,7 +6213,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H28" s="36" t="s">
         <v>22</v>
@@ -6159,25 +6221,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E29" s="32">
         <v>3</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H29" s="31" t="s">
         <v>22</v>
@@ -6188,13 +6250,13 @@
         <v>144</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E30" s="37">
         <v>3</v>
@@ -6203,7 +6265,7 @@
         <v>141</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H30" s="36" t="s">
         <v>22</v>
@@ -6214,13 +6276,13 @@
         <v>156</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E31" s="32">
         <v>5</v>
@@ -6229,7 +6291,7 @@
         <v>153</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H31" s="31" t="s">
         <v>22</v>
@@ -6240,13 +6302,13 @@
         <v>148</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E32" s="37">
         <v>3</v>
@@ -6255,7 +6317,7 @@
         <v>145</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H32" s="36" t="s">
         <v>22</v>
@@ -6266,13 +6328,13 @@
         <v>152</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E33" s="32">
         <v>3</v>
@@ -6281,7 +6343,7 @@
         <v>149</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H33" s="31" t="s">
         <v>22</v>
@@ -6289,25 +6351,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="35" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E34" s="37">
         <v>5</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H34" s="36" t="s">
         <v>22</v>
@@ -6315,25 +6377,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E35" s="32">
         <v>5</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H35" s="31" t="s">
         <v>22</v>
@@ -6344,13 +6406,13 @@
         <v>261</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E36" s="37">
         <v>3</v>
@@ -6359,7 +6421,7 @@
         <v>258</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H36" s="36" t="s">
         <v>22</v>
@@ -6370,22 +6432,22 @@
         <v>189</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E37" s="32">
         <v>5</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H37" s="31" t="s">
         <v>22</v>
@@ -6396,13 +6458,13 @@
         <v>193</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="E38" s="37">
         <v>3</v>
@@ -6411,7 +6473,7 @@
         <v>190</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H38" s="36" t="s">
         <v>22</v>
@@ -6422,13 +6484,13 @@
         <v>210</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E39" s="32">
         <v>3</v>
@@ -6437,7 +6499,7 @@
         <v>207</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H39" s="31" t="s">
         <v>22</v>
@@ -6448,22 +6510,22 @@
         <v>214</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="E40" s="37">
         <v>2</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H40" s="36" t="s">
         <v>22</v>
@@ -6474,25 +6536,25 @@
         <v>222</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E41" s="32">
         <v>3</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6500,22 +6562,22 @@
         <v>237</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E42" s="37">
         <v>5</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H42" s="36" t="s">
         <v>22</v>
@@ -6526,13 +6588,13 @@
         <v>241</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E43" s="32">
         <v>3</v>
@@ -6541,7 +6603,7 @@
         <v>238</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="H43" s="31" t="s">
         <v>22</v>
@@ -6549,7 +6611,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -6562,25 +6624,25 @@
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="H46" s="29" t="s">
         <v>22</v>
@@ -6597,19 +6659,19 @@
         <v>264</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="E47" s="32">
         <v>2</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
@@ -6619,22 +6681,22 @@
         <v>274</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E48" s="32">
         <v>2</v>
       </c>
       <c r="F48" s="45" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
@@ -6647,19 +6709,19 @@
         <v>277</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E49" s="32">
         <v>8</v>
       </c>
       <c r="F49" s="45" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
@@ -6669,29 +6731,29 @@
         <v>285</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E50" s="32">
         <v>5</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G50" s="31" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B52" s="46"/>
       <c r="C52" s="46"/>
@@ -6713,7 +6775,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="E53" s="29" t="s">
         <v>22</v>
@@ -6742,7 +6804,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="E54" s="31"/>
       <c r="F54" s="31"/>
@@ -6761,7 +6823,7 @@
         <v>44</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="E55" s="31"/>
       <c r="F55" s="31"/>
@@ -6780,7 +6842,7 @@
         <v>139</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
@@ -6799,7 +6861,7 @@
         <v>196</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
@@ -6818,7 +6880,7 @@
         <v>205</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="E58" s="31"/>
       <c r="F58" s="31"/>
@@ -6828,7 +6890,7 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="49" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="B60" s="49"/>
       <c r="C60" s="49"/>
@@ -6850,13 +6912,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="G61" s="29" t="s">
         <v>22</v>
@@ -6876,16 +6938,16 @@
         <v>64</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>18</v>
+        <v>389</v>
       </c>
       <c r="F62" s="51" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="G62" s="51"/>
       <c r="H62" s="51"/>
@@ -6899,16 +6961,16 @@
         <v>64</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="G63" s="51"/>
       <c r="H63" s="51"/>
@@ -6922,16 +6984,16 @@
         <v>140</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="G64" s="51"/>
       <c r="H64" s="51"/>
@@ -6945,16 +7007,16 @@
         <v>298</v>
       </c>
       <c r="C65" s="31" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="G65" s="51"/>
       <c r="H65" s="51"/>
@@ -6968,16 +7030,16 @@
         <v>185</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>273</v>
+        <v>363</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
@@ -6985,7 +7047,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
@@ -6996,163 +7058,163 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B69" s="29" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="G69" s="29" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="30" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>305</v>
       </c>
       <c r="C70" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E70" s="32">
         <v>5</v>
       </c>
       <c r="F70" s="44" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="B71" s="31" t="s">
         <v>309</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E71" s="32">
         <v>8</v>
       </c>
       <c r="F71" s="45" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G71" s="31" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="B72" s="31" t="s">
         <v>312</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>356</v>
+        <v>389</v>
       </c>
       <c r="E72" s="32">
         <v>3</v>
       </c>
       <c r="F72" s="44" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="G72" s="31" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="30" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>316</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E73" s="32">
         <v>5</v>
       </c>
       <c r="F73" s="45" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="30" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="B74" s="31" t="s">
         <v>321</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E74" s="32">
         <v>5</v>
       </c>
       <c r="F74" s="44" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G74" s="31" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="30" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>324</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E75" s="32">
         <v>5</v>
       </c>
       <c r="F75" s="45" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -7163,19 +7225,19 @@
         <v>327</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="E76" s="32">
         <v>2</v>
       </c>
       <c r="F76" s="44" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -7218,14 +7280,14 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -7235,10 +7297,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -7276,7 +7338,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B8" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Backlog")</f>
@@ -7287,7 +7349,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B9" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Blocked")</f>
@@ -7298,7 +7360,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B10" s="59">
         <f>COUNTA('Feature List'!$G$5:$G$200)</f>
@@ -7307,7 +7369,6 @@
         <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,1)</f>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.25"/>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>10</v>
@@ -7320,10 +7381,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -7361,7 +7422,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="B17" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Failed")</f>
@@ -7372,7 +7433,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="55" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="B18" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Blocked")</f>
@@ -7383,7 +7444,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B19" s="59">
         <f>COUNTA('Feature List'!$I$5:$I$200)</f>
@@ -7392,7 +7453,6 @@
         <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,1)</f>
       </c>
     </row>
-    <row r="20" spans="2:3" x14ac:dyDescent="0.25"/>
     <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
         <v>7</v>
@@ -7405,10 +7465,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -7457,7 +7517,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="B27" s="59">
         <f>COUNTA('Feature List'!$F$5:$F$200)</f>
@@ -7468,14 +7528,14 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="61" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B29" s="56">
         <v>60</v>
@@ -7483,15 +7543,15 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="55" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="B30" s="56">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="55" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="B31" s="56">
         <v>4</v>
@@ -7499,15 +7559,15 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="55" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="B32" s="56">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="55" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="B33" s="56">
         <v>0</v>
@@ -7515,10 +7575,10 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="55" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="B34" s="56">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -7545,16 +7605,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="B1" s="52"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7562,7 +7622,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7570,7 +7630,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7578,7 +7638,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7586,7 +7646,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7594,7 +7654,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7602,15 +7662,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1350" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="516">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -949,7 +949,10 @@
     <t>Checklist or wizard walking a consultant through module selection, scope tagging, coverage mapping, and export.</t>
   </si>
   <si>
-    <t>Future enhancement. Story 3282 under Feature 3195 (View Switcher &amp; Shared Shell).</t>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>Story 3282 under Feature 3195 (View Switcher &amp; Shared Shell). Board state Active (13 pts) as at 2026-09-15 — work started; nothing in the codebase yet.</t>
   </si>
   <si>
     <t>Duplicate a version</t>
@@ -973,9 +976,6 @@
     <t>docxExport.js · buildBrandedDocument() (cover + TOC) — executive summary not built</t>
   </si>
   <si>
-    <t>In Progress</t>
-  </si>
-  <si>
     <t>Partially delivered: cover page and auto table of contents built by the Open Box house-style export (70a941a, fa6d8fb); cover client name added 2026-09-14 (d349d98). Executive summary is the only outstanding element. Story 3284 under Feature 3213 (Word &amp; PDF Export).</t>
   </si>
   <si>
@@ -1069,7 +1069,7 @@
     <t>DevOps Backlog ⇄ App Feature Comparison</t>
   </si>
   <si>
-    <t>Board export 2026-09-14: 60 user stories — 9 Closed, 6 Resolved, 3 Pending Feedback, 1 Testing, 1 Development, 40 New (20 of 60 progressed beyond New). 27 stories still read "New" although the tracker records them built. 4 app features have no story. 4 on board only (section B); section E = nice-to-haves.</t>
+    <t>Board export 2026-09-15: 60 user stories, 224 story points — 8 Pending Feedback, 22 Resolved, 1 Active, 1 Development, 9 Closed, 1 Testing, 4 Analysis, 14 New. 46 of 60 progressed beyond New; 99 of 224 pts Resolved/Closed. 2 stories still read "New" although the tracker records them built. 4 app features have no story (Feature List #83-#86).</t>
   </si>
   <si>
     <t>A · Matched — board story ↔ existing feature</t>
@@ -1105,138 +1105,141 @@
     <t>Must</t>
   </si>
   <si>
+    <t>Pending Feedback</t>
+  </si>
+  <si>
+    <t>Done (in code)</t>
+  </si>
+  <si>
+    <t>Open a detail panel for any card</t>
+  </si>
+  <si>
+    <t>Resolved</t>
+  </si>
+  <si>
+    <t>Detail panel; Core activities &amp; overview</t>
+  </si>
+  <si>
+    <t>3218</t>
+  </si>
+  <si>
+    <t>Browse the Tab-Column-Card hierarchy</t>
+  </si>
+  <si>
+    <t>Process/sub card grid; Module tab bar</t>
+  </si>
+  <si>
+    <t>Expand and collapse sub-processes</t>
+  </si>
+  <si>
+    <t>Should</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>Browse CRE value streams</t>
+  </si>
+  <si>
+    <t>CRE value-stream taxonomy; Value-stream tab bar</t>
+  </si>
+  <si>
+    <t>See which cards still need enrichment</t>
+  </si>
+  <si>
+    <t>Analysis</t>
+  </si>
+  <si>
+    <t>View market variation for a process</t>
+  </si>
+  <si>
+    <t>View vertical/sector detail for a process</t>
+  </si>
+  <si>
+    <t>See standards and frameworks on a process</t>
+  </si>
+  <si>
+    <t>Could</t>
+  </si>
+  <si>
+    <t>Filter value streams by market</t>
+  </si>
+  <si>
+    <t>Filter value streams by vertical</t>
+  </si>
+  <si>
+    <t>Browse the MRI PMX system taxonomy</t>
+  </si>
+  <si>
+    <t>Process/sub card grid; 9 built-in MRI modules</t>
+  </si>
+  <si>
+    <t>See MRI setup detail for a system process</t>
+  </si>
+  <si>
+    <t>MRI module reference; Setup prerequisites; Associated screens</t>
+  </si>
+  <si>
+    <t>See linked counterparts in both directions</t>
+  </si>
+  <si>
+    <t>Closed</t>
+  </si>
+  <si>
+    <t>Board = Pending Feedback; implemented in code.</t>
+  </si>
+  <si>
+    <t>3232</t>
+  </si>
+  <si>
+    <t>Navigate to a linked counterpart</t>
+  </si>
+  <si>
+    <t>Add a link in Edit Mode</t>
+  </si>
+  <si>
+    <t>Inline link editor; Add-link drill-down combobox</t>
+  </si>
+  <si>
+    <t>Board = Resolved.</t>
+  </si>
+  <si>
+    <t>3234</t>
+  </si>
+  <si>
+    <t>Remove a link in Edit Mode</t>
+  </si>
+  <si>
+    <t>Inline link editor (remove)</t>
+  </si>
+  <si>
+    <t>View the coverage mapping matrix</t>
+  </si>
+  <si>
+    <t>Coverage matrix; Coverage colour coding</t>
+  </si>
+  <si>
+    <t>Drill into a matrix cell</t>
+  </si>
+  <si>
+    <t>Identify coverage gaps</t>
+  </si>
+  <si>
+    <t>3238</t>
+  </si>
+  <si>
+    <t>Tag a value-stream process with system coverage</t>
+  </si>
+  <si>
+    <t>3239</t>
+  </si>
+  <si>
+    <t>See context for a coverage tag on hover</t>
+  </si>
+  <si>
     <t>New</t>
   </si>
   <si>
-    <t>Done (in code)</t>
-  </si>
-  <si>
-    <t>Open a detail panel for any card</t>
-  </si>
-  <si>
-    <t>Resolved</t>
-  </si>
-  <si>
-    <t>Detail panel; Core activities &amp; overview</t>
-  </si>
-  <si>
-    <t>3218</t>
-  </si>
-  <si>
-    <t>Browse the Tab-Column-Card hierarchy</t>
-  </si>
-  <si>
-    <t>Pending Feedback</t>
-  </si>
-  <si>
-    <t>Process/sub card grid; Module tab bar</t>
-  </si>
-  <si>
-    <t>Expand and collapse sub-processes</t>
-  </si>
-  <si>
-    <t>Should</t>
-  </si>
-  <si>
-    <t>Development</t>
-  </si>
-  <si>
-    <t>Browse CRE value streams</t>
-  </si>
-  <si>
-    <t>CRE value-stream taxonomy; Value-stream tab bar</t>
-  </si>
-  <si>
-    <t>See which cards still need enrichment</t>
-  </si>
-  <si>
-    <t>View market variation for a process</t>
-  </si>
-  <si>
-    <t>View vertical/sector detail for a process</t>
-  </si>
-  <si>
-    <t>See standards and frameworks on a process</t>
-  </si>
-  <si>
-    <t>Could</t>
-  </si>
-  <si>
-    <t>Filter value streams by market</t>
-  </si>
-  <si>
-    <t>Filter value streams by vertical</t>
-  </si>
-  <si>
-    <t>Browse the MRI PMX system taxonomy</t>
-  </si>
-  <si>
-    <t>Process/sub card grid; 9 built-in MRI modules</t>
-  </si>
-  <si>
-    <t>See MRI setup detail for a system process</t>
-  </si>
-  <si>
-    <t>MRI module reference; Setup prerequisites; Associated screens</t>
-  </si>
-  <si>
-    <t>See linked counterparts in both directions</t>
-  </si>
-  <si>
-    <t>Closed</t>
-  </si>
-  <si>
-    <t>Board = Pending Feedback; implemented in code.</t>
-  </si>
-  <si>
-    <t>3232</t>
-  </si>
-  <si>
-    <t>Navigate to a linked counterpart</t>
-  </si>
-  <si>
-    <t>Add a link in Edit Mode</t>
-  </si>
-  <si>
-    <t>Inline link editor; Add-link drill-down combobox</t>
-  </si>
-  <si>
-    <t>Board = Resolved.</t>
-  </si>
-  <si>
-    <t>3234</t>
-  </si>
-  <si>
-    <t>Remove a link in Edit Mode</t>
-  </si>
-  <si>
-    <t>Inline link editor (remove)</t>
-  </si>
-  <si>
-    <t>View the coverage mapping matrix</t>
-  </si>
-  <si>
-    <t>Coverage matrix; Coverage colour coding</t>
-  </si>
-  <si>
-    <t>Drill into a matrix cell</t>
-  </si>
-  <si>
-    <t>Identify coverage gaps</t>
-  </si>
-  <si>
-    <t>3238</t>
-  </si>
-  <si>
-    <t>Tag a value-stream process with system coverage</t>
-  </si>
-  <si>
-    <t>3239</t>
-  </si>
-  <si>
-    <t>See context for a coverage tag on hover</t>
-  </si>
-  <si>
     <t>Coverage colour coding (coverageTooltip)</t>
   </si>
   <si>
@@ -1444,6 +1447,9 @@
     <t>3282</t>
   </si>
   <si>
+    <t>Active</t>
+  </si>
+  <si>
     <t>Future enhancement. Feature List #77.</t>
   </si>
   <si>
@@ -1472,6 +1478,9 @@
   </si>
   <si>
     <t>Future enhancement. Feature List #81.</t>
+  </si>
+  <si>
+    <t>—</t>
   </si>
   <si>
     <t>Future enhancement. Feature List #82.</t>
@@ -5145,7 +5154,7 @@
         <v>307</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>273</v>
+        <v>311</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>280</v>
@@ -5157,7 +5166,7 @@
         <v>3282</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5168,13 +5177,13 @@
         <v>185</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>307</v>
@@ -5192,7 +5201,7 @@
         <v>3283</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5203,19 +5212,19 @@
         <v>229</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>307</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>19</v>
@@ -5658,13 +5667,13 @@
         <v>362</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E7" s="32">
         <v>2</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G7" s="34" t="s">
         <v>364</v>
@@ -5678,13 +5687,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="36" t="s">
+        <v>371</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>372</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="D8" s="38" t="s">
         <v>373</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>374</v>
       </c>
       <c r="E8" s="37">
         <v>3</v>
@@ -5704,19 +5713,19 @@
         <v>33</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C9" s="32" t="s">
         <v>362</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E9" s="32">
         <v>3</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G9" s="34" t="s">
         <v>364</v>
@@ -5730,13 +5739,13 @@
         <v>94</v>
       </c>
       <c r="B10" s="36" t="s">
+        <v>376</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="D10" s="38" t="s">
         <v>377</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>373</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>363</v>
       </c>
       <c r="E10" s="37">
         <v>2</v>
@@ -5759,10 +5768,10 @@
         <v>378</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="E11" s="32">
         <v>3</v>
@@ -5785,7 +5794,7 @@
         <v>379</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D12" s="38" t="s">
         <v>363</v>
@@ -5837,10 +5846,10 @@
         <v>382</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E14" s="37">
         <v>2</v>
@@ -5863,7 +5872,7 @@
         <v>383</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D15" s="33" t="s">
         <v>363</v>
@@ -5892,7 +5901,7 @@
         <v>362</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E16" s="37">
         <v>3</v>
@@ -5918,7 +5927,7 @@
         <v>362</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E17" s="32">
         <v>3</v>
@@ -6045,10 +6054,10 @@
         <v>399</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E22" s="37">
         <v>5</v>
@@ -6071,7 +6080,7 @@
         <v>401</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D23" s="33" t="s">
         <v>389</v>
@@ -6097,10 +6106,10 @@
         <v>402</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E24" s="37">
         <v>3</v>
@@ -6126,7 +6135,7 @@
         <v>362</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E25" s="32">
         <v>3</v>
@@ -6149,22 +6158,22 @@
         <v>406</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E26" s="37">
         <v>2</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G26" s="34" t="s">
         <v>364</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -6172,13 +6181,13 @@
         <v>164</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C27" s="32" t="s">
         <v>362</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E27" s="32">
         <v>3</v>
@@ -6198,13 +6207,13 @@
         <v>90</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E28" s="37">
         <v>3</v>
@@ -6221,22 +6230,22 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C29" s="32" t="s">
         <v>381</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E29" s="32">
         <v>3</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G29" s="34" t="s">
         <v>364</v>
@@ -6250,10 +6259,10 @@
         <v>144</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D30" s="38" t="s">
         <v>363</v>
@@ -6276,13 +6285,13 @@
         <v>156</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E31" s="32">
         <v>5</v>
@@ -6302,13 +6311,13 @@
         <v>148</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C32" s="37" t="s">
         <v>381</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E32" s="37">
         <v>3</v>
@@ -6328,13 +6337,13 @@
         <v>152</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E33" s="32">
         <v>3</v>
@@ -6351,22 +6360,22 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="35" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C34" s="37" t="s">
         <v>362</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E34" s="37">
         <v>5</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G34" s="34" t="s">
         <v>364</v>
@@ -6377,22 +6386,22 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C35" s="32" t="s">
         <v>362</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="E35" s="32">
         <v>5</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G35" s="34" t="s">
         <v>364</v>
@@ -6406,13 +6415,13 @@
         <v>261</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E36" s="37">
         <v>3</v>
@@ -6432,7 +6441,7 @@
         <v>189</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C37" s="32" t="s">
         <v>362</v>
@@ -6444,7 +6453,7 @@
         <v>5</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G37" s="34" t="s">
         <v>364</v>
@@ -6458,7 +6467,7 @@
         <v>193</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C38" s="37" t="s">
         <v>362</v>
@@ -6484,10 +6493,10 @@
         <v>210</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D39" s="33" t="s">
         <v>366</v>
@@ -6510,7 +6519,7 @@
         <v>214</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C40" s="37" t="s">
         <v>381</v>
@@ -6522,7 +6531,7 @@
         <v>2</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G40" s="34" t="s">
         <v>364</v>
@@ -6536,25 +6545,25 @@
         <v>222</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C41" s="32" t="s">
         <v>381</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E41" s="32">
         <v>3</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G41" s="34" t="s">
         <v>364</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6562,19 +6571,19 @@
         <v>237</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E42" s="37">
         <v>5</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G42" s="34" t="s">
         <v>364</v>
@@ -6588,13 +6597,13 @@
         <v>241</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E43" s="32">
         <v>3</v>
@@ -6611,7 +6620,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -6642,7 +6651,7 @@
         <v>359</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H46" s="29" t="s">
         <v>22</v>
@@ -6671,7 +6680,7 @@
         <v>364</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
@@ -6681,22 +6690,22 @@
         <v>274</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C48" s="32" t="s">
         <v>381</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E48" s="32">
         <v>2</v>
       </c>
       <c r="F48" s="45" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
@@ -6709,19 +6718,19 @@
         <v>277</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E49" s="32">
         <v>8</v>
       </c>
       <c r="F49" s="45" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
@@ -6731,29 +6740,29 @@
         <v>285</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C50" s="32" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D50" s="31" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E50" s="32">
         <v>5</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G50" s="31" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B52" s="46"/>
       <c r="C52" s="46"/>
@@ -6775,7 +6784,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="E53" s="29" t="s">
         <v>22</v>
@@ -6804,7 +6813,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="E54" s="31"/>
       <c r="F54" s="31"/>
@@ -6823,7 +6832,7 @@
         <v>44</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E55" s="31"/>
       <c r="F55" s="31"/>
@@ -6842,7 +6851,7 @@
         <v>139</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
@@ -6861,7 +6870,7 @@
         <v>196</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
@@ -6880,7 +6889,7 @@
         <v>205</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E58" s="31"/>
       <c r="F58" s="31"/>
@@ -6890,7 +6899,7 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="49" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B60" s="49"/>
       <c r="C60" s="49"/>
@@ -6912,13 +6921,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G61" s="29" t="s">
         <v>22</v>
@@ -6938,16 +6947,16 @@
         <v>64</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="E62" s="50" t="s">
         <v>389</v>
       </c>
       <c r="F62" s="51" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G62" s="51"/>
       <c r="H62" s="51"/>
@@ -6961,16 +6970,16 @@
         <v>64</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G63" s="51"/>
       <c r="H63" s="51"/>
@@ -6984,16 +6993,16 @@
         <v>140</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G64" s="51"/>
       <c r="H64" s="51"/>
@@ -7007,16 +7016,16 @@
         <v>298</v>
       </c>
       <c r="C65" s="31" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G65" s="51"/>
       <c r="H65" s="51"/>
@@ -7030,16 +7039,16 @@
         <v>185</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
@@ -7047,7 +7056,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
@@ -7076,12 +7085,12 @@
         <v>359</v>
       </c>
       <c r="G69" s="29" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="30" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>305</v>
@@ -7090,21 +7099,21 @@
         <v>381</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E70" s="32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F70" s="44" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B71" s="31" t="s">
         <v>309</v>
@@ -7113,24 +7122,24 @@
         <v>381</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>363</v>
+        <v>477</v>
       </c>
       <c r="E71" s="32">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F71" s="45" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G71" s="31" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C72" s="32" t="s">
         <v>381</v>
@@ -7145,35 +7154,35 @@
         <v>364</v>
       </c>
       <c r="G72" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="30" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C73" s="32" t="s">
         <v>381</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E73" s="32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F73" s="45" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="30" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B74" s="31" t="s">
         <v>321</v>
@@ -7182,21 +7191,21 @@
         <v>381</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E74" s="32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F74" s="44" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G74" s="31" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="30" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B75" s="31" t="s">
         <v>324</v>
@@ -7205,16 +7214,16 @@
         <v>381</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>363</v>
+        <v>407</v>
       </c>
       <c r="E75" s="32">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F75" s="45" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -7228,16 +7237,16 @@
         <v>381</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="E76" s="32">
-        <v>2</v>
+        <v>407</v>
+      </c>
+      <c r="E76" s="32" t="s">
+        <v>488</v>
       </c>
       <c r="F76" s="44" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
   </sheetData>
@@ -7280,14 +7289,14 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -7297,10 +7306,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -7316,7 +7325,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B6" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"In Progress")</f>
@@ -7338,7 +7347,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B8" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Backlog")</f>
@@ -7349,7 +7358,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B9" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Blocked")</f>
@@ -7360,7 +7369,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B10" s="59">
         <f>COUNTA('Feature List'!$G$5:$G$200)</f>
@@ -7381,10 +7390,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -7400,7 +7409,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="55" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="B15" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"In Progress")</f>
@@ -7422,7 +7431,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B17" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Failed")</f>
@@ -7433,7 +7442,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="55" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B18" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Blocked")</f>
@@ -7444,7 +7453,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B19" s="59">
         <f>COUNTA('Feature List'!$I$5:$I$200)</f>
@@ -7465,10 +7474,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -7517,7 +7526,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B27" s="59">
         <f>COUNTA('Feature List'!$F$5:$F$200)</f>
@@ -7528,14 +7537,14 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="61" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="B29" s="56">
         <v>60</v>
@@ -7543,7 +7552,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="55" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="B30" s="56">
         <v>60</v>
@@ -7551,7 +7560,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="55" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B31" s="56">
         <v>4</v>
@@ -7559,7 +7568,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="55" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B32" s="56">
         <v>4</v>
@@ -7567,7 +7576,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="55" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B33" s="56">
         <v>0</v>
@@ -7575,10 +7584,10 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="55" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B34" s="56">
-        <v>27</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -7605,16 +7614,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B1" s="52"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7622,7 +7631,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7630,7 +7639,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7638,7 +7647,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7646,7 +7655,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7654,7 +7663,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7662,15 +7671,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>

--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="517">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -898,7 +898,7 @@
     <t>Confirm that value-stream names and structures are meaningful for both US and UK markets — e.g. "Recoveries" (UK) vs "Service Charges" (US) — and reconcile terminology where they diverge.</t>
   </si>
   <si>
-    <t>Story 3271 under Feature 3197 (CRE Powered Value Streams Taxonomy). Added to DevOps.</t>
+    <t>Story 3271 under Feature 3197 (CRE Powered Value Streams Taxonomy). Board New as at 2026-09-15.</t>
   </si>
   <si>
     <t>Tagging methodology review and taxonomy alignment</t>
@@ -907,7 +907,7 @@
     <t>Review current scope and coverage tagging to confirm the most appropriate approach, including whether tags should align with the existing taxonomy structure or follow a separate scheme.</t>
   </si>
   <si>
-    <t>Story 3272 under Feature 3205 (Item-Level System Coverage Tag). Added to DevOps.</t>
+    <t>Story 3272 under Feature 3205 (Item-Level System Coverage Tag). Board New as at 2026-09-15.</t>
   </si>
   <si>
     <t>Security &amp; Access Control</t>
@@ -919,7 +919,7 @@
     <t>Define who can change or edit the master copy, whether access should grant editing rights, and the responsibility boundaries between roles (e.g. consultant vs client vs admin).</t>
   </si>
   <si>
-    <t>Story 3273 under Feature 3269 (Security &amp; Access Control). Added to DevOps.</t>
+    <t>Story 3273 under Feature 3269 (Security &amp; Access Control). Board New as at 2026-09-15.</t>
   </si>
   <si>
     <t>Database persistence (replace localStorage)</t>
@@ -928,7 +928,7 @@
     <t>Move version and taxonomy data from browser localStorage to a database backend so that data persists across browsers, machines, and users.</t>
   </si>
   <si>
-    <t>Story 3274 under Feature 3211 (Client Versions). Added to DevOps.</t>
+    <t>Story 3274 under Feature 3211 (Client Versions). Board New as at 2026-09-15.</t>
   </si>
   <si>
     <t>Version comparison (side-by-side diff)</t>
@@ -949,6 +949,9 @@
     <t>Checklist or wizard walking a consultant through module selection, scope tagging, coverage mapping, and export.</t>
   </si>
   <si>
+    <t>— not in the codebase yet (board: Active, 13 pts)</t>
+  </si>
+  <si>
     <t>In Progress</t>
   </si>
   <si>
@@ -1186,7 +1189,7 @@
     <t>Closed</t>
   </si>
   <si>
-    <t>Board = Pending Feedback; implemented in code.</t>
+    <t>Board Closed as at 2026-09-15; implemented in code.</t>
   </si>
   <si>
     <t>3232</t>
@@ -1201,9 +1204,6 @@
     <t>Inline link editor; Add-link drill-down combobox</t>
   </si>
   <si>
-    <t>Board = Resolved.</t>
-  </si>
-  <si>
     <t>3234</t>
   </si>
   <si>
@@ -1243,7 +1243,7 @@
     <t>Coverage colour coding (coverageTooltip)</t>
   </si>
   <si>
-    <t>Tooltip exists in code; was not a separately listed feature.</t>
+    <t>Tooltip exists in code (coverageTooltip); feature #26 Done. Board still New as at 2026-09-15 — needs moving.</t>
   </si>
   <si>
     <t>Be warned when a covered process is unlinked</t>
@@ -1267,6 +1267,9 @@
     <t>Auto-derive out-of-scope for unlinked processes</t>
   </si>
   <si>
+    <t>Feature #37 Done (grid.js · effectiveScope). Board still New as at 2026-09-15 — needs moving.</t>
+  </si>
+  <si>
     <t>Bulk-tag a system column's scope</t>
   </si>
   <si>
@@ -1318,7 +1321,10 @@
     <t>Per-module visibility; Visibility saved per version</t>
   </si>
   <si>
-    <t>PARTIAL: module visibility built; per-stream (value-stream) visibility not separately implemented.</t>
+    <t>Partially built</t>
+  </si>
+  <si>
+    <t>PARTIAL: module visibility built (#54-#56); per-stream (value-stream) visibility never implemented. Board Resolved as at 2026-09-15 — query whether the story was closed on partial delivery.</t>
   </si>
   <si>
     <t>Export to Word</t>
@@ -1336,7 +1342,7 @@
     <t>Action / note</t>
   </si>
   <si>
-    <t>Implemented via CSS overflow; added to Feature List. Board still shows New.</t>
+    <t>Implemented via CSS overflow; added to Feature List. Board Closed as at 2026-09-15 — reconciled.</t>
   </si>
   <si>
     <t>See placeholder modules flagged</t>
@@ -1366,19 +1372,19 @@
     <t>Note</t>
   </si>
   <si>
-    <t>Story 3278 created.</t>
-  </si>
-  <si>
-    <t>Story 3279 created.</t>
-  </si>
-  <si>
-    <t>Story 3276 created.</t>
-  </si>
-  <si>
-    <t>Story 3277 created.</t>
-  </si>
-  <si>
-    <t>Story 3280 created.</t>
+    <t>Story 3278 created. Board Pending Feedback as at 2026-09-15.</t>
+  </si>
+  <si>
+    <t>Story 3279 created. Board Testing as at 2026-09-15.</t>
+  </si>
+  <si>
+    <t>Story 3276 created. Board Analysis as at 2026-09-15.</t>
+  </si>
+  <si>
+    <t>Story 3277 created. Board Resolved as at 2026-09-15.</t>
+  </si>
+  <si>
+    <t>Story 3280 created. Board Resolved as at 2026-09-15.</t>
   </si>
   <si>
     <t>D · New requirements — added to DevOps board</t>
@@ -1462,9 +1468,6 @@
     <t>3284</t>
   </si>
   <si>
-    <t>Partially built</t>
-  </si>
-  <si>
     <t>Cover page + TOC built; executive summary outstanding. Feature List #79.</t>
   </si>
   <si>
@@ -1525,7 +1528,7 @@
     <t>In app only (no story)</t>
   </si>
   <si>
-    <t>New requirements (to add to board)</t>
+    <t>New requirements still to raise</t>
   </si>
   <si>
     <t>Board "New" but built in code</t>
@@ -1543,7 +1546,7 @@
     <t>Existing = already in the app (source-derived baseline).  DevOps Backlog = folded in from the board.  New Requirement = raised during review.  Nice to Have = future enhancement.</t>
   </si>
   <si>
-    <t>Done = built in the codebase.  In Progress = under active development.  Not Started / Backlog = planned only.  Blocked = cannot proceed.</t>
+    <t>Done = built in the codebase.  In Progress = under active development (board Active/Development, or partially built).  Not Started / Backlog = planned only.  Blocked = cannot proceed.</t>
   </si>
   <si>
     <t>Yes = QA complete.  No = not yet tested.  Partial = some testing done.  N/A = no QA needed.</t>
@@ -1561,7 +1564,7 @@
     <t>Comparison sheet</t>
   </si>
   <si>
-    <t>A = matched (board ↔ feature); B = on board only; C = in app only. "Actual (in code)" = what the source actually does, vs the board state.</t>
+    <t>A = matched (board story ↔ feature); B = on board only; C = previously app-only, now has a story; D = new requirements added to the board; E = nice-to-have stories. "Actual (in code)" = what the source actually does, vs the board state. "Board state" and "Pts" come from the latest DevOps export (2026-09-15).</t>
   </si>
 </sst>
 </file>
@@ -5148,13 +5151,13 @@
         <v>310</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>272</v>
+        <v>311</v>
       </c>
       <c r="F81" s="10" t="s">
         <v>307</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H81" s="10" t="s">
         <v>280</v>
@@ -5166,7 +5169,7 @@
         <v>3282</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5177,13 +5180,13 @@
         <v>185</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F82" s="10" t="s">
         <v>307</v>
@@ -5201,7 +5204,7 @@
         <v>3283</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5212,19 +5215,19 @@
         <v>229</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F83" s="10" t="s">
         <v>307</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>19</v>
@@ -5236,7 +5239,7 @@
         <v>3284</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5247,10 +5250,10 @@
         <v>97</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E84" s="9" t="s">
         <v>272</v>
@@ -5271,7 +5274,7 @@
         <v>3285</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5282,10 +5285,10 @@
         <v>121</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>272</v>
@@ -5306,7 +5309,7 @@
         <v>3286</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -5317,10 +5320,10 @@
         <v>185</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E86" s="25" t="s">
         <v>272</v>
@@ -5338,10 +5341,10 @@
         <v>20</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K86" s="25" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -5352,13 +5355,13 @@
         <v>185</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>17</v>
@@ -5373,10 +5376,10 @@
         <v>20</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K87" s="13" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -5387,13 +5390,13 @@
         <v>185</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F88" s="25" t="s">
         <v>17</v>
@@ -5408,10 +5411,10 @@
         <v>20</v>
       </c>
       <c r="J88" s="25" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K88" s="25" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5422,13 +5425,13 @@
         <v>229</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>17</v>
@@ -5443,10 +5446,10 @@
         <v>110</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5457,13 +5460,13 @@
         <v>185</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F90" s="25" t="s">
         <v>267</v>
@@ -5478,10 +5481,10 @@
         <v>20</v>
       </c>
       <c r="J90" s="25" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K90" s="25" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
   </sheetData>
@@ -5538,7 +5541,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -5551,7 +5554,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -5564,7 +5567,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -5577,28 +5580,28 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="I4" s="29" t="s">
         <v>22</v>
@@ -5609,13 +5612,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E5" s="32">
         <v>3</v>
@@ -5624,7 +5627,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H5" s="31" t="s">
         <v>22</v>
@@ -5635,22 +5638,22 @@
         <v>37</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E6" s="37">
         <v>2</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H6" s="36" t="s">
         <v>22</v>
@@ -5658,25 +5661,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E7" s="32">
         <v>2</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H7" s="31" t="s">
         <v>22</v>
@@ -5687,13 +5690,13 @@
         <v>41</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E8" s="37">
         <v>3</v>
@@ -5702,7 +5705,7 @@
         <v>38</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H8" s="36" t="s">
         <v>22</v>
@@ -5713,22 +5716,22 @@
         <v>33</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E9" s="32">
         <v>3</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H9" s="31" t="s">
         <v>22</v>
@@ -5739,13 +5742,13 @@
         <v>94</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E10" s="37">
         <v>2</v>
@@ -5754,7 +5757,7 @@
         <v>91</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>22</v>
@@ -5765,13 +5768,13 @@
         <v>71</v>
       </c>
       <c r="B11" s="31" t="s">
+        <v>379</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="D11" s="33" t="s">
         <v>378</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>372</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>377</v>
       </c>
       <c r="E11" s="32">
         <v>3</v>
@@ -5780,7 +5783,7 @@
         <v>68</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H11" s="31" t="s">
         <v>22</v>
@@ -5791,13 +5794,13 @@
         <v>75</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E12" s="37">
         <v>3</v>
@@ -5806,7 +5809,7 @@
         <v>72</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H12" s="36" t="s">
         <v>22</v>
@@ -5817,13 +5820,13 @@
         <v>78</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E13" s="32">
         <v>2</v>
@@ -5832,7 +5835,7 @@
         <v>76</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H13" s="31" t="s">
         <v>22</v>
@@ -5843,13 +5846,13 @@
         <v>82</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E14" s="37">
         <v>2</v>
@@ -5858,7 +5861,7 @@
         <v>79</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H14" s="36" t="s">
         <v>22</v>
@@ -5869,13 +5872,13 @@
         <v>86</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E15" s="32">
         <v>2</v>
@@ -5884,7 +5887,7 @@
         <v>83</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H15" s="31" t="s">
         <v>22</v>
@@ -5895,22 +5898,22 @@
         <v>63</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E16" s="37">
         <v>3</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H16" s="36" t="s">
         <v>22</v>
@@ -5921,22 +5924,22 @@
         <v>52</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E17" s="32">
         <v>3</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H17" s="31" t="s">
         <v>22</v>
@@ -5947,13 +5950,13 @@
         <v>173</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E18" s="37">
         <v>3</v>
@@ -5962,24 +5965,24 @@
         <v>174</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H18" s="36" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D19" s="40" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E19" s="32">
         <v>3</v>
@@ -5988,10 +5991,10 @@
         <v>117</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -5999,25 +6002,25 @@
         <v>184</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E20" s="37">
         <v>5</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -6028,10 +6031,10 @@
         <v>397</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E21" s="32">
         <v>3</v>
@@ -6040,10 +6043,10 @@
         <v>398</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6054,10 +6057,10 @@
         <v>399</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E22" s="37">
         <v>5</v>
@@ -6066,7 +6069,7 @@
         <v>400</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H22" s="36" t="s">
         <v>22</v>
@@ -6080,10 +6083,10 @@
         <v>401</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E23" s="32">
         <v>3</v>
@@ -6092,7 +6095,7 @@
         <v>106</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H23" s="31" t="s">
         <v>22</v>
@@ -6106,10 +6109,10 @@
         <v>402</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E24" s="37">
         <v>3</v>
@@ -6118,7 +6121,7 @@
         <v>102</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H24" s="36" t="s">
         <v>22</v>
@@ -6132,10 +6135,10 @@
         <v>404</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E25" s="32">
         <v>3</v>
@@ -6144,7 +6147,7 @@
         <v>157</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H25" s="31" t="s">
         <v>22</v>
@@ -6158,7 +6161,7 @@
         <v>406</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D26" s="38" t="s">
         <v>407</v>
@@ -6170,7 +6173,7 @@
         <v>408</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H26" s="36" t="s">
         <v>409</v>
@@ -6184,10 +6187,10 @@
         <v>410</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E27" s="32">
         <v>3</v>
@@ -6196,7 +6199,7 @@
         <v>161</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>22</v>
@@ -6210,10 +6213,10 @@
         <v>411</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E28" s="37">
         <v>3</v>
@@ -6222,7 +6225,7 @@
         <v>87</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H28" s="36" t="s">
         <v>22</v>
@@ -6236,10 +6239,10 @@
         <v>413</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E29" s="32">
         <v>3</v>
@@ -6248,7 +6251,7 @@
         <v>414</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H29" s="31" t="s">
         <v>22</v>
@@ -6262,10 +6265,10 @@
         <v>415</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E30" s="37">
         <v>3</v>
@@ -6274,7 +6277,7 @@
         <v>141</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H30" s="36" t="s">
         <v>22</v>
@@ -6288,7 +6291,7 @@
         <v>416</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D31" s="33" t="s">
         <v>407</v>
@@ -6300,10 +6303,10 @@
         <v>153</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>22</v>
+        <v>417</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -6311,13 +6314,13 @@
         <v>148</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E32" s="37">
         <v>3</v>
@@ -6326,7 +6329,7 @@
         <v>145</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H32" s="36" t="s">
         <v>22</v>
@@ -6337,13 +6340,13 @@
         <v>152</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E33" s="32">
         <v>3</v>
@@ -6352,7 +6355,7 @@
         <v>149</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H33" s="31" t="s">
         <v>22</v>
@@ -6360,25 +6363,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="35" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E34" s="37">
         <v>5</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H34" s="36" t="s">
         <v>22</v>
@@ -6386,25 +6389,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E35" s="32">
         <v>5</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H35" s="31" t="s">
         <v>22</v>
@@ -6415,13 +6418,13 @@
         <v>261</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E36" s="37">
         <v>3</v>
@@ -6430,7 +6433,7 @@
         <v>258</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H36" s="36" t="s">
         <v>22</v>
@@ -6441,22 +6444,22 @@
         <v>189</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E37" s="32">
         <v>5</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H37" s="31" t="s">
         <v>22</v>
@@ -6467,13 +6470,13 @@
         <v>193</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E38" s="37">
         <v>3</v>
@@ -6482,7 +6485,7 @@
         <v>190</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H38" s="36" t="s">
         <v>22</v>
@@ -6493,13 +6496,13 @@
         <v>210</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E39" s="32">
         <v>3</v>
@@ -6508,7 +6511,7 @@
         <v>207</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H39" s="31" t="s">
         <v>22</v>
@@ -6519,22 +6522,22 @@
         <v>214</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E40" s="37">
         <v>2</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H40" s="36" t="s">
         <v>22</v>
@@ -6545,25 +6548,25 @@
         <v>222</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E41" s="32">
         <v>3</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>364</v>
+        <v>435</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -6571,22 +6574,22 @@
         <v>237</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E42" s="37">
         <v>5</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H42" s="36" t="s">
         <v>22</v>
@@ -6597,13 +6600,13 @@
         <v>241</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E43" s="32">
         <v>3</v>
@@ -6612,7 +6615,7 @@
         <v>238</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H43" s="31" t="s">
         <v>22</v>
@@ -6620,7 +6623,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -6633,25 +6636,25 @@
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="H46" s="29" t="s">
         <v>22</v>
@@ -6668,19 +6671,19 @@
         <v>264</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E47" s="32">
         <v>2</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
@@ -6690,10 +6693,10 @@
         <v>274</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D48" s="31" t="s">
         <v>407</v>
@@ -6702,10 +6705,10 @@
         <v>2</v>
       </c>
       <c r="F48" s="45" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
@@ -6718,7 +6721,7 @@
         <v>277</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D49" s="31" t="s">
         <v>407</v>
@@ -6727,10 +6730,10 @@
         <v>8</v>
       </c>
       <c r="F49" s="45" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
@@ -6740,10 +6743,10 @@
         <v>285</v>
       </c>
       <c r="B50" s="31" t="s">
+        <v>448</v>
+      </c>
+      <c r="C50" s="32" t="s">
         <v>446</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>444</v>
       </c>
       <c r="D50" s="31" t="s">
         <v>407</v>
@@ -6752,17 +6755,17 @@
         <v>5</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G50" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B52" s="46"/>
       <c r="C52" s="46"/>
@@ -6784,7 +6787,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E53" s="29" t="s">
         <v>22</v>
@@ -6813,7 +6816,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E54" s="31"/>
       <c r="F54" s="31"/>
@@ -6832,7 +6835,7 @@
         <v>44</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E55" s="31"/>
       <c r="F55" s="31"/>
@@ -6851,7 +6854,7 @@
         <v>139</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
@@ -6870,7 +6873,7 @@
         <v>196</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
@@ -6889,7 +6892,7 @@
         <v>205</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E58" s="31"/>
       <c r="F58" s="31"/>
@@ -6899,7 +6902,7 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="49" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B60" s="49"/>
       <c r="C60" s="49"/>
@@ -6921,13 +6924,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="G61" s="29" t="s">
         <v>22</v>
@@ -6947,16 +6950,16 @@
         <v>64</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F62" s="51" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="G62" s="51"/>
       <c r="H62" s="51"/>
@@ -6970,16 +6973,16 @@
         <v>64</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E63" s="50" t="s">
         <v>407</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="G63" s="51"/>
       <c r="H63" s="51"/>
@@ -6993,16 +6996,16 @@
         <v>140</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E64" s="50" t="s">
         <v>407</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="G64" s="51"/>
       <c r="H64" s="51"/>
@@ -7016,16 +7019,16 @@
         <v>298</v>
       </c>
       <c r="C65" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E65" s="50" t="s">
         <v>407</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G65" s="51"/>
       <c r="H65" s="51"/>
@@ -7039,16 +7042,16 @@
         <v>185</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E66" s="50" t="s">
         <v>407</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
@@ -7056,7 +7059,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
@@ -7067,36 +7070,36 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B69" s="29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="G69" s="29" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="30" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B70" s="31" t="s">
         <v>305</v>
       </c>
       <c r="C70" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D70" s="31" t="s">
         <v>407</v>
@@ -7105,67 +7108,67 @@
         <v>8</v>
       </c>
       <c r="F70" s="44" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B71" s="31" t="s">
         <v>309</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E71" s="32">
         <v>13</v>
       </c>
       <c r="F71" s="45" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G71" s="31" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E72" s="32">
         <v>3</v>
       </c>
       <c r="F72" s="44" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G72" s="31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="30" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D73" s="31" t="s">
         <v>407</v>
@@ -7174,21 +7177,21 @@
         <v>8</v>
       </c>
       <c r="F73" s="45" t="s">
-        <v>482</v>
+        <v>435</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="30" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D74" s="31" t="s">
         <v>407</v>
@@ -7197,21 +7200,21 @@
         <v>8</v>
       </c>
       <c r="F74" s="44" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G74" s="31" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="30" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D75" s="31" t="s">
         <v>407</v>
@@ -7220,33 +7223,33 @@
         <v>8</v>
       </c>
       <c r="F75" s="45" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="30" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C76" s="32" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D76" s="31" t="s">
         <v>407</v>
       </c>
       <c r="E76" s="32" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F76" s="44" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -7289,14 +7292,14 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -7306,10 +7309,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -7325,7 +7328,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B6" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"In Progress")</f>
@@ -7347,7 +7350,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B8" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Backlog")</f>
@@ -7358,7 +7361,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B9" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Blocked")</f>
@@ -7369,7 +7372,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B10" s="59">
         <f>COUNTA('Feature List'!$G$5:$G$200)</f>
@@ -7390,10 +7393,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -7409,7 +7412,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="55" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B15" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"In Progress")</f>
@@ -7431,7 +7434,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B17" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Failed")</f>
@@ -7442,7 +7445,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="55" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B18" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Blocked")</f>
@@ -7453,7 +7456,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B19" s="59">
         <f>COUNTA('Feature List'!$I$5:$I$200)</f>
@@ -7474,10 +7477,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -7526,7 +7529,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B27" s="59">
         <f>COUNTA('Feature List'!$F$5:$F$200)</f>
@@ -7537,14 +7540,14 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="61" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B29" s="56">
         <v>60</v>
@@ -7552,7 +7555,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="55" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B30" s="56">
         <v>60</v>
@@ -7560,7 +7563,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="55" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B31" s="56">
         <v>4</v>
@@ -7568,7 +7571,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="55" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B32" s="56">
         <v>4</v>
@@ -7576,7 +7579,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="55" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B33" s="56">
         <v>0</v>
@@ -7584,7 +7587,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="55" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B34" s="56">
         <v>2</v>
@@ -7614,16 +7617,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B1" s="52"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7631,7 +7634,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7639,7 +7642,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7647,7 +7650,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7655,7 +7658,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7663,7 +7666,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7671,15 +7674,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
   </sheetData>

--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="519">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -103,9 +103,18 @@
     <t>main.js · switchTab() / index.html</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
     <t>3218, 3228</t>
   </si>
   <si>
+    <t>Tested and closed 15 Sept 2026.</t>
+  </si>
+  <si>
     <t>Value-stream tab bar</t>
   </si>
   <si>
@@ -343,12 +352,6 @@
     <t>mappingView.js · showCell()</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
     <t>3236</t>
   </si>
   <si>
@@ -940,7 +943,10 @@
     <t>Nice to Have</t>
   </si>
   <si>
-    <t>Future enhancement. Story 3281 under Feature 3211 (Client Versions).</t>
+    <t>Ready for Testing</t>
+  </si>
+  <si>
+    <t>Future enhancement. Story 3281 under Feature 3211 (Client Versions). | Development complete, ready for testing.</t>
   </si>
   <si>
     <t>Guided discovery workflow</t>
@@ -1716,7 +1722,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1740,7 +1746,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1751,11 +1757,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F7F4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1933,7 +1934,7 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1945,7 +1946,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1993,10 +1994,10 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2005,10 +2006,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2020,7 +2021,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2032,13 +2033,13 @@
     <xf numFmtId="9" fontId="28" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="27" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2570,16 +2571,16 @@
         <v>18</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K7" s="13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -2590,13 +2591,13 @@
         <v>13</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F8" s="10" t="s">
         <v>17</v>
@@ -2611,7 +2612,7 @@
         <v>20</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K8" s="20" t="s">
         <v>22</v>
@@ -2625,13 +2626,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F9" s="10" t="s">
         <v>17</v>
@@ -2646,7 +2647,7 @@
         <v>20</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K9" s="13" t="s">
         <v>22</v>
@@ -2660,13 +2661,13 @@
         <v>13</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>17</v>
@@ -2681,7 +2682,7 @@
         <v>20</v>
       </c>
       <c r="J10" s="19" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K10" s="20" t="s">
         <v>22</v>
@@ -2695,13 +2696,13 @@
         <v>13</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>17</v>
@@ -2727,16 +2728,16 @@
         <v>8</v>
       </c>
       <c r="B12" s="22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>17</v>
@@ -2745,16 +2746,16 @@
         <v>18</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J12" s="19" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -2762,16 +2763,16 @@
         <v>9</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>17</v>
@@ -2786,7 +2787,7 @@
         <v>20</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>22</v>
@@ -2797,16 +2798,16 @@
         <v>10</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D14" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>54</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>51</v>
       </c>
       <c r="F14" s="10" t="s">
         <v>17</v>
@@ -2821,7 +2822,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K14" s="20" t="s">
         <v>22</v>
@@ -2832,16 +2833,16 @@
         <v>11</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F15" s="10" t="s">
         <v>17</v>
@@ -2856,7 +2857,7 @@
         <v>20</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="K15" s="13" t="s">
         <v>22</v>
@@ -2867,16 +2868,16 @@
         <v>12</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D16" s="17" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F16" s="10" t="s">
         <v>17</v>
@@ -2891,7 +2892,7 @@
         <v>20</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K16" s="20" t="s">
         <v>22</v>
@@ -2902,16 +2903,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>17</v>
@@ -2920,16 +2921,16 @@
         <v>18</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2937,16 +2938,16 @@
         <v>14</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F18" s="10" t="s">
         <v>17</v>
@@ -2961,7 +2962,7 @@
         <v>20</v>
       </c>
       <c r="J18" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" s="20" t="s">
         <v>22</v>
@@ -2972,16 +2973,16 @@
         <v>15</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>17</v>
@@ -2996,7 +2997,7 @@
         <v>20</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K19" s="13" t="s">
         <v>22</v>
@@ -3007,16 +3008,16 @@
         <v>16</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>17</v>
@@ -3031,7 +3032,7 @@
         <v>20</v>
       </c>
       <c r="J20" s="19" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K20" s="20" t="s">
         <v>22</v>
@@ -3042,16 +3043,16 @@
         <v>17</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D21" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="E21" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="F21" s="10" t="s">
         <v>17</v>
@@ -3066,7 +3067,7 @@
         <v>20</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K21" s="13" t="s">
         <v>22</v>
@@ -3077,16 +3078,16 @@
         <v>18</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E22" s="18" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F22" s="10" t="s">
         <v>17</v>
@@ -3101,7 +3102,7 @@
         <v>20</v>
       </c>
       <c r="J22" s="19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="K22" s="20" t="s">
         <v>22</v>
@@ -3112,16 +3113,16 @@
         <v>19</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F23" s="10" t="s">
         <v>17</v>
@@ -3136,7 +3137,7 @@
         <v>20</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K23" s="13" t="s">
         <v>22</v>
@@ -3147,16 +3148,16 @@
         <v>20</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E24" s="18" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F24" s="10" t="s">
         <v>17</v>
@@ -3171,7 +3172,7 @@
         <v>20</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K24" s="20" t="s">
         <v>22</v>
@@ -3182,16 +3183,16 @@
         <v>21</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F25" s="10" t="s">
         <v>17</v>
@@ -3206,7 +3207,7 @@
         <v>20</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K25" s="13" t="s">
         <v>22</v>
@@ -3217,16 +3218,16 @@
         <v>22</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E26" s="18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>17</v>
@@ -3241,7 +3242,7 @@
         <v>20</v>
       </c>
       <c r="J26" s="19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K26" s="20" t="s">
         <v>22</v>
@@ -3252,16 +3253,16 @@
         <v>23</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>17</v>
@@ -3276,7 +3277,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K27" s="13" t="s">
         <v>22</v>
@@ -3287,16 +3288,16 @@
         <v>24</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>17</v>
@@ -3311,7 +3312,7 @@
         <v>20</v>
       </c>
       <c r="J28" s="19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K28" s="20" t="s">
         <v>22</v>
@@ -3322,16 +3323,16 @@
         <v>25</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F29" s="10" t="s">
         <v>17</v>
@@ -3340,16 +3341,16 @@
         <v>18</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K29" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -3357,16 +3358,16 @@
         <v>26</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="10" t="s">
         <v>17</v>
@@ -3381,7 +3382,7 @@
         <v>20</v>
       </c>
       <c r="J30" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K30" s="20" t="s">
         <v>22</v>
@@ -3392,16 +3393,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F31" s="10" t="s">
         <v>17</v>
@@ -3410,16 +3411,16 @@
         <v>18</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I31" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K31" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -3427,16 +3428,16 @@
         <v>28</v>
       </c>
       <c r="B32" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F32" s="10" t="s">
         <v>17</v>
@@ -3451,7 +3452,7 @@
         <v>20</v>
       </c>
       <c r="J32" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K32" s="20" t="s">
         <v>22</v>
@@ -3462,16 +3463,16 @@
         <v>29</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F33" s="10" t="s">
         <v>17</v>
@@ -3486,7 +3487,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K33" s="13" t="s">
         <v>22</v>
@@ -3497,16 +3498,16 @@
         <v>30</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C34" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="E34" s="18" t="s">
         <v>129</v>
-      </c>
-      <c r="D34" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="E34" s="18" t="s">
-        <v>128</v>
       </c>
       <c r="F34" s="10" t="s">
         <v>17</v>
@@ -3521,7 +3522,7 @@
         <v>20</v>
       </c>
       <c r="J34" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K34" s="20" t="s">
         <v>22</v>
@@ -3532,16 +3533,16 @@
         <v>31</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F35" s="10" t="s">
         <v>17</v>
@@ -3556,7 +3557,7 @@
         <v>20</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K35" s="13" t="s">
         <v>22</v>
@@ -3567,16 +3568,16 @@
         <v>32</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F36" s="10" t="s">
         <v>17</v>
@@ -3591,7 +3592,7 @@
         <v>20</v>
       </c>
       <c r="J36" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K36" s="20" t="s">
         <v>22</v>
@@ -3602,16 +3603,16 @@
         <v>33</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F37" s="10" t="s">
         <v>17</v>
@@ -3637,16 +3638,16 @@
         <v>34</v>
       </c>
       <c r="B38" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F38" s="10" t="s">
         <v>17</v>
@@ -3661,7 +3662,7 @@
         <v>20</v>
       </c>
       <c r="J38" s="19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K38" s="20" t="s">
         <v>22</v>
@@ -3672,16 +3673,16 @@
         <v>35</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F39" s="10" t="s">
         <v>17</v>
@@ -3696,7 +3697,7 @@
         <v>20</v>
       </c>
       <c r="J39" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K39" s="13" t="s">
         <v>22</v>
@@ -3707,16 +3708,16 @@
         <v>36</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F40" s="10" t="s">
         <v>17</v>
@@ -3731,7 +3732,7 @@
         <v>20</v>
       </c>
       <c r="J40" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K40" s="20" t="s">
         <v>22</v>
@@ -3742,16 +3743,16 @@
         <v>37</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F41" s="10" t="s">
         <v>17</v>
@@ -3766,7 +3767,7 @@
         <v>20</v>
       </c>
       <c r="J41" s="12" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="K41" s="13" t="s">
         <v>22</v>
@@ -3777,16 +3778,16 @@
         <v>38</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F42" s="10" t="s">
         <v>17</v>
@@ -3801,7 +3802,7 @@
         <v>20</v>
       </c>
       <c r="J42" s="19" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K42" s="20" t="s">
         <v>22</v>
@@ -3812,16 +3813,16 @@
         <v>39</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F43" s="10" t="s">
         <v>17</v>
@@ -3836,7 +3837,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="K43" s="13" t="s">
         <v>22</v>
@@ -3847,16 +3848,16 @@
         <v>40</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F44" s="10" t="s">
         <v>17</v>
@@ -3865,16 +3866,16 @@
         <v>18</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J44" s="19" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -3882,16 +3883,16 @@
         <v>41</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F45" s="10" t="s">
         <v>17</v>
@@ -3900,16 +3901,16 @@
         <v>18</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J45" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K45" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -3917,16 +3918,16 @@
         <v>42</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F46" s="10" t="s">
         <v>17</v>
@@ -3935,16 +3936,16 @@
         <v>18</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J46" s="19" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -3952,16 +3953,16 @@
         <v>43</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F47" s="10" t="s">
         <v>17</v>
@@ -3976,7 +3977,7 @@
         <v>20</v>
       </c>
       <c r="J47" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K47" s="13" t="s">
         <v>22</v>
@@ -3987,16 +3988,16 @@
         <v>44</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D48" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F48" s="10" t="s">
         <v>17</v>
@@ -4011,7 +4012,7 @@
         <v>20</v>
       </c>
       <c r="J48" s="19" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K48" s="20" t="s">
         <v>22</v>
@@ -4022,16 +4023,16 @@
         <v>45</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F49" s="10" t="s">
         <v>17</v>
@@ -4040,16 +4041,16 @@
         <v>18</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K49" s="13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
@@ -4057,16 +4058,16 @@
         <v>46</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F50" s="10" t="s">
         <v>17</v>
@@ -4075,16 +4076,16 @@
         <v>18</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J50" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K50" s="20" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
@@ -4092,16 +4093,16 @@
         <v>47</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F51" s="10" t="s">
         <v>17</v>
@@ -4127,16 +4128,16 @@
         <v>48</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C52" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D52" s="17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F52" s="10" t="s">
         <v>17</v>
@@ -4145,16 +4146,16 @@
         <v>18</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I52" s="10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J52" s="19" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K52" s="20" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -4162,16 +4163,16 @@
         <v>49</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F53" s="10" t="s">
         <v>17</v>
@@ -4180,16 +4181,16 @@
         <v>18</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I53" s="10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J53" s="12" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K53" s="13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -4197,16 +4198,16 @@
         <v>50</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C54" s="16" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D54" s="17" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F54" s="10" t="s">
         <v>17</v>
@@ -4232,16 +4233,16 @@
         <v>51</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F55" s="10" t="s">
         <v>17</v>
@@ -4256,7 +4257,7 @@
         <v>20</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K55" s="13" t="s">
         <v>22</v>
@@ -4267,16 +4268,16 @@
         <v>52</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D56" s="17" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="E56" s="18" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F56" s="10" t="s">
         <v>17</v>
@@ -4291,7 +4292,7 @@
         <v>20</v>
       </c>
       <c r="J56" s="19" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K56" s="20" t="s">
         <v>22</v>
@@ -4302,16 +4303,16 @@
         <v>53</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F57" s="10" t="s">
         <v>17</v>
@@ -4326,7 +4327,7 @@
         <v>20</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K57" s="13" t="s">
         <v>22</v>
@@ -4337,16 +4338,16 @@
         <v>54</v>
       </c>
       <c r="B58" s="22" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C58" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D58" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E58" s="18" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F58" s="10" t="s">
         <v>17</v>
@@ -4361,10 +4362,10 @@
         <v>20</v>
       </c>
       <c r="J58" s="19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K58" s="20" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -4372,16 +4373,16 @@
         <v>55</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F59" s="10" t="s">
         <v>17</v>
@@ -4396,7 +4397,7 @@
         <v>20</v>
       </c>
       <c r="J59" s="12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K59" s="13" t="s">
         <v>22</v>
@@ -4407,16 +4408,16 @@
         <v>56</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C60" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D60" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F60" s="10" t="s">
         <v>17</v>
@@ -4431,7 +4432,7 @@
         <v>20</v>
       </c>
       <c r="J60" s="19" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K60" s="20" t="s">
         <v>22</v>
@@ -4442,16 +4443,16 @@
         <v>57</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F61" s="10" t="s">
         <v>17</v>
@@ -4466,7 +4467,7 @@
         <v>20</v>
       </c>
       <c r="J61" s="12" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K61" s="13" t="s">
         <v>22</v>
@@ -4477,16 +4478,16 @@
         <v>58</v>
       </c>
       <c r="B62" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C62" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D62" s="17" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F62" s="10" t="s">
         <v>17</v>
@@ -4501,7 +4502,7 @@
         <v>20</v>
       </c>
       <c r="J62" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K62" s="20" t="s">
         <v>22</v>
@@ -4512,16 +4513,16 @@
         <v>59</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F63" s="10" t="s">
         <v>17</v>
@@ -4536,7 +4537,7 @@
         <v>20</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K63" s="13" t="s">
         <v>22</v>
@@ -4547,16 +4548,16 @@
         <v>60</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C64" s="16" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D64" s="17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F64" s="10" t="s">
         <v>17</v>
@@ -4571,7 +4572,7 @@
         <v>20</v>
       </c>
       <c r="J64" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K64" s="20" t="s">
         <v>22</v>
@@ -4582,16 +4583,16 @@
         <v>61</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F65" s="10" t="s">
         <v>17</v>
@@ -4606,7 +4607,7 @@
         <v>20</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K65" s="13" t="s">
         <v>22</v>
@@ -4617,16 +4618,16 @@
         <v>62</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C66" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F66" s="10" t="s">
         <v>17</v>
@@ -4641,7 +4642,7 @@
         <v>20</v>
       </c>
       <c r="J66" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K66" s="20" t="s">
         <v>22</v>
@@ -4652,16 +4653,16 @@
         <v>63</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F67" s="10" t="s">
         <v>17</v>
@@ -4676,7 +4677,7 @@
         <v>20</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K67" s="13" t="s">
         <v>22</v>
@@ -4687,16 +4688,16 @@
         <v>64</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C68" s="16" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D68" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F68" s="10" t="s">
         <v>17</v>
@@ -4711,7 +4712,7 @@
         <v>20</v>
       </c>
       <c r="J68" s="19" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K68" s="20" t="s">
         <v>22</v>
@@ -4722,16 +4723,16 @@
         <v>65</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F69" s="10" t="s">
         <v>17</v>
@@ -4740,16 +4741,16 @@
         <v>18</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J69" s="12" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K69" s="13" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -4757,16 +4758,16 @@
         <v>66</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E70" s="18" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F70" s="10" t="s">
         <v>17</v>
@@ -4781,7 +4782,7 @@
         <v>20</v>
       </c>
       <c r="J70" s="19" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="K70" s="20" t="s">
         <v>22</v>
@@ -4795,31 +4796,31 @@
         <v>13</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G71" s="11" t="s">
         <v>18</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J71" s="12" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K71" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -4827,22 +4828,22 @@
         <v>68</v>
       </c>
       <c r="B72" s="22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="E72" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F72" s="24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H72" s="10" t="s">
         <v>19</v>
@@ -4851,10 +4852,10 @@
         <v>20</v>
       </c>
       <c r="J72" s="19" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K72" s="20" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -4862,34 +4863,34 @@
         <v>69</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I73" s="10" t="s">
         <v>20</v>
       </c>
       <c r="J73" s="12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K73" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -4897,34 +4898,34 @@
         <v>70</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D74" s="17" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E74" s="18" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F74" s="24" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I74" s="10" t="s">
         <v>20</v>
       </c>
       <c r="J74" s="19" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K74" s="20" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -4932,34 +4933,34 @@
         <v>71</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G75" s="10" t="s">
         <v>18</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J75" s="12">
         <v>3270</v>
       </c>
       <c r="K75" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -4967,25 +4968,25 @@
         <v>72</v>
       </c>
       <c r="B76" s="15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E76" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I76" s="10" t="s">
         <v>20</v>
@@ -4994,7 +4995,7 @@
         <v>3271</v>
       </c>
       <c r="K76" s="20" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -5002,25 +5003,25 @@
         <v>73</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I77" s="10" t="s">
         <v>20</v>
@@ -5029,7 +5030,7 @@
         <v>3272</v>
       </c>
       <c r="K77" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -5037,25 +5038,25 @@
         <v>74</v>
       </c>
       <c r="B78" s="22" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="E78" s="18" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I78" s="10" t="s">
         <v>20</v>
@@ -5064,7 +5065,7 @@
         <v>3273</v>
       </c>
       <c r="K78" s="20" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -5072,25 +5073,25 @@
         <v>75</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I79" s="10" t="s">
         <v>20</v>
@@ -5099,7 +5100,7 @@
         <v>3274</v>
       </c>
       <c r="K79" s="13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -5107,34 +5108,34 @@
         <v>76</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="E80" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>20</v>
+        <v>309</v>
       </c>
       <c r="J80" s="12">
         <v>3281</v>
       </c>
       <c r="K80" s="13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -5145,22 +5146,22 @@
         <v>13</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I81" s="10" t="s">
         <v>20</v>
@@ -5169,7 +5170,7 @@
         <v>3282</v>
       </c>
       <c r="K81" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -5177,34 +5178,34 @@
         <v>78</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E82" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>18</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J82" s="12">
         <v>3283</v>
       </c>
       <c r="K82" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -5212,22 +5213,22 @@
         <v>79</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F83" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G83" s="10" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H83" s="10" t="s">
         <v>19</v>
@@ -5239,7 +5240,7 @@
         <v>3284</v>
       </c>
       <c r="K83" s="13" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -5247,25 +5248,25 @@
         <v>80</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E84" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F84" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G84" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H84" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I84" s="10" t="s">
         <v>20</v>
@@ -5274,7 +5275,7 @@
         <v>3285</v>
       </c>
       <c r="K84" s="13" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -5282,25 +5283,25 @@
         <v>81</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F85" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G85" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H85" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I85" s="10" t="s">
         <v>20</v>
@@ -5309,7 +5310,7 @@
         <v>3286</v>
       </c>
       <c r="K85" s="13" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -5317,34 +5318,34 @@
         <v>82</v>
       </c>
       <c r="B86" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C86" s="25" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E86" s="25" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F86" s="25" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G86" s="25" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H86" s="25" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I86" s="25" t="s">
         <v>20</v>
       </c>
       <c r="J86" s="25" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="K86" s="25" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -5352,16 +5353,16 @@
         <v>83</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F87" s="10" t="s">
         <v>17</v>
@@ -5376,10 +5377,10 @@
         <v>20</v>
       </c>
       <c r="J87" s="12" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="K87" s="13" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -5387,16 +5388,16 @@
         <v>84</v>
       </c>
       <c r="B88" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C88" s="25" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E88" s="25" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="F88" s="25" t="s">
         <v>17</v>
@@ -5411,10 +5412,10 @@
         <v>20</v>
       </c>
       <c r="J88" s="25" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K88" s="25" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -5422,16 +5423,16 @@
         <v>85</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F89" s="10" t="s">
         <v>17</v>
@@ -5440,16 +5441,16 @@
         <v>18</v>
       </c>
       <c r="H89" s="10" t="s">
-        <v>109</v>
+        <v>29</v>
       </c>
       <c r="I89" s="10" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="J89" s="12" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="K89" s="13" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -5457,19 +5458,19 @@
         <v>86</v>
       </c>
       <c r="B90" s="25" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C90" s="25" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E90" s="25" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F90" s="25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G90" s="25" t="s">
         <v>18</v>
@@ -5481,10 +5482,10 @@
         <v>20</v>
       </c>
       <c r="J90" s="25" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="K90" s="25" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5541,7 +5542,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="26" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B1" s="26"/>
       <c r="C1" s="26"/>
@@ -5554,7 +5555,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="27" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B2" s="27"/>
       <c r="C2" s="27"/>
@@ -5567,7 +5568,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="28" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -5580,28 +5581,28 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C4" s="29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="G4" s="29" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="H4" s="29" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="I4" s="29" t="s">
         <v>22</v>
@@ -5612,13 +5613,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="31" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E5" s="32">
         <v>3</v>
@@ -5627,7 +5628,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H5" s="31" t="s">
         <v>22</v>
@@ -5635,25 +5636,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E6" s="37">
         <v>2</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="G6" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H6" s="36" t="s">
         <v>22</v>
@@ -5661,25 +5662,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="30" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B7" s="31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E7" s="32">
         <v>2</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="G7" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H7" s="31" t="s">
         <v>22</v>
@@ -5687,25 +5688,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="35" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" s="36" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C8" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E8" s="37">
         <v>3</v>
       </c>
       <c r="F8" s="36" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H8" s="36" t="s">
         <v>22</v>
@@ -5713,25 +5714,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="30" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B9" s="31" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E9" s="32">
         <v>3</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G9" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H9" s="31" t="s">
         <v>22</v>
@@ -5739,25 +5740,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="35" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B10" s="36" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D10" s="38" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E10" s="37">
         <v>2</v>
       </c>
       <c r="F10" s="36" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G10" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H10" s="36" t="s">
         <v>22</v>
@@ -5765,25 +5766,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="30" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B11" s="31" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C11" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D11" s="33" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E11" s="32">
         <v>3</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G11" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H11" s="31" t="s">
         <v>22</v>
@@ -5791,25 +5792,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="35" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B12" s="36" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D12" s="38" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E12" s="37">
         <v>3</v>
       </c>
       <c r="F12" s="36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G12" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H12" s="36" t="s">
         <v>22</v>
@@ -5817,25 +5818,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="30" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C13" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E13" s="32">
         <v>2</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H13" s="31" t="s">
         <v>22</v>
@@ -5843,25 +5844,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="35" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B14" s="36" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D14" s="38" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E14" s="37">
         <v>2</v>
       </c>
       <c r="F14" s="36" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G14" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H14" s="36" t="s">
         <v>22</v>
@@ -5869,25 +5870,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="30" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E15" s="32">
         <v>2</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H15" s="31" t="s">
         <v>22</v>
@@ -5895,25 +5896,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="35" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C16" s="37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E16" s="37">
         <v>3</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="G16" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H16" s="36" t="s">
         <v>22</v>
@@ -5921,25 +5922,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="30" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E17" s="32">
         <v>3</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="G17" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H17" s="31" t="s">
         <v>22</v>
@@ -5947,129 +5948,129 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B18" s="36" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C18" s="37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D18" s="39" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E18" s="37">
         <v>3</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G18" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H18" s="36" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>365</v>
+      </c>
+      <c r="D19" s="40" t="s">
         <v>392</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>393</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>390</v>
       </c>
       <c r="E19" s="32">
         <v>3</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G19" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C20" s="37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D20" s="41" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E20" s="37">
         <v>5</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="G20" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H20" s="36" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B21" s="31" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D21" s="42" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E21" s="32">
         <v>3</v>
       </c>
       <c r="F21" s="31" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G21" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H21" s="31" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="35" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D22" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E22" s="37">
         <v>5</v>
       </c>
       <c r="F22" s="36" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="G22" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H22" s="36" t="s">
         <v>22</v>
@@ -6077,25 +6078,25 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E23" s="32">
         <v>3</v>
       </c>
       <c r="F23" s="31" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G23" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H23" s="31" t="s">
         <v>22</v>
@@ -6103,25 +6104,25 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="35" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C24" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E24" s="37">
         <v>3</v>
       </c>
       <c r="F24" s="36" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H24" s="36" t="s">
         <v>22</v>
@@ -6129,25 +6130,25 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="30" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B25" s="31" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C25" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E25" s="32">
         <v>3</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G25" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H25" s="31" t="s">
         <v>22</v>
@@ -6155,51 +6156,51 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="35" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C26" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D26" s="38" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E26" s="37">
         <v>2</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G26" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H26" s="36" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E27" s="32">
         <v>3</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>22</v>
@@ -6207,25 +6208,25 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="35" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B28" s="36" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C28" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D28" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E28" s="37">
         <v>3</v>
       </c>
       <c r="F28" s="36" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="G28" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H28" s="36" t="s">
         <v>22</v>
@@ -6233,25 +6234,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="30" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C29" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E29" s="32">
         <v>3</v>
       </c>
       <c r="F29" s="31" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="G29" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H29" s="31" t="s">
         <v>22</v>
@@ -6259,25 +6260,25 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C30" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D30" s="38" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E30" s="37">
         <v>3</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G30" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H30" s="36" t="s">
         <v>22</v>
@@ -6285,51 +6286,51 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B31" s="31" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C31" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E31" s="32">
         <v>5</v>
       </c>
       <c r="F31" s="31" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G31" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H31" s="31" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B32" s="36" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C32" s="37" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D32" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E32" s="37">
         <v>3</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G32" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H32" s="36" t="s">
         <v>22</v>
@@ -6337,25 +6338,25 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B33" s="31" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C33" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E33" s="32">
         <v>3</v>
       </c>
       <c r="F33" s="31" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G33" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H33" s="31" t="s">
         <v>22</v>
@@ -6363,25 +6364,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="35" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D34" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E34" s="37">
         <v>5</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G34" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H34" s="36" t="s">
         <v>22</v>
@@ -6389,25 +6390,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="30" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B35" s="31" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C35" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E35" s="32">
         <v>5</v>
       </c>
       <c r="F35" s="31" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="G35" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H35" s="31" t="s">
         <v>22</v>
@@ -6415,25 +6416,25 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="35" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B36" s="36" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D36" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E36" s="37">
         <v>3</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G36" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H36" s="36" t="s">
         <v>22</v>
@@ -6441,25 +6442,25 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="30" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B37" s="31" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C37" s="32" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E37" s="32">
         <v>5</v>
       </c>
       <c r="F37" s="31" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="G37" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H37" s="31" t="s">
         <v>22</v>
@@ -6467,25 +6468,25 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B38" s="36" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C38" s="37" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D38" s="38" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E38" s="37">
         <v>3</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G38" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H38" s="36" t="s">
         <v>22</v>
@@ -6493,25 +6494,25 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="30" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E39" s="32">
         <v>3</v>
       </c>
       <c r="F39" s="31" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="G39" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H39" s="31" t="s">
         <v>22</v>
@@ -6519,25 +6520,25 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B40" s="36" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D40" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E40" s="37">
         <v>2</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="G40" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H40" s="36" t="s">
         <v>22</v>
@@ -6545,51 +6546,51 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="30" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E41" s="32">
         <v>3</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="G41" s="34" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="H41" s="31" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="35" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B42" s="36" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C42" s="37" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E42" s="37">
         <v>5</v>
       </c>
       <c r="F42" s="36" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="G42" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H42" s="36" t="s">
         <v>22</v>
@@ -6597,25 +6598,25 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="30" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C43" s="32" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E43" s="32">
         <v>3</v>
       </c>
       <c r="F43" s="31" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="G43" s="34" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="H43" s="31" t="s">
         <v>22</v>
@@ -6623,7 +6624,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="43" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B45" s="43"/>
       <c r="C45" s="43"/>
@@ -6636,25 +6637,25 @@
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B46" s="29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C46" s="29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D46" s="29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E46" s="29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F46" s="29" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="H46" s="29" t="s">
         <v>22</v>
@@ -6665,107 +6666,107 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="30" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C47" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D47" s="31" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E47" s="32">
         <v>2</v>
       </c>
       <c r="F47" s="44" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G47" s="31" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="H47" s="31"/>
       <c r="I47" s="31"/>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="30" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D48" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E48" s="32">
         <v>2</v>
       </c>
       <c r="F48" s="45" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G48" s="31" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H48" s="31"/>
       <c r="I48" s="31"/>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D49" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E49" s="32">
         <v>8</v>
       </c>
       <c r="F49" s="45" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G49" s="31" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="H49" s="31"/>
       <c r="I49" s="31"/>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="30" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B50" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="C50" s="32" t="s">
         <v>448</v>
       </c>
-      <c r="C50" s="32" t="s">
-        <v>446</v>
-      </c>
       <c r="D50" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E50" s="32">
         <v>5</v>
       </c>
       <c r="F50" s="45" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G50" s="31" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H50" s="31"/>
       <c r="I50" s="31"/>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="46" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B52" s="46"/>
       <c r="C52" s="46"/>
@@ -6787,7 +6788,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="29" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E53" s="29" t="s">
         <v>22</v>
@@ -6816,7 +6817,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="31" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E54" s="31"/>
       <c r="F54" s="31"/>
@@ -6826,16 +6827,16 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="47" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B55" s="31" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="48" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D55" s="31" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E55" s="31"/>
       <c r="F55" s="31"/>
@@ -6845,16 +6846,16 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="47" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C56" s="48" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D56" s="31" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E56" s="31"/>
       <c r="F56" s="31"/>
@@ -6864,16 +6865,16 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C57" s="48" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D57" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E57" s="31"/>
       <c r="F57" s="31"/>
@@ -6883,16 +6884,16 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="47" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C58" s="48" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D58" s="31" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E58" s="31"/>
       <c r="F58" s="31"/>
@@ -6902,7 +6903,7 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="49" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B60" s="49"/>
       <c r="C60" s="49"/>
@@ -6924,13 +6925,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="29" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E61" s="29" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="G61" s="29" t="s">
         <v>22</v>
@@ -6944,22 +6945,22 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="47" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C62" s="31" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D62" s="31" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E62" s="50" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="F62" s="51" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="G62" s="51"/>
       <c r="H62" s="51"/>
@@ -6967,22 +6968,22 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="47" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C63" s="31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D63" s="31" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E63" s="50" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F63" s="51" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G63" s="51"/>
       <c r="H63" s="51"/>
@@ -6990,22 +6991,22 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="47" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C64" s="31" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D64" s="31" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E64" s="50" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F64" s="51" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="G64" s="51"/>
       <c r="H64" s="51"/>
@@ -7013,22 +7014,22 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="47" t="s">
+        <v>300</v>
+      </c>
+      <c r="B65" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="B65" s="31" t="s">
-        <v>298</v>
-      </c>
       <c r="C65" s="31" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D65" s="31" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E65" s="50" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F65" s="51" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="G65" s="51"/>
       <c r="H65" s="51"/>
@@ -7036,22 +7037,22 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="47" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C66" s="31" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D66" s="31" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E66" s="50" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F66" s="51" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G66" s="51"/>
       <c r="H66" s="51"/>
@@ -7059,7 +7060,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="43" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B68" s="43"/>
       <c r="C68" s="43"/>
@@ -7070,186 +7071,186 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="29" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B69" s="29" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C69" s="29" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D69" s="29" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E69" s="29" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F69" s="29" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G69" s="29" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="30" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C70" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D70" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E70" s="32">
         <v>8</v>
       </c>
       <c r="F70" s="44" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G70" s="31" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="30" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B71" s="31" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C71" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D71" s="31" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E71" s="32">
         <v>13</v>
       </c>
       <c r="F71" s="45" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G71" s="31" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="30" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C72" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D72" s="31" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E72" s="32">
         <v>3</v>
       </c>
       <c r="F72" s="44" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="G72" s="31" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="30" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B73" s="31" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C73" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D73" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E73" s="32">
         <v>8</v>
       </c>
       <c r="F73" s="45" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G73" s="31" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="30" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B74" s="31" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C74" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D74" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E74" s="32">
         <v>8</v>
       </c>
       <c r="F74" s="44" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G74" s="31" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="30" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C75" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D75" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E75" s="32">
         <v>8</v>
       </c>
       <c r="F75" s="45" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B76" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="B76" s="31" t="s">
-        <v>328</v>
-      </c>
       <c r="C76" s="32" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D76" s="31" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E76" s="32" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="F76" s="44" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G76" s="31" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -7292,14 +7293,14 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B1" s="52"/>
       <c r="C1" s="52"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -7309,10 +7310,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C4" s="54" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -7328,7 +7329,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B6" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"In Progress")</f>
@@ -7339,7 +7340,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="55" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B7" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Not Started")</f>
@@ -7350,7 +7351,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B8" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Backlog")</f>
@@ -7361,7 +7362,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="55" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B9" s="56">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Blocked")</f>
@@ -7372,7 +7373,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="58" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B10" s="59">
         <f>COUNTA('Feature List'!$G$5:$G$200)</f>
@@ -7393,10 +7394,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="54" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C13" s="54" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -7412,7 +7413,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="55" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B15" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"In Progress")</f>
@@ -7423,7 +7424,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="B16" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Pass")</f>
@@ -7434,7 +7435,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="55" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B17" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Failed")</f>
@@ -7445,7 +7446,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="55" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B18" s="56">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Blocked")</f>
@@ -7456,7 +7457,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="58" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B19" s="59">
         <f>COUNTA('Feature List'!$I$5:$I$200)</f>
@@ -7477,10 +7478,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="54" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C22" s="54" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -7496,7 +7497,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="55" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B24" s="56">
         <f>COUNTIF('Feature List'!$F$5:$F$200,"DevOps Backlog")</f>
@@ -7507,7 +7508,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="55" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B25" s="56">
         <f>COUNTIF('Feature List'!$F$5:$F$200,"New Requirement")</f>
@@ -7518,7 +7519,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="58" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B26" s="59">
         <f>COUNTIF('Feature List'!$F$5:$F$200,"Nice to Have")</f>
@@ -7529,7 +7530,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="58" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B27" s="59">
         <f>COUNTA('Feature List'!$F$5:$F$200)</f>
@@ -7540,14 +7541,14 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="61" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B28" s="61"/>
       <c r="C28" s="61"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="55" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B29" s="56">
         <v>60</v>
@@ -7555,7 +7556,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="55" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B30" s="56">
         <v>60</v>
@@ -7563,7 +7564,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="55" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B31" s="56">
         <v>4</v>
@@ -7571,7 +7572,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="55" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B32" s="56">
         <v>4</v>
@@ -7579,7 +7580,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="55" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B33" s="56">
         <v>0</v>
@@ -7587,7 +7588,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="55" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B34" s="56">
         <v>2</v>
@@ -7617,16 +7618,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="52" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B1" s="52"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="62" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7634,7 +7635,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="65" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7642,7 +7643,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="65" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7650,7 +7651,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="65" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7658,7 +7659,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="65" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7666,7 +7667,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="65" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -7674,15 +7675,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="65" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="64" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B10" s="65" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1351" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="592">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -1073,6 +1073,225 @@
   </si>
   <si>
     <t>Added from the 2026-09-14 board export, which raised this as a Feature. Built but had no tracker row and still has no user story beneath the feature.</t>
+  </si>
+  <si>
+    <t>Proposed Scope Tagging</t>
+  </si>
+  <si>
+    <t>Lets Open Box record, on either side of the taxonomy, where discovery has identified potential value add beyond what the client does today — a flag orthogonal to the existing coverage/scope tags, so the current-state tag is preserved.</t>
+  </si>
+  <si>
+    <t>src/components/proposalField.js, grid.js, businessView.js, genModal.js, docxExport.js; src/data/links.js</t>
+  </si>
+  <si>
+    <t>3350</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps Feature 3350. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Flag a value-stream process as Proposed Scope</t>
+  </si>
+  <si>
+    <t>A Propose control on each Value Streams card in Edit Mode; flagging it does not change the coverage tag; the card shows both tags together; saved with the version.</t>
+  </si>
+  <si>
+    <t>3352</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3352. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Flag an MRI PMX system process as Proposed Scope</t>
+  </si>
+  <si>
+    <t>A Propose control on each System view card in Edit Mode; the existing scope tag (Core/Custom/Out of scope) is retained; saved with the version.</t>
+  </si>
+  <si>
+    <t>3353</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3353. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Capture the value-add rationale for a proposal</t>
+  </si>
+  <si>
+    <t>Both edit modals expose a Proposed Scope checkbox and rationale field; the rationale appears in the detail panel and generated document; unticking clears it.</t>
+  </si>
+  <si>
+    <t>3354</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3354. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Distinguish a proposal from agreed client scope at a glance</t>
+  </si>
+  <si>
+    <t>Proposals use a distinct marker and dashed treatment, differing by shape as well as colour for colour-blind legibility; the panel states the item is a recommendation, not agreed scope.</t>
+  </si>
+  <si>
+    <t>3355</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3355. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Style the Proposed Scope tag to the Open Box brand palette</t>
+  </si>
+  <si>
+    <t>The ✦ PROPOSED chip and related badges use the Open Box brand colour (CSS var(--prop) / var(--prop-accent)).</t>
+  </si>
+  <si>
+    <t>3356</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3356. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Bulk-propose or clear proposals for a column</t>
+  </si>
+  <si>
+    <t>The Tag all menu in both views offers Propose all / Clear proposals, applied to every process and sub-process in the column, leaving coverage/scope tags untouched; one undo step.</t>
+  </si>
+  <si>
+    <t>3351</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3351. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Filter both views by Proposed Scope</t>
+  </si>
+  <si>
+    <t>A Proposed Scope toggle in both view filter bars narrows the existing coverage/scope selection rather than replacing it. Verified: toggling it hides non-proposed items and shows "No items match the selected filters" on empty columns.</t>
+  </si>
+  <si>
+    <t>3357</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3357. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Clear proposals when loading the Discovery Baseline</t>
+  </si>
+  <si>
+    <t>Loading the Discovery Baseline clears item proposals and proposed links on both sides, leaving the agreed link set intact (main.js clearProp / link filter on load).</t>
+  </si>
+  <si>
+    <t>3358</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3358. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Proposed Scope Propagation Across Links</t>
+  </si>
+  <si>
+    <t>Carries a proposal across existing business↔system links so it is only captured once; derivation is deliberately one-hop only to avoid cascading through the link graph.</t>
+  </si>
+  <si>
+    <t>3359</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps Feature 3359. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Imply a proposal across links in both directions</t>
+  </si>
+  <si>
+    <t>Flagging either side of a linked pair marks its linked counterparts as implied (derived); implied items render hollow/distinct from direct proposals, per links.js refreshDerivedProposals.</t>
+  </si>
+  <si>
+    <t>3360</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3360. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Prevent proposal propagation from cascading</t>
+  </si>
+  <si>
+    <t>Derivation reads only the directly-set `proposed` flag, never an implied one, so implication stops after one hop — confirmed in links.js comments and logic.</t>
+  </si>
+  <si>
+    <t>3361</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3361. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Propose a link that does not exist today</t>
+  </si>
+  <si>
+    <t>addLink() takes a `proposed` flag and toggleLinkProposed() exists; proposed links render dashed/distinct (map-chip-proposed, cell-flow-chip-proposed CSS).</t>
+  </si>
+  <si>
+    <t>3362</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3362. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Keep proposed links out of agreed-scope derivation</t>
+  </si>
+  <si>
+    <t>linkedSystemIds()/hasLink() filter out `proposed` links before deriving agreed scope (links.js), so a proposed link cannot lift an item out of auto out-of-scope.</t>
+  </si>
+  <si>
+    <t>3363</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3363. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Value-Add Proposals Document</t>
+  </si>
+  <si>
+    <t>Turns captured proposals into a client-facing section, excluded from generated documents unless explicitly included.</t>
+  </si>
+  <si>
+    <t>3364</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps Feature 3364. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Exclude proposals from generated documents by default</t>
+  </si>
+  <si>
+    <t>The export options include a Proposed Scope checkbox defaulting to unticked (genModal.js / docxExport.js inclProposed = false); no proposal content appears unless it is ticked.</t>
+  </si>
+  <si>
+    <t>3365</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3365. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Generate a Value-Add Proposals section</t>
+  </si>
+  <si>
+    <t>With Proposed Scope ticked, the document gains a Value-Add Proposals section grouped by side/module, opening with a recommendations-not-agreed-scope disclaimer (docxExport.js proposalsBlocks()).</t>
+  </si>
+  <si>
+    <t>3366</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3366. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+  </si>
+  <si>
+    <t>Nest linked counterparts under each proposal</t>
+  </si>
+  <si>
+    <t>Each proposal entry lists its linked counterparts as supporting detail, with proposed links marked as such in the list.</t>
+  </si>
+  <si>
+    <t>3367</t>
+  </si>
+  <si>
+    <t>Added 2026-10-01. DevOps User Story 3367. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
   </si>
   <si>
     <t>DevOps Backlog ⇄ App Feature Comparison</t>
@@ -1722,7 +1941,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1757,6 +1976,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF7F7F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -1860,7 +2084,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1937,6 +2161,9 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -1946,7 +2173,7 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1994,10 +2221,10 @@
     <xf numFmtId="0" fontId="22" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2006,10 +2233,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2021,7 +2248,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2033,13 +2260,13 @@
     <xf numFmtId="9" fontId="28" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
-    <xf numFmtId="9" fontId="27" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="27" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2396,7 +2623,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K108"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -5486,6 +5713,636 @@
       </c>
       <c r="K90" s="25" t="s">
         <v>352</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" s="26">
+        <v>87</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C91" s="26" t="s">
+        <v>353</v>
+      </c>
+      <c r="D91" s="26" t="s">
+        <v>354</v>
+      </c>
+      <c r="E91" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F91" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G91" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H91" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I91" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J91" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="K91" s="26" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" s="26">
+        <v>88</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C92" s="26" t="s">
+        <v>358</v>
+      </c>
+      <c r="D92" s="26" t="s">
+        <v>359</v>
+      </c>
+      <c r="E92" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F92" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G92" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I92" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J92" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="K92" s="26" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" s="26">
+        <v>89</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C93" s="26" t="s">
+        <v>362</v>
+      </c>
+      <c r="D93" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="E93" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F93" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G93" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H93" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I93" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J93" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="K93" s="26" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" s="26">
+        <v>90</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C94" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="D94" s="26" t="s">
+        <v>367</v>
+      </c>
+      <c r="E94" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F94" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G94" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H94" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I94" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J94" s="26" t="s">
+        <v>368</v>
+      </c>
+      <c r="K94" s="26" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" s="26">
+        <v>91</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C95" s="26" t="s">
+        <v>370</v>
+      </c>
+      <c r="D95" s="26" t="s">
+        <v>371</v>
+      </c>
+      <c r="E95" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F95" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G95" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H95" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I95" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J95" s="26" t="s">
+        <v>372</v>
+      </c>
+      <c r="K95" s="26" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" s="26">
+        <v>92</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C96" s="26" t="s">
+        <v>374</v>
+      </c>
+      <c r="D96" s="26" t="s">
+        <v>375</v>
+      </c>
+      <c r="E96" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G96" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H96" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I96" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J96" s="26" t="s">
+        <v>376</v>
+      </c>
+      <c r="K96" s="26" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="26">
+        <v>93</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C97" s="26" t="s">
+        <v>378</v>
+      </c>
+      <c r="D97" s="26" t="s">
+        <v>379</v>
+      </c>
+      <c r="E97" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G97" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H97" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I97" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J97" s="26" t="s">
+        <v>380</v>
+      </c>
+      <c r="K97" s="26" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="26">
+        <v>94</v>
+      </c>
+      <c r="B98" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C98" s="26" t="s">
+        <v>382</v>
+      </c>
+      <c r="D98" s="26" t="s">
+        <v>383</v>
+      </c>
+      <c r="E98" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F98" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G98" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I98" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J98" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="K98" s="26" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="26">
+        <v>95</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="C99" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="D99" s="26" t="s">
+        <v>387</v>
+      </c>
+      <c r="E99" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F99" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G99" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H99" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I99" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J99" s="26" t="s">
+        <v>388</v>
+      </c>
+      <c r="K99" s="26" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="26">
+        <v>96</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="D100" s="26" t="s">
+        <v>391</v>
+      </c>
+      <c r="E100" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G100" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H100" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I100" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J100" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="K100" s="26" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="26">
+        <v>97</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C101" s="26" t="s">
+        <v>394</v>
+      </c>
+      <c r="D101" s="26" t="s">
+        <v>395</v>
+      </c>
+      <c r="E101" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F101" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G101" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H101" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I101" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J101" s="26" t="s">
+        <v>396</v>
+      </c>
+      <c r="K101" s="26" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="26">
+        <v>98</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C102" s="26" t="s">
+        <v>398</v>
+      </c>
+      <c r="D102" s="26" t="s">
+        <v>399</v>
+      </c>
+      <c r="E102" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F102" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G102" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H102" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I102" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J102" s="26" t="s">
+        <v>400</v>
+      </c>
+      <c r="K102" s="26" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="26">
+        <v>99</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C103" s="26" t="s">
+        <v>402</v>
+      </c>
+      <c r="D103" s="26" t="s">
+        <v>403</v>
+      </c>
+      <c r="E103" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F103" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G103" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H103" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I103" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J103" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="K103" s="26" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="26">
+        <v>100</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C104" s="26" t="s">
+        <v>406</v>
+      </c>
+      <c r="D104" s="26" t="s">
+        <v>407</v>
+      </c>
+      <c r="E104" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F104" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G104" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H104" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I104" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J104" s="26" t="s">
+        <v>408</v>
+      </c>
+      <c r="K104" s="26" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="26">
+        <v>101</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C105" s="26" t="s">
+        <v>410</v>
+      </c>
+      <c r="D105" s="26" t="s">
+        <v>411</v>
+      </c>
+      <c r="E105" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F105" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G105" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H105" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I105" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J105" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="K105" s="26" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="26">
+        <v>102</v>
+      </c>
+      <c r="B106" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C106" s="26" t="s">
+        <v>414</v>
+      </c>
+      <c r="D106" s="26" t="s">
+        <v>415</v>
+      </c>
+      <c r="E106" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F106" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G106" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H106" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I106" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J106" s="26" t="s">
+        <v>416</v>
+      </c>
+      <c r="K106" s="26" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="26">
+        <v>103</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C107" s="26" t="s">
+        <v>418</v>
+      </c>
+      <c r="D107" s="26" t="s">
+        <v>419</v>
+      </c>
+      <c r="E107" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F107" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G107" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H107" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I107" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J107" s="26" t="s">
+        <v>420</v>
+      </c>
+      <c r="K107" s="26" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="26">
+        <v>104</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="C108" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="D108" s="26" t="s">
+        <v>423</v>
+      </c>
+      <c r="E108" s="26" t="s">
+        <v>355</v>
+      </c>
+      <c r="F108" s="26" t="s">
+        <v>268</v>
+      </c>
+      <c r="G108" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="H108" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="I108" s="26" t="s">
+        <v>309</v>
+      </c>
+      <c r="J108" s="26" t="s">
+        <v>424</v>
+      </c>
+      <c r="K108" s="26" t="s">
+        <v>425</v>
       </c>
     </row>
   </sheetData>
@@ -5541,1716 +6398,1716 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
-        <v>353</v>
-      </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
+      <c r="A1" s="27" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
-        <v>354</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
+      <c r="A2" s="28" t="s">
+        <v>427</v>
+      </c>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="28" t="s">
-        <v>355</v>
-      </c>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
+      <c r="A3" s="29" t="s">
+        <v>428</v>
+      </c>
+      <c r="B3" s="29"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="29"/>
+      <c r="I3" s="29"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
-        <v>356</v>
-      </c>
-      <c r="B4" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="C4" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>363</v>
-      </c>
-      <c r="I4" s="29" t="s">
+      <c r="A4" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>432</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="F4" s="30" t="s">
+        <v>434</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="H4" s="30" t="s">
+        <v>436</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="31" t="s">
-        <v>364</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="E5" s="32">
+      <c r="B5" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="C5" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="E5" s="33">
         <v>3</v>
       </c>
-      <c r="F5" s="31" t="s">
+      <c r="F5" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H5" s="31" t="s">
+      <c r="G5" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H5" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="35" t="s">
+      <c r="A6" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="36" t="s">
-        <v>368</v>
-      </c>
-      <c r="C6" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D6" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E6" s="37">
+      <c r="B6" s="37" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E6" s="38">
         <v>2</v>
       </c>
-      <c r="F6" s="36" t="s">
-        <v>370</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H6" s="36" t="s">
+      <c r="F6" s="37" t="s">
+        <v>443</v>
+      </c>
+      <c r="G6" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H6" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>372</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="E7" s="32">
+      <c r="A7" s="31" t="s">
+        <v>444</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="C7" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="E7" s="33">
         <v>2</v>
       </c>
-      <c r="F7" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="G7" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H7" s="31" t="s">
+      <c r="F7" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="G7" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H7" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="36" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="36" t="s">
-        <v>374</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D8" s="38" t="s">
-        <v>376</v>
-      </c>
-      <c r="E8" s="37">
+      <c r="B8" s="37" t="s">
+        <v>447</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>449</v>
+      </c>
+      <c r="E8" s="38">
         <v>3</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H8" s="36" t="s">
+      <c r="G8" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H8" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="C9" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E9" s="32">
+      <c r="B9" s="32" t="s">
+        <v>450</v>
+      </c>
+      <c r="C9" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E9" s="33">
         <v>3</v>
       </c>
-      <c r="F9" s="31" t="s">
-        <v>378</v>
-      </c>
-      <c r="G9" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H9" s="31" t="s">
+      <c r="F9" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="G9" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H9" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="35" t="s">
+      <c r="A10" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="36" t="s">
-        <v>379</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D10" s="38" t="s">
-        <v>380</v>
-      </c>
-      <c r="E10" s="37">
+      <c r="B10" s="37" t="s">
+        <v>452</v>
+      </c>
+      <c r="C10" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>453</v>
+      </c>
+      <c r="E10" s="38">
         <v>2</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="37" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H10" s="36" t="s">
+      <c r="G10" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H10" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+      <c r="A11" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="31" t="s">
-        <v>381</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>380</v>
-      </c>
-      <c r="E11" s="32">
+      <c r="B11" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="C11" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="E11" s="33">
         <v>3</v>
       </c>
-      <c r="F11" s="31" t="s">
+      <c r="F11" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H11" s="31" t="s">
+      <c r="G11" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H11" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="B12" s="36" t="s">
-        <v>382</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>366</v>
-      </c>
-      <c r="E12" s="37">
+      <c r="B12" s="37" t="s">
+        <v>455</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>439</v>
+      </c>
+      <c r="E12" s="38">
         <v>3</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="37" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H12" s="36" t="s">
+      <c r="G12" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H12" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+      <c r="A13" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="31" t="s">
-        <v>383</v>
-      </c>
-      <c r="C13" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="E13" s="32">
+      <c r="B13" s="32" t="s">
+        <v>456</v>
+      </c>
+      <c r="C13" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="E13" s="33">
         <v>2</v>
       </c>
-      <c r="F13" s="31" t="s">
+      <c r="F13" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H13" s="31" t="s">
+      <c r="G13" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H13" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="35" t="s">
+      <c r="A14" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="B14" s="36" t="s">
-        <v>385</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D14" s="38" t="s">
-        <v>366</v>
-      </c>
-      <c r="E14" s="37">
+      <c r="B14" s="37" t="s">
+        <v>458</v>
+      </c>
+      <c r="C14" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>439</v>
+      </c>
+      <c r="E14" s="38">
         <v>2</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="37" t="s">
         <v>82</v>
       </c>
-      <c r="G14" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H14" s="36" t="s">
+      <c r="G14" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H14" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+      <c r="A15" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="31" t="s">
-        <v>386</v>
-      </c>
-      <c r="C15" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>366</v>
-      </c>
-      <c r="E15" s="32">
+      <c r="B15" s="32" t="s">
+        <v>459</v>
+      </c>
+      <c r="C15" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="E15" s="33">
         <v>2</v>
       </c>
-      <c r="F15" s="31" t="s">
+      <c r="F15" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="G15" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H15" s="31" t="s">
+      <c r="G15" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H15" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="35" t="s">
+      <c r="A16" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="B16" s="36" t="s">
-        <v>387</v>
-      </c>
-      <c r="C16" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D16" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E16" s="37">
+      <c r="B16" s="37" t="s">
+        <v>460</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="D16" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E16" s="38">
         <v>3</v>
       </c>
-      <c r="F16" s="36" t="s">
-        <v>388</v>
-      </c>
-      <c r="G16" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H16" s="36" t="s">
+      <c r="F16" s="37" t="s">
+        <v>461</v>
+      </c>
+      <c r="G16" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H16" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
+      <c r="A17" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="31" t="s">
-        <v>389</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E17" s="32">
+      <c r="B17" s="32" t="s">
+        <v>462</v>
+      </c>
+      <c r="C17" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E17" s="33">
         <v>3</v>
       </c>
-      <c r="F17" s="31" t="s">
-        <v>390</v>
-      </c>
-      <c r="G17" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H17" s="31" t="s">
+      <c r="F17" s="32" t="s">
+        <v>463</v>
+      </c>
+      <c r="G17" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H17" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="35" t="s">
+      <c r="A18" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="B18" s="36" t="s">
-        <v>391</v>
-      </c>
-      <c r="C18" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>392</v>
-      </c>
-      <c r="E18" s="37">
+      <c r="B18" s="37" t="s">
+        <v>464</v>
+      </c>
+      <c r="C18" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>465</v>
+      </c>
+      <c r="E18" s="38">
         <v>3</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F18" s="37" t="s">
         <v>175</v>
       </c>
-      <c r="G18" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H18" s="36" t="s">
-        <v>393</v>
+      <c r="G18" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H18" s="37" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
-        <v>394</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>395</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>392</v>
-      </c>
-      <c r="E19" s="32">
+      <c r="A19" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>468</v>
+      </c>
+      <c r="C19" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D19" s="41" t="s">
+        <v>465</v>
+      </c>
+      <c r="E19" s="33">
         <v>3</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="G19" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H19" s="31" t="s">
-        <v>393</v>
+      <c r="G19" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H19" s="32" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="35" t="s">
+      <c r="A20" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="36" t="s">
-        <v>396</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>392</v>
-      </c>
-      <c r="E20" s="37">
+      <c r="B20" s="37" t="s">
+        <v>469</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="D20" s="42" t="s">
+        <v>465</v>
+      </c>
+      <c r="E20" s="38">
         <v>5</v>
       </c>
-      <c r="F20" s="36" t="s">
-        <v>397</v>
-      </c>
-      <c r="G20" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H20" s="36" t="s">
-        <v>393</v>
+      <c r="F20" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="G20" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
-        <v>398</v>
-      </c>
-      <c r="B21" s="31" t="s">
-        <v>399</v>
-      </c>
-      <c r="C21" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D21" s="42" t="s">
-        <v>392</v>
-      </c>
-      <c r="E21" s="32">
+      <c r="A21" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>472</v>
+      </c>
+      <c r="C21" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>465</v>
+      </c>
+      <c r="E21" s="33">
         <v>3</v>
       </c>
-      <c r="F21" s="31" t="s">
-        <v>400</v>
-      </c>
-      <c r="G21" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H21" s="31" t="s">
-        <v>393</v>
+      <c r="F21" s="32" t="s">
+        <v>473</v>
+      </c>
+      <c r="G21" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H21" s="32" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
+      <c r="A22" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="B22" s="36" t="s">
-        <v>401</v>
-      </c>
-      <c r="C22" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D22" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E22" s="37">
+      <c r="B22" s="37" t="s">
+        <v>474</v>
+      </c>
+      <c r="C22" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D22" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E22" s="38">
         <v>5</v>
       </c>
-      <c r="F22" s="36" t="s">
-        <v>402</v>
-      </c>
-      <c r="G22" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H22" s="36" t="s">
+      <c r="F22" s="37" t="s">
+        <v>475</v>
+      </c>
+      <c r="G22" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H22" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
+      <c r="A23" s="31" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>403</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>392</v>
-      </c>
-      <c r="E23" s="32">
+      <c r="B23" s="32" t="s">
+        <v>476</v>
+      </c>
+      <c r="C23" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="E23" s="33">
         <v>3</v>
       </c>
-      <c r="F23" s="31" t="s">
+      <c r="F23" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="G23" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H23" s="31" t="s">
+      <c r="G23" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H23" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
+      <c r="A24" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="B24" s="36" t="s">
-        <v>404</v>
-      </c>
-      <c r="C24" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E24" s="37">
+      <c r="B24" s="37" t="s">
+        <v>477</v>
+      </c>
+      <c r="C24" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D24" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E24" s="38">
         <v>3</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="37" t="s">
         <v>105</v>
       </c>
-      <c r="G24" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H24" s="36" t="s">
+      <c r="G24" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H24" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
-        <v>405</v>
-      </c>
-      <c r="B25" s="31" t="s">
-        <v>406</v>
-      </c>
-      <c r="C25" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E25" s="32">
+      <c r="A25" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>479</v>
+      </c>
+      <c r="C25" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E25" s="33">
         <v>3</v>
       </c>
-      <c r="F25" s="31" t="s">
+      <c r="F25" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="G25" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H25" s="31" t="s">
+      <c r="G25" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H25" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="35" t="s">
-        <v>407</v>
-      </c>
-      <c r="B26" s="36" t="s">
-        <v>408</v>
-      </c>
-      <c r="C26" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D26" s="38" t="s">
-        <v>409</v>
-      </c>
-      <c r="E26" s="37">
+      <c r="A26" s="36" t="s">
+        <v>480</v>
+      </c>
+      <c r="B26" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="C26" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>482</v>
+      </c>
+      <c r="E26" s="38">
         <v>2</v>
       </c>
-      <c r="F26" s="36" t="s">
-        <v>410</v>
-      </c>
-      <c r="G26" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>411</v>
+      <c r="F26" s="37" t="s">
+        <v>483</v>
+      </c>
+      <c r="G26" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H26" s="37" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="B27" s="31" t="s">
-        <v>412</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E27" s="32">
+      <c r="B27" s="32" t="s">
+        <v>485</v>
+      </c>
+      <c r="C27" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E27" s="33">
         <v>3</v>
       </c>
-      <c r="F27" s="31" t="s">
+      <c r="F27" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="G27" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H27" s="31" t="s">
+      <c r="G27" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H27" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="B28" s="36" t="s">
-        <v>413</v>
-      </c>
-      <c r="C28" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E28" s="37">
+      <c r="B28" s="37" t="s">
+        <v>486</v>
+      </c>
+      <c r="C28" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E28" s="38">
         <v>3</v>
       </c>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="37" t="s">
         <v>90</v>
       </c>
-      <c r="G28" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H28" s="36" t="s">
+      <c r="G28" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H28" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
-        <v>414</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>415</v>
-      </c>
-      <c r="C29" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E29" s="32">
+      <c r="A29" s="31" t="s">
+        <v>487</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>488</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E29" s="33">
         <v>3</v>
       </c>
-      <c r="F29" s="31" t="s">
-        <v>416</v>
-      </c>
-      <c r="G29" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H29" s="31" t="s">
+      <c r="F29" s="32" t="s">
+        <v>489</v>
+      </c>
+      <c r="G29" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H29" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="35" t="s">
+      <c r="A30" s="36" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="36" t="s">
-        <v>417</v>
-      </c>
-      <c r="C30" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>366</v>
-      </c>
-      <c r="E30" s="37">
+      <c r="B30" s="37" t="s">
+        <v>490</v>
+      </c>
+      <c r="C30" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D30" s="39" t="s">
+        <v>439</v>
+      </c>
+      <c r="E30" s="38">
         <v>3</v>
       </c>
-      <c r="F30" s="36" t="s">
+      <c r="F30" s="37" t="s">
         <v>142</v>
       </c>
-      <c r="G30" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H30" s="36" t="s">
+      <c r="G30" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H30" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="B31" s="31" t="s">
-        <v>418</v>
-      </c>
-      <c r="C31" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D31" s="33" t="s">
-        <v>409</v>
-      </c>
-      <c r="E31" s="32">
+      <c r="B31" s="32" t="s">
+        <v>491</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="E31" s="33">
         <v>5</v>
       </c>
-      <c r="F31" s="31" t="s">
+      <c r="F31" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="G31" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H31" s="31" t="s">
-        <v>419</v>
+      <c r="G31" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H31" s="32" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
+      <c r="A32" s="36" t="s">
         <v>149</v>
       </c>
-      <c r="B32" s="36" t="s">
-        <v>420</v>
-      </c>
-      <c r="C32" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E32" s="37">
+      <c r="B32" s="37" t="s">
+        <v>493</v>
+      </c>
+      <c r="C32" s="38" t="s">
+        <v>457</v>
+      </c>
+      <c r="D32" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E32" s="38">
         <v>3</v>
       </c>
-      <c r="F32" s="36" t="s">
+      <c r="F32" s="37" t="s">
         <v>146</v>
       </c>
-      <c r="G32" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H32" s="36" t="s">
+      <c r="G32" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H32" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="B33" s="31" t="s">
-        <v>421</v>
-      </c>
-      <c r="C33" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E33" s="32">
+      <c r="B33" s="32" t="s">
+        <v>494</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E33" s="33">
         <v>3</v>
       </c>
-      <c r="F33" s="31" t="s">
+      <c r="F33" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="G33" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H33" s="31" t="s">
+      <c r="G33" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H33" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
-        <v>422</v>
-      </c>
-      <c r="B34" s="36" t="s">
-        <v>423</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E34" s="37">
+      <c r="A34" s="36" t="s">
+        <v>495</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>496</v>
+      </c>
+      <c r="C34" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="D34" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E34" s="38">
         <v>5</v>
       </c>
-      <c r="F34" s="36" t="s">
-        <v>424</v>
-      </c>
-      <c r="G34" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H34" s="36" t="s">
+      <c r="F34" s="37" t="s">
+        <v>497</v>
+      </c>
+      <c r="G34" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H34" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="30" t="s">
-        <v>425</v>
-      </c>
-      <c r="B35" s="31" t="s">
-        <v>426</v>
-      </c>
-      <c r="C35" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D35" s="33" t="s">
-        <v>380</v>
-      </c>
-      <c r="E35" s="32">
+      <c r="A35" s="31" t="s">
+        <v>498</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>499</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="E35" s="33">
         <v>5</v>
       </c>
-      <c r="F35" s="31" t="s">
-        <v>427</v>
-      </c>
-      <c r="G35" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H35" s="31" t="s">
+      <c r="F35" s="32" t="s">
+        <v>500</v>
+      </c>
+      <c r="G35" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H35" s="32" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="35" t="s">
+      <c r="A36" s="36" t="s">
         <v>262</v>
       </c>
-      <c r="B36" s="36" t="s">
-        <v>428</v>
-      </c>
-      <c r="C36" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E36" s="37">
+      <c r="B36" s="37" t="s">
+        <v>501</v>
+      </c>
+      <c r="C36" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D36" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E36" s="38">
         <v>3</v>
       </c>
-      <c r="F36" s="36" t="s">
+      <c r="F36" s="37" t="s">
         <v>259</v>
       </c>
-      <c r="G36" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H36" s="36" t="s">
+      <c r="G36" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H36" s="37" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="30" t="s">
+      <c r="A37" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="32" t="s">
+        <v>502</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>438</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E37" s="33">
+        <v>5</v>
+      </c>
+      <c r="F37" s="32" t="s">
+        <v>503</v>
+      </c>
+      <c r="G37" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H37" s="32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B38" s="37" t="s">
+        <v>504</v>
+      </c>
+      <c r="C38" s="38" t="s">
+        <v>438</v>
+      </c>
+      <c r="D38" s="39" t="s">
+        <v>465</v>
+      </c>
+      <c r="E38" s="38">
+        <v>3</v>
+      </c>
+      <c r="F38" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="G38" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H38" s="37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="31" t="s">
+        <v>211</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="C39" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E39" s="33">
+        <v>3</v>
+      </c>
+      <c r="F39" s="32" t="s">
+        <v>208</v>
+      </c>
+      <c r="G39" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H39" s="32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="37" t="s">
+        <v>506</v>
+      </c>
+      <c r="C40" s="38" t="s">
+        <v>457</v>
+      </c>
+      <c r="D40" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E40" s="38">
+        <v>2</v>
+      </c>
+      <c r="F40" s="37" t="s">
+        <v>507</v>
+      </c>
+      <c r="G40" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H40" s="37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E41" s="33">
+        <v>3</v>
+      </c>
+      <c r="F41" s="32" t="s">
+        <v>509</v>
+      </c>
+      <c r="G41" s="35" t="s">
+        <v>510</v>
+      </c>
+      <c r="H41" s="32" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="B42" s="37" t="s">
+        <v>512</v>
+      </c>
+      <c r="C42" s="38" t="s">
+        <v>448</v>
+      </c>
+      <c r="D42" s="39" t="s">
+        <v>442</v>
+      </c>
+      <c r="E42" s="38">
+        <v>5</v>
+      </c>
+      <c r="F42" s="37" t="s">
+        <v>513</v>
+      </c>
+      <c r="G42" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H42" s="37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>514</v>
+      </c>
+      <c r="C43" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E43" s="33">
+        <v>3</v>
+      </c>
+      <c r="F43" s="32" t="s">
+        <v>239</v>
+      </c>
+      <c r="G43" s="35" t="s">
+        <v>440</v>
+      </c>
+      <c r="H43" s="32" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="44" t="s">
+        <v>515</v>
+      </c>
+      <c r="B45" s="44"/>
+      <c r="C45" s="44"/>
+      <c r="D45" s="44"/>
+      <c r="E45" s="44"/>
+      <c r="F45" s="44"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="44"/>
+      <c r="I45" s="44"/>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="30" t="s">
         <v>429</v>
       </c>
-      <c r="C37" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E37" s="32">
+      <c r="B46" s="30" t="s">
+        <v>430</v>
+      </c>
+      <c r="C46" s="30" t="s">
+        <v>431</v>
+      </c>
+      <c r="D46" s="30" t="s">
+        <v>432</v>
+      </c>
+      <c r="E46" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="F46" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="G46" s="30" t="s">
+        <v>516</v>
+      </c>
+      <c r="H46" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="31" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="C47" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>465</v>
+      </c>
+      <c r="E47" s="33">
+        <v>2</v>
+      </c>
+      <c r="F47" s="45" t="s">
+        <v>440</v>
+      </c>
+      <c r="G47" s="32" t="s">
+        <v>517</v>
+      </c>
+      <c r="H47" s="32"/>
+      <c r="I47" s="32"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="31" t="s">
+        <v>275</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>518</v>
+      </c>
+      <c r="C48" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E48" s="33">
+        <v>2</v>
+      </c>
+      <c r="F48" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="G48" s="32" t="s">
+        <v>520</v>
+      </c>
+      <c r="H48" s="32"/>
+      <c r="I48" s="32"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="31" t="s">
+        <v>282</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="C49" s="33" t="s">
+        <v>521</v>
+      </c>
+      <c r="D49" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E49" s="33">
+        <v>8</v>
+      </c>
+      <c r="F49" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="G49" s="32" t="s">
+        <v>522</v>
+      </c>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>523</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>521</v>
+      </c>
+      <c r="D50" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E50" s="33">
         <v>5</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F50" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="G50" s="32" t="s">
+        <v>524</v>
+      </c>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+    </row>
+    <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="47" t="s">
+        <v>525</v>
+      </c>
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
+      <c r="G52" s="47"/>
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" s="30" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" s="30" t="s">
+        <v>526</v>
+      </c>
+      <c r="E53" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="F53" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="G53" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H53" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="48" t="s">
+        <v>23</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>527</v>
+      </c>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="D55" s="32" t="s">
+        <v>528</v>
+      </c>
+      <c r="E55" s="32"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="32"/>
+      <c r="H55" s="32"/>
+      <c r="I55" s="32"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="48" t="s">
+        <v>138</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C56" s="49" t="s">
+        <v>140</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>529</v>
+      </c>
+      <c r="E56" s="32"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="32"/>
+      <c r="H56" s="32"/>
+      <c r="I56" s="32"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="48" t="s">
+        <v>195</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="49" t="s">
+        <v>197</v>
+      </c>
+      <c r="D57" s="32" t="s">
+        <v>530</v>
+      </c>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="48" t="s">
+        <v>204</v>
+      </c>
+      <c r="B58" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="C58" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="D58" s="32" t="s">
+        <v>531</v>
+      </c>
+      <c r="E58" s="32"/>
+      <c r="F58" s="32"/>
+      <c r="G58" s="32"/>
+      <c r="H58" s="32"/>
+      <c r="I58" s="32"/>
+    </row>
+    <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="50" t="s">
+        <v>532</v>
+      </c>
+      <c r="B60" s="50"/>
+      <c r="C60" s="50"/>
+      <c r="D60" s="50"/>
+      <c r="E60" s="50"/>
+      <c r="F60" s="50"/>
+      <c r="G60" s="50"/>
+      <c r="H60" s="50"/>
+      <c r="I60" s="50"/>
+    </row>
+    <row r="61" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B61" s="30" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" s="30" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>533</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="30" t="s">
+        <v>534</v>
+      </c>
+      <c r="G61" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="H61" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="30" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="48" t="s">
+        <v>288</v>
+      </c>
+      <c r="B62" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C62" s="32" t="s">
+        <v>535</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>536</v>
+      </c>
+      <c r="E62" s="51" t="s">
+        <v>465</v>
+      </c>
+      <c r="F62" s="52" t="s">
+        <v>537</v>
+      </c>
+      <c r="G62" s="52"/>
+      <c r="H62" s="52"/>
+      <c r="I62" s="52"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="48" t="s">
+        <v>293</v>
+      </c>
+      <c r="B63" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="32" t="s">
+        <v>538</v>
+      </c>
+      <c r="D63" s="32" t="s">
+        <v>539</v>
+      </c>
+      <c r="E63" s="51" t="s">
+        <v>482</v>
+      </c>
+      <c r="F63" s="52" t="s">
+        <v>540</v>
+      </c>
+      <c r="G63" s="52"/>
+      <c r="H63" s="52"/>
+      <c r="I63" s="52"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="48" t="s">
+        <v>296</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="32" t="s">
+        <v>541</v>
+      </c>
+      <c r="D64" s="32" t="s">
+        <v>542</v>
+      </c>
+      <c r="E64" s="51" t="s">
+        <v>482</v>
+      </c>
+      <c r="F64" s="52" t="s">
+        <v>543</v>
+      </c>
+      <c r="G64" s="52"/>
+      <c r="H64" s="52"/>
+      <c r="I64" s="52"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="48" t="s">
+        <v>300</v>
+      </c>
+      <c r="B65" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="C65" s="32" t="s">
+        <v>544</v>
+      </c>
+      <c r="D65" s="32" t="s">
+        <v>545</v>
+      </c>
+      <c r="E65" s="51" t="s">
+        <v>482</v>
+      </c>
+      <c r="F65" s="52" t="s">
+        <v>546</v>
+      </c>
+      <c r="G65" s="52"/>
+      <c r="H65" s="52"/>
+      <c r="I65" s="52"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="48" t="s">
+        <v>303</v>
+      </c>
+      <c r="B66" s="32" t="s">
+        <v>186</v>
+      </c>
+      <c r="C66" s="32" t="s">
+        <v>547</v>
+      </c>
+      <c r="D66" s="32" t="s">
+        <v>548</v>
+      </c>
+      <c r="E66" s="51" t="s">
+        <v>482</v>
+      </c>
+      <c r="F66" s="52" t="s">
+        <v>549</v>
+      </c>
+      <c r="G66" s="52"/>
+      <c r="H66" s="52"/>
+      <c r="I66" s="52"/>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="44" t="s">
+        <v>550</v>
+      </c>
+      <c r="B68" s="44"/>
+      <c r="C68" s="44"/>
+      <c r="D68" s="44"/>
+      <c r="E68" s="44"/>
+      <c r="F68" s="44"/>
+      <c r="G68" s="44"/>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="B69" s="30" t="s">
         <v>430</v>
       </c>
-      <c r="G37" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H37" s="31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="B38" s="36" t="s">
+      <c r="C69" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="C38" s="37" t="s">
-        <v>365</v>
-      </c>
-      <c r="D38" s="38" t="s">
-        <v>392</v>
-      </c>
-      <c r="E38" s="37">
+      <c r="D69" s="30" t="s">
+        <v>432</v>
+      </c>
+      <c r="E69" s="30" t="s">
+        <v>433</v>
+      </c>
+      <c r="F69" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="G69" s="30" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" s="31" t="s">
+        <v>551</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C70" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D70" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E70" s="33">
+        <v>8</v>
+      </c>
+      <c r="F70" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="G70" s="32" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" s="31" t="s">
+        <v>553</v>
+      </c>
+      <c r="B71" s="32" t="s">
+        <v>311</v>
+      </c>
+      <c r="C71" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D71" s="32" t="s">
+        <v>554</v>
+      </c>
+      <c r="E71" s="33">
+        <v>13</v>
+      </c>
+      <c r="F71" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="G71" s="32" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="31" t="s">
+        <v>556</v>
+      </c>
+      <c r="B72" s="32" t="s">
+        <v>316</v>
+      </c>
+      <c r="C72" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D72" s="32" t="s">
+        <v>465</v>
+      </c>
+      <c r="E72" s="33">
         <v>3</v>
       </c>
-      <c r="F38" s="36" t="s">
-        <v>191</v>
-      </c>
-      <c r="G38" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H38" s="36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>432</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E39" s="32">
-        <v>3</v>
-      </c>
-      <c r="F39" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="G39" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H39" s="31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="35" t="s">
-        <v>215</v>
-      </c>
-      <c r="B40" s="36" t="s">
-        <v>433</v>
-      </c>
-      <c r="C40" s="37" t="s">
-        <v>384</v>
-      </c>
-      <c r="D40" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E40" s="37">
-        <v>2</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>434</v>
-      </c>
-      <c r="G40" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H40" s="36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="30" t="s">
-        <v>223</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>435</v>
-      </c>
-      <c r="C41" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E41" s="32">
-        <v>3</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>436</v>
-      </c>
-      <c r="G41" s="34" t="s">
-        <v>437</v>
-      </c>
-      <c r="H41" s="31" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="B42" s="36" t="s">
-        <v>439</v>
-      </c>
-      <c r="C42" s="37" t="s">
-        <v>375</v>
-      </c>
-      <c r="D42" s="38" t="s">
-        <v>369</v>
-      </c>
-      <c r="E42" s="37">
-        <v>5</v>
-      </c>
-      <c r="F42" s="36" t="s">
+      <c r="F72" s="45" t="s">
         <v>440</v>
       </c>
-      <c r="G42" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H42" s="36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="30" t="s">
-        <v>242</v>
-      </c>
-      <c r="B43" s="31" t="s">
-        <v>441</v>
-      </c>
-      <c r="C43" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>369</v>
-      </c>
-      <c r="E43" s="32">
-        <v>3</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="G43" s="34" t="s">
-        <v>367</v>
-      </c>
-      <c r="H43" s="31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="43" t="s">
-        <v>442</v>
-      </c>
-      <c r="B45" s="43"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="43"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="43"/>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-    </row>
-    <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="29" t="s">
-        <v>356</v>
-      </c>
-      <c r="B46" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="C46" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="D46" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="E46" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="F46" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="G46" s="29" t="s">
-        <v>443</v>
-      </c>
-      <c r="H46" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I46" s="29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
-        <v>269</v>
-      </c>
-      <c r="B47" s="31" t="s">
-        <v>265</v>
-      </c>
-      <c r="C47" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="E47" s="32">
-        <v>2</v>
-      </c>
-      <c r="F47" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="G47" s="31" t="s">
-        <v>444</v>
-      </c>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="30" t="s">
-        <v>275</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>445</v>
-      </c>
-      <c r="C48" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D48" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E48" s="32">
-        <v>2</v>
-      </c>
-      <c r="F48" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="G48" s="31" t="s">
-        <v>447</v>
-      </c>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="30" t="s">
-        <v>282</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>278</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="D49" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E49" s="32">
+      <c r="G72" s="32" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" s="31" t="s">
+        <v>558</v>
+      </c>
+      <c r="B73" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="C73" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D73" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E73" s="33">
         <v>8</v>
       </c>
-      <c r="F49" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="G49" s="31" t="s">
-        <v>449</v>
-      </c>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="30" t="s">
-        <v>286</v>
-      </c>
-      <c r="B50" s="31" t="s">
-        <v>450</v>
-      </c>
-      <c r="C50" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="D50" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E50" s="32">
-        <v>5</v>
-      </c>
-      <c r="F50" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="G50" s="31" t="s">
-        <v>451</v>
-      </c>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-    </row>
-    <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="46" t="s">
-        <v>452</v>
-      </c>
-      <c r="B52" s="46"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="46"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="46"/>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-    </row>
-    <row r="53" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B53" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C53" s="29" t="s">
-        <v>6</v>
-      </c>
-      <c r="D53" s="29" t="s">
-        <v>453</v>
-      </c>
-      <c r="E53" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="F53" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="G53" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H53" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I53" s="29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B54" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C54" s="48" t="s">
-        <v>25</v>
-      </c>
-      <c r="D54" s="31" t="s">
-        <v>454</v>
-      </c>
-      <c r="E54" s="31"/>
-      <c r="F54" s="31"/>
-      <c r="G54" s="31"/>
-      <c r="H54" s="31"/>
-      <c r="I54" s="31"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="47" t="s">
-        <v>45</v>
-      </c>
-      <c r="B55" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="C55" s="48" t="s">
-        <v>47</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>455</v>
-      </c>
-      <c r="E55" s="31"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="31"/>
-      <c r="H55" s="31"/>
-      <c r="I55" s="31"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="47" t="s">
-        <v>138</v>
-      </c>
-      <c r="B56" s="31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C56" s="48" t="s">
-        <v>140</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>456</v>
-      </c>
-      <c r="E56" s="31"/>
-      <c r="F56" s="31"/>
-      <c r="G56" s="31"/>
-      <c r="H56" s="31"/>
-      <c r="I56" s="31"/>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="47" t="s">
-        <v>195</v>
-      </c>
-      <c r="B57" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C57" s="48" t="s">
-        <v>197</v>
-      </c>
-      <c r="D57" s="31" t="s">
+      <c r="F73" s="46" t="s">
+        <v>510</v>
+      </c>
+      <c r="G73" s="32" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" s="31" t="s">
+        <v>560</v>
+      </c>
+      <c r="B74" s="32" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="33" t="s">
         <v>457</v>
       </c>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="47" t="s">
-        <v>204</v>
-      </c>
-      <c r="B58" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C58" s="48" t="s">
-        <v>206</v>
-      </c>
-      <c r="D58" s="31" t="s">
-        <v>458</v>
-      </c>
-      <c r="E58" s="31"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="31"/>
-      <c r="H58" s="31"/>
-      <c r="I58" s="31"/>
-    </row>
-    <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="49" t="s">
-        <v>459</v>
-      </c>
-      <c r="B60" s="49"/>
-      <c r="C60" s="49"/>
-      <c r="D60" s="49"/>
-      <c r="E60" s="49"/>
-      <c r="F60" s="49"/>
-      <c r="G60" s="49"/>
-      <c r="H60" s="49"/>
-      <c r="I60" s="49"/>
-    </row>
-    <row r="61" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="B61" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="C61" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>460</v>
-      </c>
-      <c r="E61" s="29" t="s">
+      <c r="D74" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E74" s="33">
         <v>8</v>
       </c>
-      <c r="F61" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="G61" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="H61" s="29" t="s">
-        <v>22</v>
-      </c>
-      <c r="I61" s="29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="47" t="s">
-        <v>288</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62" s="31" t="s">
-        <v>462</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>463</v>
-      </c>
-      <c r="E62" s="50" t="s">
-        <v>392</v>
-      </c>
-      <c r="F62" s="51" t="s">
-        <v>464</v>
-      </c>
-      <c r="G62" s="51"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="47" t="s">
-        <v>293</v>
-      </c>
-      <c r="B63" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="C63" s="31" t="s">
-        <v>465</v>
-      </c>
-      <c r="D63" s="31" t="s">
-        <v>466</v>
-      </c>
-      <c r="E63" s="50" t="s">
-        <v>409</v>
-      </c>
-      <c r="F63" s="51" t="s">
-        <v>467</v>
-      </c>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="47" t="s">
-        <v>296</v>
-      </c>
-      <c r="B64" s="31" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="31" t="s">
-        <v>468</v>
-      </c>
-      <c r="D64" s="31" t="s">
-        <v>469</v>
-      </c>
-      <c r="E64" s="50" t="s">
-        <v>409</v>
-      </c>
-      <c r="F64" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="G64" s="51"/>
-      <c r="H64" s="51"/>
-      <c r="I64" s="51"/>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="47" t="s">
-        <v>300</v>
-      </c>
-      <c r="B65" s="31" t="s">
-        <v>299</v>
-      </c>
-      <c r="C65" s="31" t="s">
-        <v>471</v>
-      </c>
-      <c r="D65" s="31" t="s">
-        <v>472</v>
-      </c>
-      <c r="E65" s="50" t="s">
-        <v>409</v>
-      </c>
-      <c r="F65" s="51" t="s">
-        <v>473</v>
-      </c>
-      <c r="G65" s="51"/>
-      <c r="H65" s="51"/>
-      <c r="I65" s="51"/>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="47" t="s">
-        <v>303</v>
-      </c>
-      <c r="B66" s="31" t="s">
-        <v>186</v>
-      </c>
-      <c r="C66" s="31" t="s">
-        <v>474</v>
-      </c>
-      <c r="D66" s="31" t="s">
-        <v>475</v>
-      </c>
-      <c r="E66" s="50" t="s">
-        <v>409</v>
-      </c>
-      <c r="F66" s="51" t="s">
-        <v>476</v>
-      </c>
-      <c r="G66" s="51"/>
-      <c r="H66" s="51"/>
-      <c r="I66" s="51"/>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A68" s="43" t="s">
-        <v>477</v>
-      </c>
-      <c r="B68" s="43"/>
-      <c r="C68" s="43"/>
-      <c r="D68" s="43"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="43"/>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A69" s="29" t="s">
-        <v>356</v>
-      </c>
-      <c r="B69" s="29" t="s">
-        <v>357</v>
-      </c>
-      <c r="C69" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="D69" s="29" t="s">
-        <v>359</v>
-      </c>
-      <c r="E69" s="29" t="s">
-        <v>360</v>
-      </c>
-      <c r="F69" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="G69" s="29" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A70" s="30" t="s">
-        <v>478</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>306</v>
-      </c>
-      <c r="C70" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D70" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E70" s="32">
+      <c r="F74" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="G74" s="32" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" s="31" t="s">
+        <v>562</v>
+      </c>
+      <c r="B75" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="C75" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D75" s="32" t="s">
+        <v>482</v>
+      </c>
+      <c r="E75" s="33">
         <v>8</v>
       </c>
-      <c r="F70" s="44" t="s">
-        <v>446</v>
-      </c>
-      <c r="G70" s="31" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A71" s="30" t="s">
-        <v>480</v>
-      </c>
-      <c r="B71" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="C71" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D71" s="31" t="s">
-        <v>481</v>
-      </c>
-      <c r="E71" s="32">
-        <v>13</v>
-      </c>
-      <c r="F71" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="G71" s="31" t="s">
+      <c r="F75" s="46" t="s">
+        <v>519</v>
+      </c>
+      <c r="G75" s="32" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" s="31" t="s">
+        <v>332</v>
+      </c>
+      <c r="B76" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="C76" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D76" s="32" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A72" s="30" t="s">
-        <v>483</v>
-      </c>
-      <c r="B72" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="C72" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D72" s="31" t="s">
-        <v>392</v>
-      </c>
-      <c r="E72" s="32">
-        <v>3</v>
-      </c>
-      <c r="F72" s="44" t="s">
-        <v>367</v>
-      </c>
-      <c r="G72" s="31" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="30" t="s">
-        <v>485</v>
-      </c>
-      <c r="B73" s="31" t="s">
-        <v>320</v>
-      </c>
-      <c r="C73" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D73" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E73" s="32">
-        <v>8</v>
-      </c>
-      <c r="F73" s="45" t="s">
-        <v>437</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A74" s="30" t="s">
-        <v>487</v>
-      </c>
-      <c r="B74" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D74" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E74" s="32">
-        <v>8</v>
-      </c>
-      <c r="F74" s="44" t="s">
-        <v>446</v>
-      </c>
-      <c r="G74" s="31" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A75" s="30" t="s">
-        <v>489</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="C75" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D75" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E75" s="32">
-        <v>8</v>
-      </c>
-      <c r="F75" s="45" t="s">
-        <v>446</v>
-      </c>
-      <c r="G75" s="31" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A76" s="30" t="s">
-        <v>332</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D76" s="31" t="s">
-        <v>409</v>
-      </c>
-      <c r="E76" s="32" t="s">
-        <v>491</v>
-      </c>
-      <c r="F76" s="44" t="s">
-        <v>446</v>
-      </c>
-      <c r="G76" s="31" t="s">
-        <v>492</v>
+      <c r="E76" s="33" t="s">
+        <v>564</v>
+      </c>
+      <c r="F76" s="45" t="s">
+        <v>519</v>
+      </c>
+      <c r="G76" s="32" t="s">
+        <v>565</v>
       </c>
     </row>
   </sheetData>
@@ -7292,305 +8149,305 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>493</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
+      <c r="A1" s="53" t="s">
+        <v>566</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="53" t="s">
-        <v>494</v>
-      </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
+      <c r="A3" s="54" t="s">
+        <v>567</v>
+      </c>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="54" t="s">
-        <v>495</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>496</v>
+      <c r="B4" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="56">
+      <c r="A5" s="56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Done")</f>
       </c>
-      <c r="C5" s="57">
+      <c r="C5" s="58">
         <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Done")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="56" t="s">
         <v>314</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"In Progress")</f>
       </c>
-      <c r="C6" s="57">
+      <c r="C6" s="58">
         <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"In Progress")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="56" t="s">
         <v>274</v>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Not Started")</f>
       </c>
-      <c r="C7" s="57">
+      <c r="C7" s="58">
         <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Not Started")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
-        <v>497</v>
-      </c>
-      <c r="B8" s="56">
+      <c r="A8" s="56" t="s">
+        <v>570</v>
+      </c>
+      <c r="B8" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Backlog")</f>
       </c>
-      <c r="C8" s="57">
+      <c r="C8" s="58">
         <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Backlog")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="B9" s="56">
+      <c r="A9" s="56" t="s">
+        <v>571</v>
+      </c>
+      <c r="B9" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Blocked")</f>
       </c>
-      <c r="C9" s="57">
+      <c r="C9" s="58">
         <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,COUNTIF('Feature List'!$G$5:$G$200,"Blocked")/COUNTA('Feature List'!$G$5:$G$200))</f>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="58" t="s">
-        <v>499</v>
-      </c>
-      <c r="B10" s="59">
+      <c r="A10" s="59" t="s">
+        <v>572</v>
+      </c>
+      <c r="B10" s="60">
         <f>COUNTA('Feature List'!$G$5:$G$200)</f>
       </c>
-      <c r="C10" s="60">
+      <c r="C10" s="61">
         <f>IF(COUNTA('Feature List'!$G$5:$G$200)=0,0,1)</f>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="53" t="s">
+      <c r="A12" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="54" t="s">
+      <c r="A13" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="54" t="s">
-        <v>495</v>
-      </c>
-      <c r="C13" s="54" t="s">
-        <v>496</v>
+      <c r="B13" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="C13" s="55" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="56">
+      <c r="B14" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Not Tested")</f>
       </c>
-      <c r="C14" s="57">
+      <c r="C14" s="58">
         <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Not Tested")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="56" t="s">
         <v>314</v>
       </c>
-      <c r="B15" s="56">
+      <c r="B15" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"In Progress")</f>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="58">
         <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"In Progress")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="55" t="s">
+      <c r="A16" s="56" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="56">
+      <c r="B16" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Pass")</f>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="58">
         <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Pass")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="55" t="s">
-        <v>500</v>
-      </c>
-      <c r="B17" s="56">
+      <c r="A17" s="56" t="s">
+        <v>573</v>
+      </c>
+      <c r="B17" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Failed")</f>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="58">
         <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Failed")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="55" t="s">
-        <v>498</v>
-      </c>
-      <c r="B18" s="56">
+      <c r="A18" s="56" t="s">
+        <v>571</v>
+      </c>
+      <c r="B18" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Blocked")</f>
       </c>
-      <c r="C18" s="57">
+      <c r="C18" s="58">
         <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,COUNTIF('Feature List'!$I$5:$I$200,"Blocked")/COUNTA('Feature List'!$I$5:$I$200))</f>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="58" t="s">
-        <v>499</v>
-      </c>
-      <c r="B19" s="59">
+      <c r="A19" s="59" t="s">
+        <v>572</v>
+      </c>
+      <c r="B19" s="60">
         <f>COUNTA('Feature List'!$I$5:$I$200)</f>
       </c>
-      <c r="C19" s="60">
+      <c r="C19" s="61">
         <f>IF(COUNTA('Feature List'!$I$5:$I$200)=0,0,1)</f>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B22" s="54" t="s">
-        <v>495</v>
-      </c>
-      <c r="C22" s="54" t="s">
-        <v>496</v>
+      <c r="B22" s="55" t="s">
+        <v>568</v>
+      </c>
+      <c r="C22" s="55" t="s">
+        <v>569</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="55" t="s">
+      <c r="A23" s="56" t="s">
         <v>17</v>
       </c>
-      <c r="B23" s="56">
+      <c r="B23" s="57">
         <f>COUNTIF('Feature List'!$F$5:$F$200,"Existing")</f>
       </c>
-      <c r="C23" s="57">
+      <c r="C23" s="58">
         <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"Existing")/COUNTA('Feature List'!$F$5:$F$200))</f>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="56" t="s">
         <v>268</v>
       </c>
-      <c r="B24" s="56">
+      <c r="B24" s="57">
         <f>COUNTIF('Feature List'!$F$5:$F$200,"DevOps Backlog")</f>
       </c>
-      <c r="C24" s="57">
+      <c r="C24" s="58">
         <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"DevOps Backlog")/COUNTA('Feature List'!$F$5:$F$200))</f>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="56" t="s">
         <v>291</v>
       </c>
-      <c r="B25" s="56">
+      <c r="B25" s="57">
         <f>COUNTIF('Feature List'!$F$5:$F$200,"New Requirement")</f>
       </c>
-      <c r="C25" s="57">
+      <c r="C25" s="58">
         <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"New Requirement")/COUNTA('Feature List'!$F$5:$F$200))</f>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="B26" s="59">
+      <c r="B26" s="60">
         <f>COUNTIF('Feature List'!$F$5:$F$200,"Nice to Have")</f>
       </c>
-      <c r="C26" s="60">
+      <c r="C26" s="61">
         <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,COUNTIF('Feature List'!$F$5:$F$200,"Nice to Have")/COUNTA('Feature List'!$F$5:$F$200))</f>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="58" t="s">
-        <v>499</v>
-      </c>
-      <c r="B27" s="59">
+      <c r="A27" s="59" t="s">
+        <v>572</v>
+      </c>
+      <c r="B27" s="60">
         <f>COUNTA('Feature List'!$F$5:$F$200)</f>
       </c>
-      <c r="C27" s="60">
+      <c r="C27" s="61">
         <f>IF(COUNTA('Feature List'!$F$5:$F$200)=0,0,1)</f>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="61" t="s">
-        <v>501</v>
-      </c>
-      <c r="B28" s="61"/>
-      <c r="C28" s="61"/>
+      <c r="A28" s="62" t="s">
+        <v>574</v>
+      </c>
+      <c r="B28" s="62"/>
+      <c r="C28" s="62"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="55" t="s">
-        <v>502</v>
-      </c>
-      <c r="B29" s="56">
+      <c r="A29" s="56" t="s">
+        <v>575</v>
+      </c>
+      <c r="B29" s="57">
         <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="55" t="s">
-        <v>503</v>
-      </c>
-      <c r="B30" s="56">
+      <c r="A30" s="56" t="s">
+        <v>576</v>
+      </c>
+      <c r="B30" s="57">
         <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="55" t="s">
-        <v>504</v>
-      </c>
-      <c r="B31" s="56">
+      <c r="A31" s="56" t="s">
+        <v>577</v>
+      </c>
+      <c r="B31" s="57">
         <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="55" t="s">
-        <v>505</v>
-      </c>
-      <c r="B32" s="56">
+      <c r="A32" s="56" t="s">
+        <v>578</v>
+      </c>
+      <c r="B32" s="57">
         <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="55" t="s">
-        <v>506</v>
-      </c>
-      <c r="B33" s="56">
+      <c r="A33" s="56" t="s">
+        <v>579</v>
+      </c>
+      <c r="B33" s="57">
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="55" t="s">
-        <v>507</v>
-      </c>
-      <c r="B34" s="56">
+      <c r="A34" s="56" t="s">
+        <v>580</v>
+      </c>
+      <c r="B34" s="57">
         <v>2</v>
       </c>
     </row>
@@ -7617,73 +8474,73 @@
   </cols>
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
-        <v>508</v>
-      </c>
-      <c r="B1" s="52"/>
+      <c r="A1" s="53" t="s">
+        <v>581</v>
+      </c>
+      <c r="B1" s="53"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="62" t="s">
-        <v>509</v>
-      </c>
-      <c r="B3" s="63" t="s">
-        <v>510</v>
+      <c r="A3" s="63" t="s">
+        <v>582</v>
+      </c>
+      <c r="B3" s="64" t="s">
+        <v>583</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="64" t="s">
+      <c r="A4" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="65" t="s">
-        <v>511</v>
+      <c r="B4" s="66" t="s">
+        <v>584</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="64" t="s">
+      <c r="A5" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="65" t="s">
-        <v>512</v>
+      <c r="B5" s="66" t="s">
+        <v>585</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="65" t="s">
-        <v>513</v>
+      <c r="B6" s="66" t="s">
+        <v>586</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="64" t="s">
+      <c r="A7" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="65" t="s">
-        <v>514</v>
+      <c r="B7" s="66" t="s">
+        <v>587</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="64" t="s">
+      <c r="A8" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="65" t="s">
-        <v>515</v>
+      <c r="B8" s="66" t="s">
+        <v>588</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="65" t="s">
-        <v>516</v>
+      <c r="B9" s="66" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="64" t="s">
-        <v>517</v>
-      </c>
-      <c r="B10" s="65" t="s">
-        <v>518</v>
+      <c r="A10" s="65" t="s">
+        <v>590</v>
+      </c>
+      <c r="B10" s="66" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>

--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="610">
   <si>
     <t>MRI ERP Implementation Taxonomy — Feature List &amp; QA Tracker</t>
   </si>
@@ -1219,7 +1219,7 @@
     <t>3361</t>
   </si>
   <si>
-    <t>Added 2026-10-01. DevOps User Story 3361. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+    <t>Added 2026-10-01. DevOps User Story 3361. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet. | Tested 2026-10-08 — Pass</t>
   </si>
   <si>
     <t>Propose a link that does not exist today</t>
@@ -1231,7 +1231,7 @@
     <t>3362</t>
   </si>
   <si>
-    <t>Added 2026-10-01. DevOps User Story 3362. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+    <t>Added 2026-10-01. DevOps User Story 3362. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet. | Tested 2026-10-08 — Pass</t>
   </si>
   <si>
     <t>Keep proposed links out of agreed-scope derivation</t>
@@ -1291,7 +1291,61 @@
     <t>3367</t>
   </si>
   <si>
-    <t>Added 2026-10-01. DevOps User Story 3367. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+    <t>Added 2026-10-01. DevOps User Story 3367. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet. | Tested 2026-10-08 — Pass</t>
+  </si>
+  <si>
+    <t>Navigate to an item from a comparison diff card</t>
+  </si>
+  <si>
+    <t>From each diff card in the comparison view, "Go to item" / "Open business process" / "Open MRI process" links jump directly to that changed item in the app. A "← Return to comparison" button re-opens the overlay at the same card. Navigation links are only shown when the item still exists in the current version.</t>
+  </si>
+  <si>
+    <t>src/components/compareView.js · setCompareNavigator() · src/main.js · compareView CSS</t>
+  </si>
+  <si>
+    <t>3368</t>
+  </si>
+  <si>
+    <t>Added 2026-10-08. comparison-links branch (commit 448b05b). Not yet merged to master.</t>
+  </si>
+  <si>
+    <t>Client Discovery</t>
+  </si>
+  <si>
+    <t>As-Is Discovery page per process</t>
+  </si>
+  <si>
+    <t>A full-page overlay accessible from any process panel (both Business and MRI System views) via an "As-Is Discovery" button. Captures: process narrative, roles &amp; responsibilities, frequency &amp; volume, tools &amp; workarounds, controls &amp; impact, evidence (source, date, participants, confidence), variations, and client target state. Criticality and discovery-status dropdowns update the badge bar instantly. "← Back to process" restores the panel.</t>
+  </si>
+  <si>
+    <t>src/components/discoveryPage.js · src/discoveryData.js · main.js · main.css</t>
+  </si>
+  <si>
+    <t>3369</t>
+  </si>
+  <si>
+    <t>Added 2026-10-08. client-as-is-discovery branch. Not yet merged to master.</t>
+  </si>
+  <si>
+    <t>As-Is Discovery data persisted per client version</t>
+  </si>
+  <si>
+    <t>Discovery data (all fields, criticality, status) is snapshotted when saving a version and restored when loading one. Data is blank when loading a version saved before this feature. Read-only in built-in baselines (Original and Discovery Baseline).</t>
+  </si>
+  <si>
+    <t>src/discoveryData.js · snapshotDiscovery() / restoreDiscovery() · main.js · versions.js</t>
+  </si>
+  <si>
+    <t>Added 2026-10-08. Part of story 3369 (client-as-is-discovery branch).</t>
+  </si>
+  <si>
+    <t>As-Is Discovery button in process panels</t>
+  </si>
+  <si>
+    <t>The "As-Is Discovery" button appears in the badge bar of both the MRI System panel and the Business Process panel. Clicking it opens the discovery overlay for that process, pre-loaded with any previously saved data.</t>
+  </si>
+  <si>
+    <t>src/components/panel.js · src/components/businessView.js · main.js (MutationObserver)</t>
   </si>
   <si>
     <t>DevOps Backlog ⇄ App Feature Comparison</t>
@@ -2623,7 +2677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -6123,10 +6177,10 @@
         <v>18</v>
       </c>
       <c r="H102" s="26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I102" s="26" t="s">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J102" s="26" t="s">
         <v>400</v>
@@ -6158,10 +6212,10 @@
         <v>18</v>
       </c>
       <c r="H103" s="26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I103" s="26" t="s">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J103" s="26" t="s">
         <v>404</v>
@@ -6333,16 +6387,156 @@
         <v>18</v>
       </c>
       <c r="H108" s="26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I108" s="26" t="s">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J108" s="26" t="s">
         <v>424</v>
       </c>
       <c r="K108" s="26" t="s">
         <v>425</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="25">
+        <v>105</v>
+      </c>
+      <c r="B109" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C109" s="25" t="s">
+        <v>426</v>
+      </c>
+      <c r="D109" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="E109" s="25" t="s">
+        <v>428</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G109" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H109" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I109" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="J109" s="25" t="s">
+        <v>429</v>
+      </c>
+      <c r="K109" s="25" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" s="25">
+        <v>106</v>
+      </c>
+      <c r="B110" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="C110" s="25" t="s">
+        <v>432</v>
+      </c>
+      <c r="D110" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="E110" s="25" t="s">
+        <v>434</v>
+      </c>
+      <c r="F110" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G110" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H110" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I110" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="J110" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="K110" s="25" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" s="25">
+        <v>107</v>
+      </c>
+      <c r="B111" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="C111" s="25" t="s">
+        <v>437</v>
+      </c>
+      <c r="D111" s="25" t="s">
+        <v>438</v>
+      </c>
+      <c r="E111" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="F111" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G111" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H111" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I111" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="J111" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="K111" s="25" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="25">
+        <v>108</v>
+      </c>
+      <c r="B112" s="25" t="s">
+        <v>431</v>
+      </c>
+      <c r="C112" s="25" t="s">
+        <v>441</v>
+      </c>
+      <c r="D112" s="25" t="s">
+        <v>442</v>
+      </c>
+      <c r="E112" s="25" t="s">
+        <v>443</v>
+      </c>
+      <c r="F112" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G112" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="H112" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I112" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="J112" s="25" t="s">
+        <v>435</v>
+      </c>
+      <c r="K112" s="25" t="s">
+        <v>440</v>
       </c>
     </row>
   </sheetData>
@@ -6399,7 +6593,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="27" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="B1" s="27"/>
       <c r="C1" s="27"/>
@@ -6412,7 +6606,7 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="28" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -6425,7 +6619,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="29" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="B3" s="29"/>
       <c r="C3" s="29"/>
@@ -6438,28 +6632,28 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="30" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="E4" s="30" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="F4" s="30" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="H4" s="30" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="I4" s="30" t="s">
         <v>22</v>
@@ -6470,13 +6664,13 @@
         <v>21</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="C5" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D5" s="34" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E5" s="33">
         <v>3</v>
@@ -6485,7 +6679,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H5" s="32" t="s">
         <v>22</v>
@@ -6496,22 +6690,22 @@
         <v>40</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E6" s="38">
         <v>2</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H6" s="37" t="s">
         <v>22</v>
@@ -6519,25 +6713,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="31" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="C7" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D7" s="34" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E7" s="33">
         <v>2</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H7" s="32" t="s">
         <v>22</v>
@@ -6548,13 +6742,13 @@
         <v>44</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="C8" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D8" s="39" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="E8" s="38">
         <v>3</v>
@@ -6563,7 +6757,7 @@
         <v>41</v>
       </c>
       <c r="G8" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H8" s="37" t="s">
         <v>22</v>
@@ -6574,22 +6768,22 @@
         <v>36</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="C9" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D9" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E9" s="33">
         <v>3</v>
       </c>
       <c r="F9" s="32" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="G9" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H9" s="32" t="s">
         <v>22</v>
@@ -6600,13 +6794,13 @@
         <v>97</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="C10" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D10" s="39" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E10" s="38">
         <v>2</v>
@@ -6615,7 +6809,7 @@
         <v>94</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H10" s="37" t="s">
         <v>22</v>
@@ -6626,13 +6820,13 @@
         <v>74</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E11" s="33">
         <v>3</v>
@@ -6641,7 +6835,7 @@
         <v>71</v>
       </c>
       <c r="G11" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H11" s="32" t="s">
         <v>22</v>
@@ -6652,13 +6846,13 @@
         <v>78</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D12" s="39" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E12" s="38">
         <v>3</v>
@@ -6667,7 +6861,7 @@
         <v>75</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H12" s="37" t="s">
         <v>22</v>
@@ -6678,13 +6872,13 @@
         <v>81</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="C13" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="D13" s="34" t="s">
         <v>457</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>439</v>
       </c>
       <c r="E13" s="33">
         <v>2</v>
@@ -6693,7 +6887,7 @@
         <v>79</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H13" s="32" t="s">
         <v>22</v>
@@ -6704,13 +6898,13 @@
         <v>85</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D14" s="39" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E14" s="38">
         <v>2</v>
@@ -6719,7 +6913,7 @@
         <v>82</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H14" s="37" t="s">
         <v>22</v>
@@ -6730,13 +6924,13 @@
         <v>89</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="C15" s="33" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D15" s="34" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E15" s="33">
         <v>2</v>
@@ -6745,7 +6939,7 @@
         <v>86</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H15" s="32" t="s">
         <v>22</v>
@@ -6756,22 +6950,22 @@
         <v>66</v>
       </c>
       <c r="B16" s="37" t="s">
+        <v>478</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>456</v>
+      </c>
+      <c r="D16" s="39" t="s">
         <v>460</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>438</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>442</v>
       </c>
       <c r="E16" s="38">
         <v>3</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H16" s="37" t="s">
         <v>22</v>
@@ -6782,22 +6976,22 @@
         <v>55</v>
       </c>
       <c r="B17" s="32" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="C17" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E17" s="33">
         <v>3</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H17" s="32" t="s">
         <v>22</v>
@@ -6808,13 +7002,13 @@
         <v>174</v>
       </c>
       <c r="B18" s="37" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D18" s="40" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E18" s="38">
         <v>3</v>
@@ -6823,24 +7017,24 @@
         <v>175</v>
       </c>
       <c r="G18" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="C19" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D19" s="41" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E19" s="33">
         <v>3</v>
@@ -6849,10 +7043,10 @@
         <v>118</v>
       </c>
       <c r="G19" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H19" s="32" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -6860,51 +7054,51 @@
         <v>185</v>
       </c>
       <c r="B20" s="37" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D20" s="42" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E20" s="38">
         <v>5</v>
       </c>
       <c r="F20" s="37" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="G20" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="B21" s="32" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="C21" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D21" s="43" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E21" s="33">
         <v>3</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="G21" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H21" s="32" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -6912,22 +7106,22 @@
         <v>104</v>
       </c>
       <c r="B22" s="37" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="C22" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D22" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E22" s="38">
         <v>5</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H22" s="37" t="s">
         <v>22</v>
@@ -6938,13 +7132,13 @@
         <v>112</v>
       </c>
       <c r="B23" s="32" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="C23" s="33" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D23" s="34" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E23" s="33">
         <v>3</v>
@@ -6953,7 +7147,7 @@
         <v>109</v>
       </c>
       <c r="G23" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H23" s="32" t="s">
         <v>22</v>
@@ -6964,13 +7158,13 @@
         <v>108</v>
       </c>
       <c r="B24" s="37" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D24" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E24" s="38">
         <v>3</v>
@@ -6979,7 +7173,7 @@
         <v>105</v>
       </c>
       <c r="G24" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H24" s="37" t="s">
         <v>22</v>
@@ -6987,16 +7181,16 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="31" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="B25" s="32" t="s">
-        <v>479</v>
+        <v>497</v>
       </c>
       <c r="C25" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D25" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E25" s="33">
         <v>3</v>
@@ -7005,7 +7199,7 @@
         <v>158</v>
       </c>
       <c r="G25" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H25" s="32" t="s">
         <v>22</v>
@@ -7013,28 +7207,28 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="36" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="B26" s="37" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="C26" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D26" s="39" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E26" s="38">
         <v>2</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="G26" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -7042,13 +7236,13 @@
         <v>165</v>
       </c>
       <c r="B27" s="32" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="C27" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D27" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E27" s="33">
         <v>3</v>
@@ -7057,7 +7251,7 @@
         <v>162</v>
       </c>
       <c r="G27" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H27" s="32" t="s">
         <v>22</v>
@@ -7068,13 +7262,13 @@
         <v>93</v>
       </c>
       <c r="B28" s="37" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="C28" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D28" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E28" s="38">
         <v>3</v>
@@ -7083,7 +7277,7 @@
         <v>90</v>
       </c>
       <c r="G28" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H28" s="37" t="s">
         <v>22</v>
@@ -7091,25 +7285,25 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="31" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="B29" s="32" t="s">
-        <v>488</v>
+        <v>506</v>
       </c>
       <c r="C29" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E29" s="33">
         <v>3</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>489</v>
+        <v>507</v>
       </c>
       <c r="G29" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H29" s="32" t="s">
         <v>22</v>
@@ -7120,13 +7314,13 @@
         <v>145</v>
       </c>
       <c r="B30" s="37" t="s">
-        <v>490</v>
+        <v>508</v>
       </c>
       <c r="C30" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D30" s="39" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="E30" s="38">
         <v>3</v>
@@ -7135,7 +7329,7 @@
         <v>142</v>
       </c>
       <c r="G30" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H30" s="37" t="s">
         <v>22</v>
@@ -7146,13 +7340,13 @@
         <v>157</v>
       </c>
       <c r="B31" s="32" t="s">
-        <v>491</v>
+        <v>509</v>
       </c>
       <c r="C31" s="33" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D31" s="34" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E31" s="33">
         <v>5</v>
@@ -7161,10 +7355,10 @@
         <v>154</v>
       </c>
       <c r="G31" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H31" s="32" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -7172,13 +7366,13 @@
         <v>149</v>
       </c>
       <c r="B32" s="37" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="C32" s="38" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D32" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E32" s="38">
         <v>3</v>
@@ -7187,7 +7381,7 @@
         <v>146</v>
       </c>
       <c r="G32" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H32" s="37" t="s">
         <v>22</v>
@@ -7198,13 +7392,13 @@
         <v>153</v>
       </c>
       <c r="B33" s="32" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="C33" s="33" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E33" s="33">
         <v>3</v>
@@ -7213,7 +7407,7 @@
         <v>150</v>
       </c>
       <c r="G33" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H33" s="32" t="s">
         <v>22</v>
@@ -7221,25 +7415,25 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="36" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="C34" s="38" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D34" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E34" s="38">
         <v>5</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="G34" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H34" s="37" t="s">
         <v>22</v>
@@ -7247,25 +7441,25 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="B35" s="32" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="C35" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D35" s="34" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="E35" s="33">
         <v>5</v>
       </c>
       <c r="F35" s="32" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="G35" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H35" s="32" t="s">
         <v>22</v>
@@ -7276,13 +7470,13 @@
         <v>262</v>
       </c>
       <c r="B36" s="37" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="C36" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D36" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E36" s="38">
         <v>3</v>
@@ -7291,7 +7485,7 @@
         <v>259</v>
       </c>
       <c r="G36" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H36" s="37" t="s">
         <v>22</v>
@@ -7302,22 +7496,22 @@
         <v>190</v>
       </c>
       <c r="B37" s="32" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="C37" s="33" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D37" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E37" s="33">
         <v>5</v>
       </c>
       <c r="F37" s="32" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="G37" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H37" s="32" t="s">
         <v>22</v>
@@ -7328,13 +7522,13 @@
         <v>194</v>
       </c>
       <c r="B38" s="37" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="C38" s="38" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="D38" s="39" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E38" s="38">
         <v>3</v>
@@ -7343,7 +7537,7 @@
         <v>191</v>
       </c>
       <c r="G38" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H38" s="37" t="s">
         <v>22</v>
@@ -7354,13 +7548,13 @@
         <v>211</v>
       </c>
       <c r="B39" s="32" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="C39" s="33" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D39" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E39" s="33">
         <v>3</v>
@@ -7369,7 +7563,7 @@
         <v>208</v>
       </c>
       <c r="G39" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H39" s="32" t="s">
         <v>22</v>
@@ -7380,22 +7574,22 @@
         <v>215</v>
       </c>
       <c r="B40" s="37" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="C40" s="38" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D40" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E40" s="38">
         <v>2</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="G40" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H40" s="37" t="s">
         <v>22</v>
@@ -7406,25 +7600,25 @@
         <v>223</v>
       </c>
       <c r="B41" s="32" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E41" s="33">
         <v>3</v>
       </c>
       <c r="F41" s="32" t="s">
-        <v>509</v>
+        <v>527</v>
       </c>
       <c r="G41" s="35" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="H41" s="32" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -7432,22 +7626,22 @@
         <v>238</v>
       </c>
       <c r="B42" s="37" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
       <c r="C42" s="38" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D42" s="39" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E42" s="38">
         <v>5</v>
       </c>
       <c r="F42" s="37" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
       <c r="G42" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H42" s="37" t="s">
         <v>22</v>
@@ -7458,13 +7652,13 @@
         <v>242</v>
       </c>
       <c r="B43" s="32" t="s">
-        <v>514</v>
+        <v>532</v>
       </c>
       <c r="C43" s="33" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="D43" s="34" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="E43" s="33">
         <v>3</v>
@@ -7473,7 +7667,7 @@
         <v>239</v>
       </c>
       <c r="G43" s="35" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="H43" s="32" t="s">
         <v>22</v>
@@ -7481,7 +7675,7 @@
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="44" t="s">
-        <v>515</v>
+        <v>533</v>
       </c>
       <c r="B45" s="44"/>
       <c r="C45" s="44"/>
@@ -7494,25 +7688,25 @@
     </row>
     <row r="46" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="30" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="B46" s="30" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C46" s="30" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="D46" s="30" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="E46" s="30" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="F46" s="30" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="G46" s="30" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
       <c r="H46" s="30" t="s">
         <v>22</v>
@@ -7529,19 +7723,19 @@
         <v>265</v>
       </c>
       <c r="C47" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D47" s="32" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E47" s="33">
         <v>2</v>
       </c>
       <c r="F47" s="45" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="G47" s="32" t="s">
-        <v>517</v>
+        <v>535</v>
       </c>
       <c r="H47" s="32"/>
       <c r="I47" s="32"/>
@@ -7551,22 +7745,22 @@
         <v>275</v>
       </c>
       <c r="B48" s="32" t="s">
-        <v>518</v>
+        <v>536</v>
       </c>
       <c r="C48" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E48" s="33">
         <v>2</v>
       </c>
       <c r="F48" s="46" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G48" s="32" t="s">
-        <v>520</v>
+        <v>538</v>
       </c>
       <c r="H48" s="32"/>
       <c r="I48" s="32"/>
@@ -7579,19 +7773,19 @@
         <v>278</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E49" s="33">
         <v>8</v>
       </c>
       <c r="F49" s="46" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G49" s="32" t="s">
-        <v>522</v>
+        <v>540</v>
       </c>
       <c r="H49" s="32"/>
       <c r="I49" s="32"/>
@@ -7601,29 +7795,29 @@
         <v>286</v>
       </c>
       <c r="B50" s="32" t="s">
-        <v>523</v>
+        <v>541</v>
       </c>
       <c r="C50" s="33" t="s">
-        <v>521</v>
+        <v>539</v>
       </c>
       <c r="D50" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E50" s="33">
         <v>5</v>
       </c>
       <c r="F50" s="46" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G50" s="32" t="s">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="H50" s="32"/>
       <c r="I50" s="32"/>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="47" t="s">
-        <v>525</v>
+        <v>543</v>
       </c>
       <c r="B52" s="47"/>
       <c r="C52" s="47"/>
@@ -7645,7 +7839,7 @@
         <v>6</v>
       </c>
       <c r="D53" s="30" t="s">
-        <v>526</v>
+        <v>544</v>
       </c>
       <c r="E53" s="30" t="s">
         <v>22</v>
@@ -7674,7 +7868,7 @@
         <v>25</v>
       </c>
       <c r="D54" s="32" t="s">
-        <v>527</v>
+        <v>545</v>
       </c>
       <c r="E54" s="32"/>
       <c r="F54" s="32"/>
@@ -7693,7 +7887,7 @@
         <v>47</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>528</v>
+        <v>546</v>
       </c>
       <c r="E55" s="32"/>
       <c r="F55" s="32"/>
@@ -7712,7 +7906,7 @@
         <v>140</v>
       </c>
       <c r="D56" s="32" t="s">
-        <v>529</v>
+        <v>547</v>
       </c>
       <c r="E56" s="32"/>
       <c r="F56" s="32"/>
@@ -7731,7 +7925,7 @@
         <v>197</v>
       </c>
       <c r="D57" s="32" t="s">
-        <v>530</v>
+        <v>548</v>
       </c>
       <c r="E57" s="32"/>
       <c r="F57" s="32"/>
@@ -7750,7 +7944,7 @@
         <v>206</v>
       </c>
       <c r="D58" s="32" t="s">
-        <v>531</v>
+        <v>549</v>
       </c>
       <c r="E58" s="32"/>
       <c r="F58" s="32"/>
@@ -7760,7 +7954,7 @@
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="50" t="s">
-        <v>532</v>
+        <v>550</v>
       </c>
       <c r="B60" s="50"/>
       <c r="C60" s="50"/>
@@ -7782,13 +7976,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="30" t="s">
-        <v>533</v>
+        <v>551</v>
       </c>
       <c r="E61" s="30" t="s">
         <v>8</v>
       </c>
       <c r="F61" s="30" t="s">
-        <v>534</v>
+        <v>552</v>
       </c>
       <c r="G61" s="30" t="s">
         <v>22</v>
@@ -7808,16 +8002,16 @@
         <v>67</v>
       </c>
       <c r="C62" s="32" t="s">
-        <v>535</v>
+        <v>553</v>
       </c>
       <c r="D62" s="32" t="s">
-        <v>536</v>
+        <v>554</v>
       </c>
       <c r="E62" s="51" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="F62" s="52" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
       <c r="G62" s="52"/>
       <c r="H62" s="52"/>
@@ -7831,16 +8025,16 @@
         <v>67</v>
       </c>
       <c r="C63" s="32" t="s">
-        <v>538</v>
+        <v>556</v>
       </c>
       <c r="D63" s="32" t="s">
-        <v>539</v>
+        <v>557</v>
       </c>
       <c r="E63" s="51" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="F63" s="52" t="s">
-        <v>540</v>
+        <v>558</v>
       </c>
       <c r="G63" s="52"/>
       <c r="H63" s="52"/>
@@ -7854,16 +8048,16 @@
         <v>141</v>
       </c>
       <c r="C64" s="32" t="s">
-        <v>541</v>
+        <v>559</v>
       </c>
       <c r="D64" s="32" t="s">
-        <v>542</v>
+        <v>560</v>
       </c>
       <c r="E64" s="51" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="F64" s="52" t="s">
-        <v>543</v>
+        <v>561</v>
       </c>
       <c r="G64" s="52"/>
       <c r="H64" s="52"/>
@@ -7877,16 +8071,16 @@
         <v>299</v>
       </c>
       <c r="C65" s="32" t="s">
-        <v>544</v>
+        <v>562</v>
       </c>
       <c r="D65" s="32" t="s">
-        <v>545</v>
+        <v>563</v>
       </c>
       <c r="E65" s="51" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="F65" s="52" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="G65" s="52"/>
       <c r="H65" s="52"/>
@@ -7900,16 +8094,16 @@
         <v>186</v>
       </c>
       <c r="C66" s="32" t="s">
-        <v>547</v>
+        <v>565</v>
       </c>
       <c r="D66" s="32" t="s">
-        <v>548</v>
+        <v>566</v>
       </c>
       <c r="E66" s="51" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="F66" s="52" t="s">
-        <v>549</v>
+        <v>567</v>
       </c>
       <c r="G66" s="52"/>
       <c r="H66" s="52"/>
@@ -7917,7 +8111,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="44" t="s">
-        <v>550</v>
+        <v>568</v>
       </c>
       <c r="B68" s="44"/>
       <c r="C68" s="44"/>
@@ -7928,163 +8122,163 @@
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="30" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="C69" s="30" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="D69" s="30" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="E69" s="30" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="F69" s="30" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="G69" s="30" t="s">
-        <v>516</v>
+        <v>534</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="31" t="s">
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="B70" s="32" t="s">
         <v>306</v>
       </c>
       <c r="C70" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D70" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E70" s="33">
         <v>8</v>
       </c>
       <c r="F70" s="45" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G70" s="32" t="s">
-        <v>552</v>
+        <v>570</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="31" t="s">
-        <v>553</v>
+        <v>571</v>
       </c>
       <c r="B71" s="32" t="s">
         <v>311</v>
       </c>
       <c r="C71" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D71" s="32" t="s">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="E71" s="33">
         <v>13</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G71" s="32" t="s">
-        <v>555</v>
+        <v>573</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="31" t="s">
-        <v>556</v>
+        <v>574</v>
       </c>
       <c r="B72" s="32" t="s">
         <v>316</v>
       </c>
       <c r="C72" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D72" s="32" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="E72" s="33">
         <v>3</v>
       </c>
       <c r="F72" s="45" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="G72" s="32" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="31" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="B73" s="32" t="s">
         <v>320</v>
       </c>
       <c r="C73" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D73" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E73" s="33">
         <v>8</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>510</v>
+        <v>528</v>
       </c>
       <c r="G73" s="32" t="s">
-        <v>559</v>
+        <v>577</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="31" t="s">
-        <v>560</v>
+        <v>578</v>
       </c>
       <c r="B74" s="32" t="s">
         <v>324</v>
       </c>
       <c r="C74" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D74" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E74" s="33">
         <v>8</v>
       </c>
       <c r="F74" s="45" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G74" s="32" t="s">
-        <v>561</v>
+        <v>579</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="31" t="s">
-        <v>562</v>
+        <v>580</v>
       </c>
       <c r="B75" s="32" t="s">
         <v>327</v>
       </c>
       <c r="C75" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D75" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E75" s="33">
         <v>8</v>
       </c>
       <c r="F75" s="46" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G75" s="32" t="s">
-        <v>563</v>
+        <v>581</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
@@ -8095,19 +8289,19 @@
         <v>330</v>
       </c>
       <c r="C76" s="33" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="D76" s="32" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="F76" s="45" t="s">
-        <v>519</v>
+        <v>537</v>
       </c>
       <c r="G76" s="32" t="s">
-        <v>565</v>
+        <v>583</v>
       </c>
     </row>
   </sheetData>
@@ -8150,14 +8344,14 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>566</v>
+        <v>584</v>
       </c>
       <c r="B1" s="53"/>
       <c r="C1" s="53"/>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="54" t="s">
-        <v>567</v>
+        <v>585</v>
       </c>
       <c r="B3" s="54"/>
       <c r="C3" s="54"/>
@@ -8167,10 +8361,10 @@
         <v>8</v>
       </c>
       <c r="B4" s="55" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="C4" s="55" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -8208,7 +8402,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="56" t="s">
-        <v>570</v>
+        <v>588</v>
       </c>
       <c r="B8" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Backlog")</f>
@@ -8219,7 +8413,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="56" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="B9" s="57">
         <f>COUNTIF('Feature List'!$G$5:$G$200,"Blocked")</f>
@@ -8230,7 +8424,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="59" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="B10" s="60">
         <f>COUNTA('Feature List'!$G$5:$G$200)</f>
@@ -8251,10 +8445,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="55" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="C13" s="55" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -8292,7 +8486,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="56" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="B17" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Failed")</f>
@@ -8303,7 +8497,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="56" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="B18" s="57">
         <f>COUNTIF('Feature List'!$I$5:$I$200,"Blocked")</f>
@@ -8314,7 +8508,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="59" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="B19" s="60">
         <f>COUNTA('Feature List'!$I$5:$I$200)</f>
@@ -8335,10 +8529,10 @@
         <v>7</v>
       </c>
       <c r="B22" s="55" t="s">
-        <v>568</v>
+        <v>586</v>
       </c>
       <c r="C22" s="55" t="s">
-        <v>569</v>
+        <v>587</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -8387,7 +8581,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="59" t="s">
-        <v>572</v>
+        <v>590</v>
       </c>
       <c r="B27" s="60">
         <f>COUNTA('Feature List'!$F$5:$F$200)</f>
@@ -8398,14 +8592,14 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="62" t="s">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="B28" s="62"/>
       <c r="C28" s="62"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="56" t="s">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="B29" s="57">
         <v>60</v>
@@ -8413,7 +8607,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="56" t="s">
-        <v>576</v>
+        <v>594</v>
       </c>
       <c r="B30" s="57">
         <v>60</v>
@@ -8421,7 +8615,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="56" t="s">
-        <v>577</v>
+        <v>595</v>
       </c>
       <c r="B31" s="57">
         <v>4</v>
@@ -8429,7 +8623,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="56" t="s">
-        <v>578</v>
+        <v>596</v>
       </c>
       <c r="B32" s="57">
         <v>4</v>
@@ -8437,7 +8631,7 @@
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="56" t="s">
-        <v>579</v>
+        <v>597</v>
       </c>
       <c r="B33" s="57">
         <v>0</v>
@@ -8445,7 +8639,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="56" t="s">
-        <v>580</v>
+        <v>598</v>
       </c>
       <c r="B34" s="57">
         <v>2</v>
@@ -8475,16 +8669,16 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="53" t="s">
-        <v>581</v>
+        <v>599</v>
       </c>
       <c r="B1" s="53"/>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="63" t="s">
-        <v>582</v>
+        <v>600</v>
       </c>
       <c r="B3" s="64" t="s">
-        <v>583</v>
+        <v>601</v>
       </c>
     </row>
     <row r="4" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8492,7 +8686,7 @@
         <v>7</v>
       </c>
       <c r="B4" s="66" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
     </row>
     <row r="5" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8500,7 +8694,7 @@
         <v>8</v>
       </c>
       <c r="B5" s="66" t="s">
-        <v>585</v>
+        <v>603</v>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8508,7 +8702,7 @@
         <v>9</v>
       </c>
       <c r="B6" s="66" t="s">
-        <v>586</v>
+        <v>604</v>
       </c>
     </row>
     <row r="7" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8516,7 +8710,7 @@
         <v>10</v>
       </c>
       <c r="B7" s="66" t="s">
-        <v>587</v>
+        <v>605</v>
       </c>
     </row>
     <row r="8" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8524,7 +8718,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="66" t="s">
-        <v>588</v>
+        <v>606</v>
       </c>
     </row>
     <row r="9" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -8532,15 +8726,15 @@
         <v>12</v>
       </c>
       <c r="B9" s="66" t="s">
-        <v>589</v>
+        <v>607</v>
       </c>
     </row>
     <row r="10" ht="34" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="65" t="s">
-        <v>590</v>
+        <v>608</v>
       </c>
       <c r="B10" s="66" t="s">
-        <v>591</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>

--- a/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
+++ b/MRI_Taxonomy_Feature_List_QA_v2.0.xlsx
@@ -1195,7 +1195,7 @@
     <t>3359</t>
   </si>
   <si>
-    <t>Added 2026-10-01. DevOps Feature 3359. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+    <t>Added 2026-10-01. DevOps Feature 3359. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet. | Tested 2026-10-08: Pass</t>
   </si>
   <si>
     <t>Imply a proposal across links in both directions</t>
@@ -1207,7 +1207,7 @@
     <t>3360</t>
   </si>
   <si>
-    <t>Added 2026-10-01. DevOps User Story 3360. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+    <t>Added 2026-10-01. DevOps User Story 3360. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet. | Tested 2026-10-08: Pass</t>
   </si>
   <si>
     <t>Prevent proposal propagation from cascading</t>
@@ -1243,7 +1243,7 @@
     <t>3363</t>
   </si>
   <si>
-    <t>Added 2026-10-01. DevOps User Story 3363. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+    <t>Added 2026-10-01. DevOps User Story 3363. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet. | Tested 2026-10-08: Pass</t>
   </si>
   <si>
     <t>Value-Add Proposals Document</t>
@@ -1255,7 +1255,7 @@
     <t>3364</t>
   </si>
   <si>
-    <t>Added 2026-10-01. DevOps Feature 3364. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet.</t>
+    <t>Added 2026-10-01. DevOps Feature 3364. Implementation confirmed present by code inspection; core flow (propose a card, filter by Proposed Scope) smoke-tested in browser — no formal QA test pass run yet. | Tested 2026-10-08: Pass</t>
   </si>
   <si>
     <t>Exclude proposals from generated documents by default</t>
@@ -6107,10 +6107,10 @@
         <v>18</v>
       </c>
       <c r="H100" s="26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J100" s="26" t="s">
         <v>392</v>
@@ -6142,10 +6142,10 @@
         <v>18</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I101" s="26" t="s">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J101" s="26" t="s">
         <v>396</v>
@@ -6247,10 +6247,10 @@
         <v>18</v>
       </c>
       <c r="H104" s="26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I104" s="26" t="s">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J104" s="26" t="s">
         <v>408</v>
@@ -6282,10 +6282,10 @@
         <v>18</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="I105" s="26" t="s">
-        <v>309</v>
+        <v>30</v>
       </c>
       <c r="J105" s="26" t="s">
         <v>412</v>
